--- a/Teacher_Schedule_Review_and_Tally.xlsx
+++ b/Teacher_Schedule_Review_and_Tally.xlsx
@@ -7498,14 +7498,14 @@
         </is>
       </c>
       <c r="C255" s="2" t="n"/>
-      <c r="D255" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E255" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D255" s="6" t="inlineStr">
+        <is>
+          <t>131-3: British Literature H - 3</t>
+        </is>
+      </c>
+      <c r="E255" s="6" t="inlineStr">
+        <is>
+          <t>131-3: British Literature H - 3</t>
         </is>
       </c>
       <c r="F255" s="2" t="n"/>
@@ -7668,14 +7668,14 @@
         </is>
       </c>
       <c r="C260" s="2" t="n"/>
-      <c r="D260" s="6" t="inlineStr">
-        <is>
-          <t>131-3: British Literature H - 3</t>
-        </is>
-      </c>
-      <c r="E260" s="6" t="inlineStr">
-        <is>
-          <t>131-3: British Literature H - 3</t>
+      <c r="D260" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E260" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F260" s="2" t="n"/>
@@ -7752,11 +7752,11 @@
         </is>
       </c>
       <c r="C263" s="2" t="n"/>
-      <c r="D263" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="E263" s="7" t="n">
-        <v>3</v>
+      <c r="D263" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E263" s="9" t="n">
+        <v>4</v>
       </c>
       <c r="F263" s="2" t="n"/>
       <c r="G263" s="7" t="n">
@@ -9815,14 +9815,14 @@
         </is>
       </c>
       <c r="C339" s="2" t="n"/>
-      <c r="D339" s="6" t="inlineStr">
-        <is>
-          <t>543-1: Anatomy/Physiology H - 1</t>
-        </is>
-      </c>
-      <c r="E339" s="6" t="inlineStr">
-        <is>
-          <t>543-1: Anatomy/Physiology H - 1</t>
+      <c r="D339" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E339" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F339" s="2" t="n"/>
@@ -9985,14 +9985,14 @@
         </is>
       </c>
       <c r="C344" s="2" t="n"/>
-      <c r="D344" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E344" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D344" s="6" t="inlineStr">
+        <is>
+          <t>542-1: Anatomy/Physiology - 1</t>
+        </is>
+      </c>
+      <c r="E344" s="6" t="inlineStr">
+        <is>
+          <t>542-1: Anatomy/Physiology - 1</t>
         </is>
       </c>
       <c r="F344" s="2" t="n"/>
@@ -10021,12 +10021,12 @@
       <c r="C345" s="2" t="n"/>
       <c r="D345" s="6" t="inlineStr">
         <is>
-          <t>542-1: Anatomy/Physiology - 1</t>
+          <t>543-1: Anatomy/Physiology H - 1</t>
         </is>
       </c>
       <c r="E345" s="6" t="inlineStr">
         <is>
-          <t>542-1: Anatomy/Physiology - 1</t>
+          <t>543-1: Anatomy/Physiology H - 1</t>
         </is>
       </c>
       <c r="F345" s="2" t="n"/>
@@ -10248,14 +10248,14 @@
         </is>
       </c>
       <c r="C354" s="2" t="n"/>
-      <c r="D354" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E354" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D354" s="6" t="inlineStr">
+        <is>
+          <t>430-4: Algebra II/Trig - 4</t>
+        </is>
+      </c>
+      <c r="E354" s="6" t="inlineStr">
+        <is>
+          <t>430-4: Algebra II/Trig - 4</t>
         </is>
       </c>
       <c r="F354" s="2" t="n"/>
@@ -10316,14 +10316,14 @@
         </is>
       </c>
       <c r="C356" s="2" t="n"/>
-      <c r="D356" s="6" t="inlineStr">
-        <is>
-          <t>430-4: Algebra II/Trig - 4</t>
-        </is>
-      </c>
-      <c r="E356" s="6" t="inlineStr">
-        <is>
-          <t>430-4: Algebra II/Trig - 4</t>
+      <c r="D356" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E356" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F356" s="2" t="n"/>
@@ -10401,10 +10401,10 @@
       </c>
       <c r="C359" s="2" t="n"/>
       <c r="D359" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E359" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F359" s="2" t="n"/>
       <c r="G359" s="7" t="n">
@@ -13461,9 +13461,9 @@
           <t>UNASSIGNED</t>
         </is>
       </c>
-      <c r="E471" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="E471" s="6" t="inlineStr">
+        <is>
+          <t>765-2-S: AP Macroeconomics - 2</t>
         </is>
       </c>
       <c r="F471" s="2" t="n"/>
@@ -13665,9 +13665,9 @@
           <t>UNASSIGNED</t>
         </is>
       </c>
-      <c r="E477" s="6" t="inlineStr">
-        <is>
-          <t>765-2-S: AP Macroeconomics - 2</t>
+      <c r="E477" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F477" s="2" t="n"/>
@@ -13889,14 +13889,14 @@
         </is>
       </c>
       <c r="C486" s="2" t="n"/>
-      <c r="D486" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E486" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D486" s="6" t="inlineStr">
+        <is>
+          <t>530-2: Physics - 2</t>
+        </is>
+      </c>
+      <c r="E486" s="6" t="inlineStr">
+        <is>
+          <t>530-2: Physics - 2</t>
         </is>
       </c>
       <c r="F486" s="2" t="n"/>
@@ -13957,14 +13957,14 @@
         </is>
       </c>
       <c r="C488" s="2" t="n"/>
-      <c r="D488" s="6" t="inlineStr">
-        <is>
-          <t>530-2: Physics - 2</t>
-        </is>
-      </c>
-      <c r="E488" s="6" t="inlineStr">
-        <is>
-          <t>530-2: Physics - 2</t>
+      <c r="D488" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E488" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F488" s="2" t="n"/>
@@ -14041,11 +14041,11 @@
         </is>
       </c>
       <c r="C491" s="2" t="n"/>
-      <c r="D491" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="E491" s="7" t="n">
-        <v>3</v>
+      <c r="D491" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E491" s="9" t="n">
+        <v>5</v>
       </c>
       <c r="F491" s="2" t="n"/>
       <c r="G491" s="9" t="n">
@@ -14587,12 +14587,12 @@
       <c r="C511" s="2" t="n"/>
       <c r="D511" s="6" t="inlineStr">
         <is>
-          <t>830-4: Theology 11 - 4; 851-1-F: Spirituality of Vocation - 1</t>
+          <t>851-1-F: Spirituality of Vocation - 1</t>
         </is>
       </c>
       <c r="E511" s="6" t="inlineStr">
         <is>
-          <t>830-4: Theology 11 - 4; 851-8-S: Spirituality of Vocation - 8</t>
+          <t>851-8-S: Spirituality of Vocation - 8</t>
         </is>
       </c>
       <c r="F511" s="2" t="n"/>
@@ -14619,14 +14619,14 @@
         </is>
       </c>
       <c r="C512" s="2" t="n"/>
-      <c r="D512" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D512" s="6" t="inlineStr">
+        <is>
+          <t>830-4: Theology 11 - 4</t>
         </is>
       </c>
       <c r="E512" s="6" t="inlineStr">
         <is>
-          <t>851-5-S: Spirituality of Vocation - 5</t>
+          <t>830-4: Theology 11 - 4; 851-5-S: Spirituality of Vocation - 5</t>
         </is>
       </c>
       <c r="F512" s="2" t="n"/>
@@ -14704,7 +14704,7 @@
       </c>
       <c r="C515" s="2" t="n"/>
       <c r="D515" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E515" s="7" t="n">
         <v>3</v>
@@ -15111,9 +15111,9 @@
         </is>
       </c>
       <c r="C531" s="2" t="n"/>
-      <c r="D531" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D531" s="6" t="inlineStr">
+        <is>
+          <t>220-1-F: Music Theory - 1</t>
         </is>
       </c>
       <c r="E531" s="7" t="inlineStr">
@@ -15145,9 +15145,9 @@
         </is>
       </c>
       <c r="C532" s="2" t="n"/>
-      <c r="D532" s="6" t="inlineStr">
-        <is>
-          <t>220-1-F: Music Theory - 1</t>
+      <c r="D532" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="E532" s="7" t="inlineStr">
@@ -19416,12 +19416,12 @@
       <c r="C687" s="2" t="n"/>
       <c r="D687" s="6" t="inlineStr">
         <is>
-          <t>830-8: Theology 11 - 8</t>
+          <t>830-9: Theology 11 - 9</t>
         </is>
       </c>
       <c r="E687" s="6" t="inlineStr">
         <is>
-          <t>830-8: Theology 11 - 8</t>
+          <t>830-9: Theology 11 - 9</t>
         </is>
       </c>
       <c r="F687" s="2" t="n"/>
@@ -19484,12 +19484,12 @@
       <c r="C689" s="2" t="n"/>
       <c r="D689" s="6" t="inlineStr">
         <is>
-          <t>830-7: Theology 11 - 7</t>
+          <t>830-8: Theology 11 - 8</t>
         </is>
       </c>
       <c r="E689" s="6" t="inlineStr">
         <is>
-          <t>830-7: Theology 11 - 7</t>
+          <t>830-8: Theology 11 - 8</t>
         </is>
       </c>
       <c r="F689" s="2" t="n"/>
@@ -19518,12 +19518,12 @@
       <c r="C690" s="2" t="n"/>
       <c r="D690" s="6" t="inlineStr">
         <is>
-          <t>830-6: Theology 11 - 6</t>
+          <t>830-7: Theology 11 - 7</t>
         </is>
       </c>
       <c r="E690" s="6" t="inlineStr">
         <is>
-          <t>830-6: Theology 11 - 6</t>
+          <t>830-7: Theology 11 - 7</t>
         </is>
       </c>
       <c r="F690" s="2" t="n"/>
@@ -19550,14 +19550,14 @@
         </is>
       </c>
       <c r="C691" s="2" t="n"/>
-      <c r="D691" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E691" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D691" s="6" t="inlineStr">
+        <is>
+          <t>830-6: Theology 11 - 6</t>
+        </is>
+      </c>
+      <c r="E691" s="6" t="inlineStr">
+        <is>
+          <t>830-6: Theology 11 - 6</t>
         </is>
       </c>
       <c r="F691" s="2" t="n"/>
@@ -19584,14 +19584,14 @@
         </is>
       </c>
       <c r="C692" s="2" t="n"/>
-      <c r="D692" s="6" t="inlineStr">
-        <is>
-          <t>830-9: Theology 11 - 9</t>
-        </is>
-      </c>
-      <c r="E692" s="6" t="inlineStr">
-        <is>
-          <t>830-9: Theology 11 - 9</t>
+      <c r="D692" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E692" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F692" s="2" t="n"/>
@@ -19669,10 +19669,10 @@
       </c>
       <c r="C695" s="2" t="n"/>
       <c r="D695" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E695" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F695" s="2" t="n"/>
       <c r="G695" s="7" t="n">
@@ -20110,14 +20110,14 @@
         </is>
       </c>
       <c r="C712" s="2" t="n"/>
-      <c r="D712" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E712" s="6" t="inlineStr">
-        <is>
-          <t>2024-2-S: TV/Film Process and Principles - 2</t>
+      <c r="D712" s="6" t="inlineStr">
+        <is>
+          <t>2034-1-F: TV/Film Production &amp; Editing I - 1</t>
+        </is>
+      </c>
+      <c r="E712" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F712" s="2" t="n"/>
@@ -20178,9 +20178,9 @@
         </is>
       </c>
       <c r="C714" s="2" t="n"/>
-      <c r="D714" s="6" t="inlineStr">
-        <is>
-          <t>2034-1-F: TV/Film Production &amp; Editing I - 1</t>
+      <c r="D714" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="E714" s="6" t="inlineStr">
@@ -20217,9 +20217,9 @@
           <t>UNASSIGNED</t>
         </is>
       </c>
-      <c r="E715" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="E715" s="6" t="inlineStr">
+        <is>
+          <t>2024-2-S: TV/Film Process and Principles - 2</t>
         </is>
       </c>
       <c r="F715" s="2" t="n"/>
@@ -20331,10 +20331,10 @@
       </c>
       <c r="C719" s="2" t="n"/>
       <c r="D719" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E719" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="E719" s="9" t="n">
+        <v>4</v>
       </c>
       <c r="F719" s="2" t="n"/>
       <c r="G719" s="7" t="n">
@@ -22427,14 +22427,14 @@
         </is>
       </c>
       <c r="C796" s="2" t="n"/>
-      <c r="D796" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E796" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D796" s="6" t="inlineStr">
+        <is>
+          <t>531-2: Physics H - 2</t>
+        </is>
+      </c>
+      <c r="E796" s="6" t="inlineStr">
+        <is>
+          <t>531-2: Physics H - 2</t>
         </is>
       </c>
       <c r="F796" s="2" t="n"/>
@@ -22597,14 +22597,14 @@
         </is>
       </c>
       <c r="C801" s="2" t="n"/>
-      <c r="D801" s="6" t="inlineStr">
-        <is>
-          <t>531-2: Physics H - 2</t>
-        </is>
-      </c>
-      <c r="E801" s="6" t="inlineStr">
-        <is>
-          <t>531-2: Physics H - 2</t>
+      <c r="D801" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E801" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F801" s="2" t="n"/>
@@ -24379,14 +24379,14 @@
         </is>
       </c>
       <c r="C867" s="2" t="n"/>
-      <c r="D867" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E867" s="6" t="inlineStr">
-        <is>
-          <t>732-2-S: Business Law - 2</t>
+      <c r="D867" s="6" t="inlineStr">
+        <is>
+          <t>732-3-F: Business Law - 3</t>
+        </is>
+      </c>
+      <c r="E867" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F867" s="2" t="n"/>
@@ -24413,9 +24413,9 @@
         </is>
       </c>
       <c r="C868" s="2" t="n"/>
-      <c r="D868" s="6" t="inlineStr">
-        <is>
-          <t>732-3-F: Business Law - 3</t>
+      <c r="D868" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="E868" s="7" t="inlineStr">
@@ -24452,9 +24452,9 @@
           <t>UNASSIGNED</t>
         </is>
       </c>
-      <c r="E869" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="E869" s="6" t="inlineStr">
+        <is>
+          <t>732-2-S: Business Law - 2</t>
         </is>
       </c>
       <c r="F869" s="2" t="n"/>
@@ -24637,7 +24637,7 @@
         <v>4</v>
       </c>
       <c r="E875" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F875" s="2" t="n"/>
       <c r="G875" s="7" t="n">

--- a/Teacher_Schedule_Review_and_Tally.xlsx
+++ b/Teacher_Schedule_Review_and_Tally.xlsx
@@ -1939,14 +1939,14 @@
         </is>
       </c>
       <c r="C53" s="2" t="n"/>
-      <c r="D53" s="6" t="inlineStr">
-        <is>
-          <t>610-3-F: Health/PE - 3</t>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>610-10-S: Health/PE - 10</t>
+          <t>610-4-S: Health/PE - 4</t>
         </is>
       </c>
       <c r="F53" s="2" t="n"/>
@@ -1973,14 +1973,14 @@
         </is>
       </c>
       <c r="C54" s="2" t="n"/>
-      <c r="D54" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>610-3-F: Health/PE - 3</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>610-4-S: Health/PE - 4</t>
+          <t>610-10-S: Health/PE - 10</t>
         </is>
       </c>
       <c r="F54" s="2" t="n"/>
@@ -2007,14 +2007,14 @@
         </is>
       </c>
       <c r="C55" s="2" t="n"/>
-      <c r="D55" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E55" s="6" t="inlineStr">
-        <is>
-          <t>610-6-S: Health/PE - 6</t>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>610-5-F: Health/PE - 5</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F55" s="2" t="n"/>
@@ -2075,14 +2075,14 @@
         </is>
       </c>
       <c r="C57" s="2" t="n"/>
-      <c r="D57" s="6" t="inlineStr">
-        <is>
-          <t>610-5-F: Health/PE - 5</t>
-        </is>
-      </c>
-      <c r="E57" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t>610-6-S: Health/PE - 6</t>
         </is>
       </c>
       <c r="F57" s="2" t="n"/>
@@ -2129,7 +2129,7 @@
         <v>3</v>
       </c>
       <c r="E59" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F59" s="2" t="n"/>
       <c r="G59" s="7" t="n">
@@ -2533,14 +2533,14 @@
         </is>
       </c>
       <c r="C75" s="2" t="n"/>
-      <c r="D75" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>491-1: AP Computer Science Principles - 1</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>472-2-S: Web Design - 2</t>
+          <t>491-1: AP Computer Science Principles - 1</t>
         </is>
       </c>
       <c r="F75" s="2" t="n"/>
@@ -2603,12 +2603,12 @@
       <c r="C77" s="2" t="n"/>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>491-1: AP Computer Science Principles - 1</t>
+          <t>496-1: AP Cybersecurity - 1</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>491-1: AP Computer Science Principles - 1</t>
+          <t>496-1: AP Cybersecurity - 1</t>
         </is>
       </c>
       <c r="F77" s="2" t="n"/>
@@ -2669,14 +2669,14 @@
         </is>
       </c>
       <c r="C79" s="2" t="n"/>
-      <c r="D79" s="6" t="inlineStr">
-        <is>
-          <t>494-1-F: Applied Programming - 1; 473-1-F: Introduction to Programming - 1</t>
+      <c r="D79" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>473-2-S: Introduction to Programming - 2</t>
+          <t>472-2-S: Web Design - 2</t>
         </is>
       </c>
       <c r="F79" s="2" t="n"/>
@@ -2703,14 +2703,14 @@
         </is>
       </c>
       <c r="C80" s="2" t="n"/>
-      <c r="D80" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E80" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>494-1-F: Applied Programming - 1; 473-1-F: Introduction to Programming - 1</t>
+        </is>
+      </c>
+      <c r="E80" s="6" t="inlineStr">
+        <is>
+          <t>473-2-S: Introduction to Programming - 2</t>
         </is>
       </c>
       <c r="F80" s="2" t="n"/>
@@ -2737,14 +2737,14 @@
         </is>
       </c>
       <c r="C81" s="2" t="n"/>
-      <c r="D81" s="6" t="inlineStr">
-        <is>
-          <t>496-1: AP Cybersecurity - 1</t>
-        </is>
-      </c>
-      <c r="E81" s="6" t="inlineStr">
-        <is>
-          <t>496-1: AP Cybersecurity - 1</t>
+      <c r="D81" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E81" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F81" s="2" t="n"/>
@@ -3528,12 +3528,12 @@
       <c r="C111" s="2" t="n"/>
       <c r="D111" s="6" t="inlineStr">
         <is>
-          <t>642-3-F: Nutrition &amp; Fitness/PE - 3</t>
+          <t>631-3-F: CPR-AED Training/PE - 3</t>
         </is>
       </c>
       <c r="E111" s="6" t="inlineStr">
         <is>
-          <t>631-2-S: CPR-AED Training/PE - 2</t>
+          <t>642-2-S: Nutrition &amp; Fitness/PE - 2</t>
         </is>
       </c>
       <c r="F111" s="2" t="n"/>
@@ -3562,12 +3562,12 @@
       <c r="C112" s="2" t="n"/>
       <c r="D112" s="6" t="inlineStr">
         <is>
-          <t>631-1-F: CPR-AED Training/PE - 1</t>
-        </is>
-      </c>
-      <c r="E112" s="6" t="inlineStr">
-        <is>
-          <t>642-2-S: Nutrition &amp; Fitness/PE - 2</t>
+          <t>642-3-F: Nutrition &amp; Fitness/PE - 3</t>
+        </is>
+      </c>
+      <c r="E112" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F112" s="2" t="n"/>
@@ -3698,7 +3698,7 @@
       <c r="C116" s="2" t="n"/>
       <c r="D116" s="6" t="inlineStr">
         <is>
-          <t>631-3-F: CPR-AED Training/PE - 3</t>
+          <t>631-1-F: CPR-AED Training/PE - 1</t>
         </is>
       </c>
       <c r="E116" s="6" t="inlineStr">
@@ -3735,9 +3735,9 @@
           <t>642-1-F: Nutrition &amp; Fitness/PE - 1</t>
         </is>
       </c>
-      <c r="E117" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="E117" s="6" t="inlineStr">
+        <is>
+          <t>631-2-S: CPR-AED Training/PE - 2</t>
         </is>
       </c>
       <c r="F117" s="2" t="n"/>
@@ -3783,8 +3783,8 @@
       <c r="D119" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E119" s="9" t="n">
-        <v>4</v>
+      <c r="E119" s="7" t="n">
+        <v>2</v>
       </c>
       <c r="F119" s="2" t="n"/>
       <c r="G119" s="7" t="n">
@@ -4029,12 +4029,12 @@
       <c r="C128" s="2" t="n"/>
       <c r="D128" s="6" t="inlineStr">
         <is>
-          <t>546-1: Forensics - 1</t>
+          <t>546-2: Forensics - 2</t>
         </is>
       </c>
       <c r="E128" s="6" t="inlineStr">
         <is>
-          <t>546-1: Forensics - 1</t>
+          <t>546-2: Forensics - 2</t>
         </is>
       </c>
       <c r="F128" s="2" t="n"/>
@@ -4063,12 +4063,12 @@
       <c r="C129" s="2" t="n"/>
       <c r="D129" s="6" t="inlineStr">
         <is>
-          <t>546-2: Forensics - 2</t>
+          <t>546-1: Forensics - 1</t>
         </is>
       </c>
       <c r="E129" s="6" t="inlineStr">
         <is>
-          <t>546-2: Forensics - 2</t>
+          <t>546-1: Forensics - 1</t>
         </is>
       </c>
       <c r="F129" s="2" t="n"/>
@@ -4188,14 +4188,14 @@
         </is>
       </c>
       <c r="C135" s="2" t="n"/>
-      <c r="D135" s="6" t="inlineStr">
-        <is>
-          <t>727-3-F: Sports and Entertainment Marketing - 3</t>
-        </is>
-      </c>
-      <c r="E135" s="6" t="inlineStr">
-        <is>
-          <t>758-2-S: Bloomberg Market Concepts - 2</t>
+      <c r="D135" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E135" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F135" s="2" t="n"/>
@@ -4324,9 +4324,9 @@
         </is>
       </c>
       <c r="C139" s="2" t="n"/>
-      <c r="D139" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D139" s="6" t="inlineStr">
+        <is>
+          <t>727-3-F: Sports and Entertainment Marketing - 3</t>
         </is>
       </c>
       <c r="E139" s="6" t="inlineStr">
@@ -4360,12 +4360,12 @@
       <c r="C140" s="2" t="n"/>
       <c r="D140" s="6" t="inlineStr">
         <is>
-          <t>732-1-F: Business Law - 1; 757-3: International Business Strategies - 3</t>
+          <t>757-3: International Business Strategies - 3</t>
         </is>
       </c>
       <c r="E140" s="6" t="inlineStr">
         <is>
-          <t>757-3: International Business Strategies - 3</t>
+          <t>758-2-S: Bloomberg Market Concepts - 2; 757-3: International Business Strategies - 3</t>
         </is>
       </c>
       <c r="F140" s="2" t="n"/>
@@ -4392,9 +4392,9 @@
         </is>
       </c>
       <c r="C141" s="2" t="n"/>
-      <c r="D141" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D141" s="6" t="inlineStr">
+        <is>
+          <t>732-1-F: Business Law - 1</t>
         </is>
       </c>
       <c r="E141" s="6" t="inlineStr">
@@ -4443,7 +4443,7 @@
       </c>
       <c r="C143" s="2" t="n"/>
       <c r="D143" s="9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E143" s="7" t="n">
         <v>3</v>
@@ -4553,14 +4553,14 @@
         </is>
       </c>
       <c r="C148" s="2" t="n"/>
-      <c r="D148" s="6" t="inlineStr">
-        <is>
-          <t>620-3-F: Driver's Ed/PE - 3</t>
-        </is>
-      </c>
-      <c r="E148" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D148" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E148" s="6" t="inlineStr">
+        <is>
+          <t>620-4-S: Driver's Ed/PE - 4</t>
         </is>
       </c>
       <c r="F148" s="2" t="n"/>
@@ -4689,14 +4689,14 @@
         </is>
       </c>
       <c r="C152" s="2" t="n"/>
-      <c r="D152" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E152" s="6" t="inlineStr">
-        <is>
-          <t>620-4-S: Driver's Ed/PE - 4</t>
+      <c r="D152" s="6" t="inlineStr">
+        <is>
+          <t>620-3-F: Driver's Ed/PE - 3</t>
+        </is>
+      </c>
+      <c r="E152" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F152" s="2" t="n"/>
@@ -4774,10 +4774,10 @@
       </c>
       <c r="C155" s="2" t="n"/>
       <c r="D155" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E155" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F155" s="2" t="n"/>
       <c r="G155" s="9" t="n">
@@ -4954,12 +4954,12 @@
       <c r="C162" s="2" t="n"/>
       <c r="D162" s="6" t="inlineStr">
         <is>
-          <t>440-2: Precalculus - 2</t>
+          <t>440-3: Precalculus - 3</t>
         </is>
       </c>
       <c r="E162" s="6" t="inlineStr">
         <is>
-          <t>440-2: Precalculus - 2</t>
+          <t>440-3: Precalculus - 3</t>
         </is>
       </c>
       <c r="F162" s="2" t="n"/>
@@ -4988,12 +4988,12 @@
       <c r="C163" s="2" t="n"/>
       <c r="D163" s="6" t="inlineStr">
         <is>
-          <t>440-3: Precalculus - 3</t>
+          <t>440-2: Precalculus - 2</t>
         </is>
       </c>
       <c r="E163" s="6" t="inlineStr">
         <is>
-          <t>440-3: Precalculus - 3</t>
+          <t>440-2: Precalculus - 2</t>
         </is>
       </c>
       <c r="F163" s="2" t="n"/>
@@ -5285,12 +5285,12 @@
       <c r="C174" s="2" t="n"/>
       <c r="D174" s="6" t="inlineStr">
         <is>
-          <t>111-2: Composition &amp; Literature H - 2</t>
+          <t>111-1: Composition &amp; Literature H - 1</t>
         </is>
       </c>
       <c r="E174" s="6" t="inlineStr">
         <is>
-          <t>111-2: Composition &amp; Literature H - 2</t>
+          <t>111-1: Composition &amp; Literature H - 1</t>
         </is>
       </c>
       <c r="F174" s="2" t="n"/>
@@ -5353,12 +5353,12 @@
       <c r="C176" s="2" t="n"/>
       <c r="D176" s="6" t="inlineStr">
         <is>
-          <t>111-1: Composition &amp; Literature H - 1</t>
+          <t>111-2: Composition &amp; Literature H - 2</t>
         </is>
       </c>
       <c r="E176" s="6" t="inlineStr">
         <is>
-          <t>111-1: Composition &amp; Literature H - 1</t>
+          <t>111-2: Composition &amp; Literature H - 2</t>
         </is>
       </c>
       <c r="F176" s="2" t="n"/>
@@ -5546,9 +5546,9 @@
         </is>
       </c>
       <c r="C184" s="2" t="n"/>
-      <c r="D184" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D184" s="6" t="inlineStr">
+        <is>
+          <t>241-1-F: Studio Art I - 1</t>
         </is>
       </c>
       <c r="E184" s="6" t="inlineStr">
@@ -5614,14 +5614,14 @@
         </is>
       </c>
       <c r="C186" s="2" t="n"/>
-      <c r="D186" s="6" t="inlineStr">
-        <is>
-          <t>242-1-F: Studio Art II - 1; 243-1-F: Studio Art III - 1</t>
-        </is>
-      </c>
-      <c r="E186" s="6" t="inlineStr">
-        <is>
-          <t>242-2-S: Studio Art II - 2; 243-2-S: Studio Art III - 2</t>
+      <c r="D186" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E186" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F186" s="2" t="n"/>
@@ -5650,12 +5650,12 @@
       <c r="C187" s="2" t="n"/>
       <c r="D187" s="6" t="inlineStr">
         <is>
-          <t>241-1-F: Studio Art I - 1</t>
+          <t>242-1-F: Studio Art II - 1; 243-1-F: Studio Art III - 1</t>
         </is>
       </c>
       <c r="E187" s="6" t="inlineStr">
         <is>
-          <t>249-2-S: Adv Painting - 2</t>
+          <t>242-2-S: Studio Art II - 2; 243-2-S: Studio Art III - 2</t>
         </is>
       </c>
       <c r="F187" s="2" t="n"/>
@@ -5721,9 +5721,9 @@
           <t>UNASSIGNED</t>
         </is>
       </c>
-      <c r="E189" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="E189" s="6" t="inlineStr">
+        <is>
+          <t>249-2-S: Adv Painting - 2</t>
         </is>
       </c>
       <c r="F189" s="2" t="n"/>
@@ -5845,12 +5845,12 @@
       <c r="C195" s="2" t="n"/>
       <c r="D195" s="6" t="inlineStr">
         <is>
-          <t>520-5: Chemistry - 5</t>
+          <t>520-4: Chemistry - 4</t>
         </is>
       </c>
       <c r="E195" s="6" t="inlineStr">
         <is>
-          <t>520-5: Chemistry - 5</t>
+          <t>520-4: Chemistry - 4</t>
         </is>
       </c>
       <c r="F195" s="2" t="n"/>
@@ -5879,12 +5879,12 @@
       <c r="C196" s="2" t="n"/>
       <c r="D196" s="6" t="inlineStr">
         <is>
-          <t>520-4: Chemistry - 4</t>
+          <t>520-5: Chemistry - 5</t>
         </is>
       </c>
       <c r="E196" s="6" t="inlineStr">
         <is>
-          <t>520-4: Chemistry - 4</t>
+          <t>520-5: Chemistry - 5</t>
         </is>
       </c>
       <c r="F196" s="2" t="n"/>
@@ -5913,12 +5913,12 @@
       <c r="C197" s="2" t="n"/>
       <c r="D197" s="6" t="inlineStr">
         <is>
-          <t>520-3: Chemistry - 3</t>
+          <t>520-2: Chemistry - 2</t>
         </is>
       </c>
       <c r="E197" s="6" t="inlineStr">
         <is>
-          <t>520-3: Chemistry - 3</t>
+          <t>520-2: Chemistry - 2</t>
         </is>
       </c>
       <c r="F197" s="2" t="n"/>
@@ -6015,12 +6015,12 @@
       <c r="C200" s="2" t="n"/>
       <c r="D200" s="6" t="inlineStr">
         <is>
-          <t>520-2: Chemistry - 2</t>
+          <t>520-3: Chemistry - 3</t>
         </is>
       </c>
       <c r="E200" s="6" t="inlineStr">
         <is>
-          <t>520-2: Chemistry - 2</t>
+          <t>520-3: Chemistry - 3</t>
         </is>
       </c>
       <c r="F200" s="2" t="n"/>
@@ -6208,14 +6208,14 @@
         </is>
       </c>
       <c r="C208" s="2" t="n"/>
-      <c r="D208" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E208" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D208" s="6" t="inlineStr">
+        <is>
+          <t>130-2: British Literature - 2</t>
+        </is>
+      </c>
+      <c r="E208" s="6" t="inlineStr">
+        <is>
+          <t>130-2: British Literature - 2</t>
         </is>
       </c>
       <c r="F208" s="2" t="n"/>
@@ -6378,14 +6378,14 @@
         </is>
       </c>
       <c r="C213" s="2" t="n"/>
-      <c r="D213" s="6" t="inlineStr">
-        <is>
-          <t>130-2: British Literature - 2</t>
-        </is>
-      </c>
-      <c r="E213" s="6" t="inlineStr">
-        <is>
-          <t>130-2: British Literature - 2</t>
+      <c r="D213" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E213" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F213" s="2" t="n"/>
@@ -6507,12 +6507,12 @@
       <c r="C219" s="2" t="n"/>
       <c r="D219" s="6" t="inlineStr">
         <is>
-          <t>726-1-F: Business Concepts - 1</t>
-        </is>
-      </c>
-      <c r="E219" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+          <t>729-2: AP Business with Personal Finance - 2</t>
+        </is>
+      </c>
+      <c r="E219" s="6" t="inlineStr">
+        <is>
+          <t>729-2: AP Business with Personal Finance - 2</t>
         </is>
       </c>
       <c r="F219" s="2" t="n"/>
@@ -6609,7 +6609,7 @@
       <c r="C222" s="2" t="n"/>
       <c r="D222" s="6" t="inlineStr">
         <is>
-          <t>726-3-F: Business Concepts - 3</t>
+          <t>726-1-F: Business Concepts - 1</t>
         </is>
       </c>
       <c r="E222" s="6" t="inlineStr">
@@ -6675,9 +6675,9 @@
         </is>
       </c>
       <c r="C224" s="2" t="n"/>
-      <c r="D224" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D224" s="6" t="inlineStr">
+        <is>
+          <t>726-3-F: Business Concepts - 3</t>
         </is>
       </c>
       <c r="E224" s="7" t="inlineStr">
@@ -6709,14 +6709,14 @@
         </is>
       </c>
       <c r="C225" s="2" t="n"/>
-      <c r="D225" s="6" t="inlineStr">
-        <is>
-          <t>729-2: AP Business with Personal Finance - 2</t>
-        </is>
-      </c>
-      <c r="E225" s="6" t="inlineStr">
-        <is>
-          <t>729-2: AP Business with Personal Finance - 2</t>
+      <c r="D225" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E225" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F225" s="2" t="n"/>
@@ -6760,10 +6760,10 @@
       </c>
       <c r="C227" s="2" t="n"/>
       <c r="D227" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="E227" s="9" t="n">
         <v>5</v>
-      </c>
-      <c r="E227" s="9" t="n">
-        <v>4</v>
       </c>
       <c r="F227" s="2" t="n"/>
       <c r="G227" s="9" t="n">
@@ -6938,9 +6938,9 @@
         </is>
       </c>
       <c r="C234" s="2" t="n"/>
-      <c r="D234" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D234" s="6" t="inlineStr">
+        <is>
+          <t>228-1-F: Adv Theater Production - 1; 227-1-F: Intermediate Theater - 1</t>
         </is>
       </c>
       <c r="E234" s="6" t="inlineStr">
@@ -7040,9 +7040,9 @@
         </is>
       </c>
       <c r="C237" s="2" t="n"/>
-      <c r="D237" s="6" t="inlineStr">
-        <is>
-          <t>228-1-F: Adv Theater Production - 1; 227-1-F: Intermediate Theater - 1</t>
+      <c r="D237" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="E237" s="7" t="inlineStr">
@@ -7091,7 +7091,7 @@
       </c>
       <c r="C239" s="2" t="n"/>
       <c r="D239" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E239" s="7" t="n">
         <v>1</v>
@@ -8822,14 +8822,14 @@
         </is>
       </c>
       <c r="C303" s="2" t="n"/>
-      <c r="D303" s="6" t="inlineStr">
-        <is>
-          <t>120-5: American Literature - 5</t>
-        </is>
-      </c>
-      <c r="E303" s="6" t="inlineStr">
-        <is>
-          <t>120-5: American Literature - 5</t>
+      <c r="D303" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E303" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F303" s="2" t="n"/>
@@ -8856,14 +8856,14 @@
         </is>
       </c>
       <c r="C304" s="2" t="n"/>
-      <c r="D304" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E304" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D304" s="6" t="inlineStr">
+        <is>
+          <t>120-5: American Literature - 5</t>
+        </is>
+      </c>
+      <c r="E304" s="6" t="inlineStr">
+        <is>
+          <t>120-5: American Literature - 5</t>
         </is>
       </c>
       <c r="F304" s="2" t="n"/>
@@ -8892,12 +8892,12 @@
       <c r="C305" s="2" t="n"/>
       <c r="D305" s="6" t="inlineStr">
         <is>
-          <t>120-2: American Literature - 2</t>
+          <t>120-3: American Literature - 3</t>
         </is>
       </c>
       <c r="E305" s="6" t="inlineStr">
         <is>
-          <t>120-2: American Literature - 2</t>
+          <t>120-3: American Literature - 3</t>
         </is>
       </c>
       <c r="F305" s="2" t="n"/>
@@ -8960,12 +8960,12 @@
       <c r="C307" s="2" t="n"/>
       <c r="D307" s="6" t="inlineStr">
         <is>
-          <t>120-3: American Literature - 3</t>
+          <t>120-1: American Literature - 1</t>
         </is>
       </c>
       <c r="E307" s="6" t="inlineStr">
         <is>
-          <t>120-3: American Literature - 3</t>
+          <t>120-1: American Literature - 1</t>
         </is>
       </c>
       <c r="F307" s="2" t="n"/>
@@ -8994,12 +8994,12 @@
       <c r="C308" s="2" t="n"/>
       <c r="D308" s="6" t="inlineStr">
         <is>
-          <t>120-1: American Literature - 1</t>
+          <t>120-2: American Literature - 2</t>
         </is>
       </c>
       <c r="E308" s="6" t="inlineStr">
         <is>
-          <t>120-1: American Literature - 1</t>
+          <t>120-2: American Literature - 2</t>
         </is>
       </c>
       <c r="F308" s="2" t="n"/>
@@ -9077,10 +9077,10 @@
       </c>
       <c r="C311" s="2" t="n"/>
       <c r="D311" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E311" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F311" s="2" t="n"/>
       <c r="G311" s="7" t="n">
@@ -9554,12 +9554,12 @@
       <c r="C329" s="2" t="n"/>
       <c r="D329" s="6" t="inlineStr">
         <is>
-          <t>810-2: Theology 9 - 2</t>
+          <t>820-2: Theology 10 - 2</t>
         </is>
       </c>
       <c r="E329" s="6" t="inlineStr">
         <is>
-          <t>810-2: Theology 9 - 2</t>
+          <t>820-2: Theology 10 - 2</t>
         </is>
       </c>
       <c r="F329" s="2" t="n"/>
@@ -9588,12 +9588,12 @@
       <c r="C330" s="2" t="n"/>
       <c r="D330" s="6" t="inlineStr">
         <is>
-          <t>820-1: Theology 10 - 1</t>
+          <t>810-1: Theology 9 - 1</t>
         </is>
       </c>
       <c r="E330" s="6" t="inlineStr">
         <is>
-          <t>820-1: Theology 10 - 1</t>
+          <t>810-1: Theology 9 - 1</t>
         </is>
       </c>
       <c r="F330" s="2" t="n"/>
@@ -9622,12 +9622,12 @@
       <c r="C331" s="2" t="n"/>
       <c r="D331" s="6" t="inlineStr">
         <is>
-          <t>820-2: Theology 10 - 2</t>
+          <t>810-3: Theology 9 - 3</t>
         </is>
       </c>
       <c r="E331" s="6" t="inlineStr">
         <is>
-          <t>820-2: Theology 10 - 2</t>
+          <t>810-3: Theology 9 - 3</t>
         </is>
       </c>
       <c r="F331" s="2" t="n"/>
@@ -9656,12 +9656,12 @@
       <c r="C332" s="2" t="n"/>
       <c r="D332" s="6" t="inlineStr">
         <is>
-          <t>810-3: Theology 9 - 3</t>
+          <t>820-1: Theology 10 - 1</t>
         </is>
       </c>
       <c r="E332" s="6" t="inlineStr">
         <is>
-          <t>810-3: Theology 9 - 3</t>
+          <t>820-1: Theology 10 - 1</t>
         </is>
       </c>
       <c r="F332" s="2" t="n"/>
@@ -9690,12 +9690,12 @@
       <c r="C333" s="2" t="n"/>
       <c r="D333" s="6" t="inlineStr">
         <is>
-          <t>810-1: Theology 9 - 1</t>
+          <t>810-2: Theology 9 - 2</t>
         </is>
       </c>
       <c r="E333" s="6" t="inlineStr">
         <is>
-          <t>810-1: Theology 9 - 1</t>
+          <t>810-2: Theology 9 - 2</t>
         </is>
       </c>
       <c r="F333" s="2" t="n"/>
@@ -11209,12 +11209,12 @@
       <c r="C389" s="2" t="n"/>
       <c r="D389" s="6" t="inlineStr">
         <is>
-          <t>420-1: Geometry - 1</t>
+          <t>412-1: Algebra I - 1</t>
         </is>
       </c>
       <c r="E389" s="6" t="inlineStr">
         <is>
-          <t>420-1: Geometry - 1</t>
+          <t>412-1: Algebra I - 1</t>
         </is>
       </c>
       <c r="F389" s="2" t="n"/>
@@ -11243,12 +11243,12 @@
       <c r="C390" s="2" t="n"/>
       <c r="D390" s="6" t="inlineStr">
         <is>
-          <t>412-1: Algebra I - 1</t>
+          <t>420-1: Geometry - 1</t>
         </is>
       </c>
       <c r="E390" s="6" t="inlineStr">
         <is>
-          <t>412-1: Algebra I - 1</t>
+          <t>420-1: Geometry - 1</t>
         </is>
       </c>
       <c r="F390" s="2" t="n"/>
@@ -12499,12 +12499,12 @@
       <c r="C436" s="2" t="n"/>
       <c r="D436" s="6" t="inlineStr">
         <is>
-          <t>810-4: Theology 9 - 4</t>
+          <t>810-7: Theology 9 - 7</t>
         </is>
       </c>
       <c r="E436" s="6" t="inlineStr">
         <is>
-          <t>810-4: Theology 9 - 4</t>
+          <t>810-7: Theology 9 - 7</t>
         </is>
       </c>
       <c r="F436" s="2" t="n"/>
@@ -12531,14 +12531,14 @@
         </is>
       </c>
       <c r="C437" s="2" t="n"/>
-      <c r="D437" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E437" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D437" s="6" t="inlineStr">
+        <is>
+          <t>810-4: Theology 9 - 4</t>
+        </is>
+      </c>
+      <c r="E437" s="6" t="inlineStr">
+        <is>
+          <t>810-4: Theology 9 - 4</t>
         </is>
       </c>
       <c r="F437" s="2" t="n"/>
@@ -12567,12 +12567,12 @@
       <c r="C438" s="2" t="n"/>
       <c r="D438" s="6" t="inlineStr">
         <is>
-          <t>810-6: Theology 9 - 6</t>
+          <t>810-8: Theology 9 - 8</t>
         </is>
       </c>
       <c r="E438" s="6" t="inlineStr">
         <is>
-          <t>810-6: Theology 9 - 6</t>
+          <t>810-8: Theology 9 - 8</t>
         </is>
       </c>
       <c r="F438" s="2" t="n"/>
@@ -12599,14 +12599,14 @@
         </is>
       </c>
       <c r="C439" s="2" t="n"/>
-      <c r="D439" s="6" t="inlineStr">
-        <is>
-          <t>810-7: Theology 9 - 7</t>
-        </is>
-      </c>
-      <c r="E439" s="6" t="inlineStr">
-        <is>
-          <t>810-7: Theology 9 - 7</t>
+      <c r="D439" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E439" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F439" s="2" t="n"/>
@@ -12633,14 +12633,14 @@
         </is>
       </c>
       <c r="C440" s="2" t="n"/>
-      <c r="D440" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E440" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D440" s="6" t="inlineStr">
+        <is>
+          <t>810-6: Theology 9 - 6</t>
+        </is>
+      </c>
+      <c r="E440" s="6" t="inlineStr">
+        <is>
+          <t>810-6: Theology 9 - 6</t>
         </is>
       </c>
       <c r="F440" s="2" t="n"/>
@@ -12667,14 +12667,14 @@
         </is>
       </c>
       <c r="C441" s="2" t="n"/>
-      <c r="D441" s="6" t="inlineStr">
-        <is>
-          <t>810-8: Theology 9 - 8</t>
-        </is>
-      </c>
-      <c r="E441" s="6" t="inlineStr">
-        <is>
-          <t>810-8: Theology 9 - 8</t>
+      <c r="D441" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E441" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F441" s="2" t="n"/>
@@ -12717,11 +12717,11 @@
         </is>
       </c>
       <c r="C443" s="2" t="n"/>
-      <c r="D443" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E443" s="7" t="n">
-        <v>2</v>
+      <c r="D443" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E443" s="9" t="n">
+        <v>4</v>
       </c>
       <c r="F443" s="2" t="n"/>
       <c r="G443" s="7" t="n">
@@ -13456,9 +13456,9 @@
         </is>
       </c>
       <c r="C471" s="2" t="n"/>
-      <c r="D471" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D471" s="6" t="inlineStr">
+        <is>
+          <t>766-2-F: AP Microeconomics - 2</t>
         </is>
       </c>
       <c r="E471" s="6" t="inlineStr">
@@ -13490,9 +13490,9 @@
         </is>
       </c>
       <c r="C472" s="2" t="n"/>
-      <c r="D472" s="6" t="inlineStr">
-        <is>
-          <t>766-2-F: AP Microeconomics - 2</t>
+      <c r="D472" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="E472" s="7" t="inlineStr">
@@ -13792,9 +13792,9 @@
           <t>UNASSIGNED</t>
         </is>
       </c>
-      <c r="E483" s="6" t="inlineStr">
-        <is>
-          <t>595-2-S: Engineering Design - 2</t>
+      <c r="E483" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F483" s="2" t="n"/>
@@ -13857,12 +13857,12 @@
       <c r="C485" s="2" t="n"/>
       <c r="D485" s="6" t="inlineStr">
         <is>
-          <t>530-3: Physics - 3</t>
+          <t>530-2: Physics - 2</t>
         </is>
       </c>
       <c r="E485" s="6" t="inlineStr">
         <is>
-          <t>530-3: Physics - 3</t>
+          <t>530-2: Physics - 2</t>
         </is>
       </c>
       <c r="F485" s="2" t="n"/>
@@ -13891,12 +13891,12 @@
       <c r="C486" s="2" t="n"/>
       <c r="D486" s="6" t="inlineStr">
         <is>
-          <t>530-2: Physics - 2</t>
+          <t>530-3: Physics - 3</t>
         </is>
       </c>
       <c r="E486" s="6" t="inlineStr">
         <is>
-          <t>530-2: Physics - 2</t>
+          <t>530-3: Physics - 3</t>
         </is>
       </c>
       <c r="F486" s="2" t="n"/>
@@ -13996,9 +13996,9 @@
           <t>595-1-F: Engineering Design - 1</t>
         </is>
       </c>
-      <c r="E489" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="E489" s="6" t="inlineStr">
+        <is>
+          <t>595-2-S: Engineering Design - 2</t>
         </is>
       </c>
       <c r="F489" s="2" t="n"/>
@@ -14045,7 +14045,7 @@
         <v>4</v>
       </c>
       <c r="E491" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F491" s="2" t="n"/>
       <c r="G491" s="9" t="n">
@@ -14186,14 +14186,14 @@
         </is>
       </c>
       <c r="C497" s="2" t="n"/>
-      <c r="D497" s="6" t="inlineStr">
-        <is>
-          <t>820-3: Theology 10 - 3</t>
-        </is>
-      </c>
-      <c r="E497" s="6" t="inlineStr">
-        <is>
-          <t>820-3: Theology 10 - 3</t>
+      <c r="D497" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E497" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F497" s="2" t="n"/>
@@ -14220,14 +14220,14 @@
         </is>
       </c>
       <c r="C498" s="2" t="n"/>
-      <c r="D498" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E498" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D498" s="6" t="inlineStr">
+        <is>
+          <t>820-5: Theology 10 - 5</t>
+        </is>
+      </c>
+      <c r="E498" s="6" t="inlineStr">
+        <is>
+          <t>820-5: Theology 10 - 5</t>
         </is>
       </c>
       <c r="F498" s="2" t="n"/>
@@ -14254,14 +14254,14 @@
         </is>
       </c>
       <c r="C499" s="2" t="n"/>
-      <c r="D499" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E499" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D499" s="6" t="inlineStr">
+        <is>
+          <t>820-3: Theology 10 - 3</t>
+        </is>
+      </c>
+      <c r="E499" s="6" t="inlineStr">
+        <is>
+          <t>820-3: Theology 10 - 3</t>
         </is>
       </c>
       <c r="F499" s="2" t="n"/>
@@ -14322,14 +14322,14 @@
         </is>
       </c>
       <c r="C501" s="2" t="n"/>
-      <c r="D501" s="6" t="inlineStr">
-        <is>
-          <t>820-5: Theology 10 - 5</t>
-        </is>
-      </c>
-      <c r="E501" s="6" t="inlineStr">
-        <is>
-          <t>820-5: Theology 10 - 5</t>
+      <c r="D501" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E501" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F501" s="2" t="n"/>
@@ -14519,12 +14519,12 @@
       <c r="C509" s="2" t="n"/>
       <c r="D509" s="6" t="inlineStr">
         <is>
-          <t>851-3-F: Spirituality of Vocation - 3</t>
-        </is>
-      </c>
-      <c r="E509" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+          <t>851-1-F: Spirituality of Vocation - 1</t>
+        </is>
+      </c>
+      <c r="E509" s="6" t="inlineStr">
+        <is>
+          <t>851-8-S: Spirituality of Vocation - 8</t>
         </is>
       </c>
       <c r="F509" s="2" t="n"/>
@@ -14551,14 +14551,14 @@
         </is>
       </c>
       <c r="C510" s="2" t="n"/>
-      <c r="D510" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E510" s="6" t="inlineStr">
-        <is>
-          <t>851-6-S: Spirituality of Vocation - 6</t>
+      <c r="D510" s="6" t="inlineStr">
+        <is>
+          <t>851-3-F: Spirituality of Vocation - 3</t>
+        </is>
+      </c>
+      <c r="E510" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F510" s="2" t="n"/>
@@ -14585,14 +14585,14 @@
         </is>
       </c>
       <c r="C511" s="2" t="n"/>
-      <c r="D511" s="6" t="inlineStr">
-        <is>
-          <t>851-1-F: Spirituality of Vocation - 1</t>
+      <c r="D511" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="E511" s="6" t="inlineStr">
         <is>
-          <t>851-8-S: Spirituality of Vocation - 8</t>
+          <t>851-5-S: Spirituality of Vocation - 5</t>
         </is>
       </c>
       <c r="F511" s="2" t="n"/>
@@ -14621,12 +14621,12 @@
       <c r="C512" s="2" t="n"/>
       <c r="D512" s="6" t="inlineStr">
         <is>
+          <t>830-4: Theology 11 - 4; 851-2-F: Spirituality of Vocation - 2</t>
+        </is>
+      </c>
+      <c r="E512" s="6" t="inlineStr">
+        <is>
           <t>830-4: Theology 11 - 4</t>
-        </is>
-      </c>
-      <c r="E512" s="6" t="inlineStr">
-        <is>
-          <t>830-4: Theology 11 - 4; 851-5-S: Spirituality of Vocation - 5</t>
         </is>
       </c>
       <c r="F512" s="2" t="n"/>
@@ -14653,14 +14653,14 @@
         </is>
       </c>
       <c r="C513" s="2" t="n"/>
-      <c r="D513" s="6" t="inlineStr">
-        <is>
-          <t>851-2-F: Spirituality of Vocation - 2</t>
-        </is>
-      </c>
-      <c r="E513" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D513" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E513" s="6" t="inlineStr">
+        <is>
+          <t>851-6-S: Spirituality of Vocation - 6</t>
         </is>
       </c>
       <c r="F513" s="2" t="n"/>
@@ -14704,7 +14704,7 @@
       </c>
       <c r="C515" s="2" t="n"/>
       <c r="D515" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E515" s="7" t="n">
         <v>3</v>
@@ -14782,12 +14782,12 @@
       <c r="C519" s="2" t="n"/>
       <c r="D519" s="6" t="inlineStr">
         <is>
-          <t>820-9: Theology 10 - 9</t>
+          <t>820-7: Theology 10 - 7</t>
         </is>
       </c>
       <c r="E519" s="6" t="inlineStr">
         <is>
-          <t>820-9: Theology 10 - 9</t>
+          <t>820-7: Theology 10 - 7</t>
         </is>
       </c>
       <c r="F519" s="2" t="n"/>
@@ -14882,14 +14882,14 @@
         </is>
       </c>
       <c r="C522" s="2" t="n"/>
-      <c r="D522" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E522" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D522" s="6" t="inlineStr">
+        <is>
+          <t>820-9: Theology 10 - 9</t>
+        </is>
+      </c>
+      <c r="E522" s="6" t="inlineStr">
+        <is>
+          <t>820-9: Theology 10 - 9</t>
         </is>
       </c>
       <c r="F522" s="2" t="n"/>
@@ -14950,14 +14950,14 @@
         </is>
       </c>
       <c r="C524" s="2" t="n"/>
-      <c r="D524" s="6" t="inlineStr">
-        <is>
-          <t>820-7: Theology 10 - 7</t>
-        </is>
-      </c>
-      <c r="E524" s="6" t="inlineStr">
-        <is>
-          <t>820-7: Theology 10 - 7</t>
+      <c r="D524" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E524" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F524" s="2" t="n"/>
@@ -15034,11 +15034,11 @@
         </is>
       </c>
       <c r="C527" s="2" t="n"/>
-      <c r="D527" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="E527" s="7" t="n">
-        <v>3</v>
+      <c r="D527" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E527" s="9" t="n">
+        <v>4</v>
       </c>
       <c r="F527" s="2" t="n"/>
       <c r="G527" s="7" t="n">
@@ -15283,12 +15283,12 @@
       <c r="C536" s="2" t="n"/>
       <c r="D536" s="6" t="inlineStr">
         <is>
-          <t>203-1: Guitar Ensemble - 1; 203-2: Guitar Ensemble - 2; 201-1-F: Introduction to Guitar - 1; 201-3-F: Introduction to Guitar - 3</t>
+          <t>209-1: String Orchestra - 1</t>
         </is>
       </c>
       <c r="E536" s="6" t="inlineStr">
         <is>
-          <t>203-1: Guitar Ensemble - 1; 203-2: Guitar Ensemble - 2; 201-2-S: Introduction to Guitar - 2</t>
+          <t>209-1: String Orchestra - 1</t>
         </is>
       </c>
       <c r="F536" s="2" t="n"/>
@@ -15317,12 +15317,12 @@
       <c r="C537" s="2" t="n"/>
       <c r="D537" s="6" t="inlineStr">
         <is>
-          <t>209-1: String Orchestra - 1</t>
+          <t>203-1: Guitar Ensemble - 1; 203-2: Guitar Ensemble - 2; 201-1-F: Introduction to Guitar - 1; 201-3-F: Introduction to Guitar - 3</t>
         </is>
       </c>
       <c r="E537" s="6" t="inlineStr">
         <is>
-          <t>209-1: String Orchestra - 1</t>
+          <t>203-1: Guitar Ensemble - 1; 203-2: Guitar Ensemble - 2; 201-2-S: Introduction to Guitar - 2</t>
         </is>
       </c>
       <c r="F537" s="2" t="n"/>
@@ -15442,14 +15442,14 @@
         </is>
       </c>
       <c r="C543" s="2" t="n"/>
-      <c r="D543" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E543" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D543" s="6" t="inlineStr">
+        <is>
+          <t>763-2: AP U.S. Government &amp; Politics - 2</t>
+        </is>
+      </c>
+      <c r="E543" s="6" t="inlineStr">
+        <is>
+          <t>763-2: AP U.S. Government &amp; Politics - 2</t>
         </is>
       </c>
       <c r="F543" s="2" t="n"/>
@@ -15646,14 +15646,14 @@
         </is>
       </c>
       <c r="C549" s="2" t="n"/>
-      <c r="D549" s="6" t="inlineStr">
-        <is>
-          <t>763-2: AP U.S. Government &amp; Politics - 2</t>
-        </is>
-      </c>
-      <c r="E549" s="6" t="inlineStr">
-        <is>
-          <t>763-2: AP U.S. Government &amp; Politics - 2</t>
+      <c r="D549" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E549" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F549" s="2" t="n"/>
@@ -15945,12 +15945,12 @@
       <c r="C560" s="2" t="n"/>
       <c r="D560" s="6" t="inlineStr">
         <is>
-          <t>955-6: Academic Support - 6</t>
+          <t>955-7: Academic Support - 7</t>
         </is>
       </c>
       <c r="E560" s="6" t="inlineStr">
         <is>
-          <t>955-6: Academic Support - 6</t>
+          <t>955-7: Academic Support - 7</t>
         </is>
       </c>
       <c r="F560" s="2" t="n"/>
@@ -15979,12 +15979,12 @@
       <c r="C561" s="2" t="n"/>
       <c r="D561" s="6" t="inlineStr">
         <is>
-          <t>955-7: Academic Support - 7</t>
+          <t>955-6: Academic Support - 6</t>
         </is>
       </c>
       <c r="E561" s="6" t="inlineStr">
         <is>
-          <t>955-7: Academic Support - 7</t>
+          <t>955-6: Academic Support - 6</t>
         </is>
       </c>
       <c r="F561" s="2" t="n"/>
@@ -16174,12 +16174,12 @@
       <c r="C569" s="2" t="n"/>
       <c r="D569" s="6" t="inlineStr">
         <is>
-          <t>580-3-F: Robotics Engineering - 3</t>
-        </is>
-      </c>
-      <c r="E569" s="6" t="inlineStr">
-        <is>
-          <t>570-2-S: Introduction to Robotics - 2</t>
+          <t>580-1-F: Robotics Engineering - 1</t>
+        </is>
+      </c>
+      <c r="E569" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F569" s="2" t="n"/>
@@ -16208,12 +16208,12 @@
       <c r="C570" s="2" t="n"/>
       <c r="D570" s="6" t="inlineStr">
         <is>
-          <t>580-1-F: Robotics Engineering - 1</t>
-        </is>
-      </c>
-      <c r="E570" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+          <t>580-3-F: Robotics Engineering - 3</t>
+        </is>
+      </c>
+      <c r="E570" s="6" t="inlineStr">
+        <is>
+          <t>570-2-S: Introduction to Robotics - 2</t>
         </is>
       </c>
       <c r="F570" s="2" t="n"/>
@@ -16361,8 +16361,8 @@
       <c r="D575" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="E575" s="7" t="n">
-        <v>3</v>
+      <c r="E575" s="9" t="n">
+        <v>4</v>
       </c>
       <c r="F575" s="2" t="n"/>
       <c r="G575" s="7" t="n">
@@ -16435,14 +16435,14 @@
         </is>
       </c>
       <c r="C579" s="2" t="n"/>
-      <c r="D579" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E579" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D579" s="6" t="inlineStr">
+        <is>
+          <t>521-4: Chemistry H - 4</t>
+        </is>
+      </c>
+      <c r="E579" s="6" t="inlineStr">
+        <is>
+          <t>521-4: Chemistry H - 4</t>
         </is>
       </c>
       <c r="F579" s="2" t="n"/>
@@ -16537,14 +16537,14 @@
         </is>
       </c>
       <c r="C582" s="2" t="n"/>
-      <c r="D582" s="6" t="inlineStr">
-        <is>
-          <t>521-4: Chemistry H - 4</t>
-        </is>
-      </c>
-      <c r="E582" s="6" t="inlineStr">
-        <is>
-          <t>521-4: Chemistry H - 4</t>
+      <c r="D582" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E582" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F582" s="2" t="n"/>
@@ -16573,12 +16573,12 @@
       <c r="C583" s="2" t="n"/>
       <c r="D583" s="6" t="inlineStr">
         <is>
-          <t>521-3: Chemistry H - 3</t>
+          <t>521-1: Chemistry H - 1</t>
         </is>
       </c>
       <c r="E583" s="6" t="inlineStr">
         <is>
-          <t>521-3: Chemistry H - 3</t>
+          <t>521-1: Chemistry H - 1</t>
         </is>
       </c>
       <c r="F583" s="2" t="n"/>
@@ -16641,12 +16641,12 @@
       <c r="C585" s="2" t="n"/>
       <c r="D585" s="6" t="inlineStr">
         <is>
-          <t>521-1: Chemistry H - 1</t>
+          <t>521-3: Chemistry H - 3</t>
         </is>
       </c>
       <c r="E585" s="6" t="inlineStr">
         <is>
-          <t>521-1: Chemistry H - 1</t>
+          <t>521-3: Chemistry H - 3</t>
         </is>
       </c>
       <c r="F585" s="2" t="n"/>
@@ -16689,11 +16689,11 @@
         </is>
       </c>
       <c r="C587" s="2" t="n"/>
-      <c r="D587" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="E587" s="9" t="n">
-        <v>5</v>
+      <c r="D587" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E587" s="7" t="n">
+        <v>3</v>
       </c>
       <c r="F587" s="2" t="n"/>
       <c r="G587" s="9" t="n">
@@ -16836,12 +16836,12 @@
       <c r="C593" s="2" t="n"/>
       <c r="D593" s="6" t="inlineStr">
         <is>
-          <t>720-2: U.S. History I - 2</t>
+          <t>720-1: U.S. History I - 1</t>
         </is>
       </c>
       <c r="E593" s="6" t="inlineStr">
         <is>
-          <t>720-2: U.S. History I - 2</t>
+          <t>720-1: U.S. History I - 1</t>
         </is>
       </c>
       <c r="F593" s="2" t="n"/>
@@ -16870,12 +16870,12 @@
       <c r="C594" s="2" t="n"/>
       <c r="D594" s="6" t="inlineStr">
         <is>
-          <t>720-1: U.S. History I - 1</t>
+          <t>720-2: U.S. History I - 2</t>
         </is>
       </c>
       <c r="E594" s="6" t="inlineStr">
         <is>
-          <t>720-1: U.S. History I - 1</t>
+          <t>720-2: U.S. History I - 2</t>
         </is>
       </c>
       <c r="F594" s="2" t="n"/>
@@ -17863,12 +17863,12 @@
       <c r="C630" s="2" t="n"/>
       <c r="D630" s="6" t="inlineStr">
         <is>
-          <t>352-1: AP Italian - 1</t>
+          <t>332-1: Italian III - 1</t>
         </is>
       </c>
       <c r="E630" s="6" t="inlineStr">
         <is>
-          <t>352-1: AP Italian - 1</t>
+          <t>332-1: Italian III - 1</t>
         </is>
       </c>
       <c r="F630" s="2" t="n"/>
@@ -17897,12 +17897,12 @@
       <c r="C631" s="2" t="n"/>
       <c r="D631" s="6" t="inlineStr">
         <is>
-          <t>332-1: Italian III - 1</t>
+          <t>352-1: AP Italian - 1</t>
         </is>
       </c>
       <c r="E631" s="6" t="inlineStr">
         <is>
-          <t>332-1: Italian III - 1</t>
+          <t>352-1: AP Italian - 1</t>
         </is>
       </c>
       <c r="F631" s="2" t="n"/>
@@ -18754,12 +18754,12 @@
       <c r="C663" s="2" t="n"/>
       <c r="D663" s="6" t="inlineStr">
         <is>
-          <t>149-2: AP English Literature - 2</t>
+          <t>149-1: AP English Literature - 1</t>
         </is>
       </c>
       <c r="E663" s="6" t="inlineStr">
         <is>
-          <t>149-2: AP English Literature - 2</t>
+          <t>149-1: AP English Literature - 1</t>
         </is>
       </c>
       <c r="F663" s="2" t="n"/>
@@ -18820,14 +18820,14 @@
         </is>
       </c>
       <c r="C665" s="2" t="n"/>
-      <c r="D665" s="6" t="inlineStr">
-        <is>
-          <t>110-1: Composition &amp; Literature - 1</t>
-        </is>
-      </c>
-      <c r="E665" s="6" t="inlineStr">
-        <is>
-          <t>110-1: Composition &amp; Literature - 1</t>
+      <c r="D665" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E665" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F665" s="2" t="n"/>
@@ -18888,14 +18888,14 @@
         </is>
       </c>
       <c r="C667" s="2" t="n"/>
-      <c r="D667" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E667" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D667" s="6" t="inlineStr">
+        <is>
+          <t>110-1: Composition &amp; Literature - 1</t>
+        </is>
+      </c>
+      <c r="E667" s="6" t="inlineStr">
+        <is>
+          <t>110-1: Composition &amp; Literature - 1</t>
         </is>
       </c>
       <c r="F667" s="2" t="n"/>
@@ -18958,12 +18958,12 @@
       <c r="C669" s="2" t="n"/>
       <c r="D669" s="6" t="inlineStr">
         <is>
-          <t>149-1: AP English Literature - 1</t>
+          <t>149-2: AP English Literature - 2</t>
         </is>
       </c>
       <c r="E669" s="6" t="inlineStr">
         <is>
-          <t>149-1: AP English Literature - 1</t>
+          <t>149-2: AP English Literature - 2</t>
         </is>
       </c>
       <c r="F669" s="2" t="n"/>
@@ -19006,11 +19006,11 @@
         </is>
       </c>
       <c r="C671" s="2" t="n"/>
-      <c r="D671" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E671" s="7" t="n">
-        <v>2</v>
+      <c r="D671" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E671" s="9" t="n">
+        <v>4</v>
       </c>
       <c r="F671" s="2" t="n"/>
       <c r="G671" s="9" t="n">
@@ -19119,12 +19119,12 @@
       <c r="C676" s="2" t="n"/>
       <c r="D676" s="6" t="inlineStr">
         <is>
-          <t>410-2: Algebra I - 2</t>
+          <t>410-1: Algebra I - 1</t>
         </is>
       </c>
       <c r="E676" s="6" t="inlineStr">
         <is>
-          <t>410-2: Algebra I - 2</t>
+          <t>410-1: Algebra I - 1</t>
         </is>
       </c>
       <c r="F676" s="2" t="n"/>
@@ -19153,12 +19153,12 @@
       <c r="C677" s="2" t="n"/>
       <c r="D677" s="6" t="inlineStr">
         <is>
-          <t>410-1: Algebra I - 1</t>
+          <t>420-3: Geometry - 3</t>
         </is>
       </c>
       <c r="E677" s="6" t="inlineStr">
         <is>
-          <t>410-1: Algebra I - 1</t>
+          <t>420-3: Geometry - 3</t>
         </is>
       </c>
       <c r="F677" s="2" t="n"/>
@@ -19187,12 +19187,12 @@
       <c r="C678" s="2" t="n"/>
       <c r="D678" s="6" t="inlineStr">
         <is>
-          <t>420-3: Geometry - 3</t>
+          <t>410-3: Algebra I - 3</t>
         </is>
       </c>
       <c r="E678" s="6" t="inlineStr">
         <is>
-          <t>420-3: Geometry - 3</t>
+          <t>410-3: Algebra I - 3</t>
         </is>
       </c>
       <c r="F678" s="2" t="n"/>
@@ -19219,14 +19219,14 @@
         </is>
       </c>
       <c r="C679" s="2" t="n"/>
-      <c r="D679" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E679" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D679" s="6" t="inlineStr">
+        <is>
+          <t>410-2: Algebra I - 2</t>
+        </is>
+      </c>
+      <c r="E679" s="6" t="inlineStr">
+        <is>
+          <t>410-2: Algebra I - 2</t>
         </is>
       </c>
       <c r="F679" s="2" t="n"/>
@@ -19287,14 +19287,14 @@
         </is>
       </c>
       <c r="C681" s="2" t="n"/>
-      <c r="D681" s="6" t="inlineStr">
-        <is>
-          <t>410-3: Algebra I - 3</t>
-        </is>
-      </c>
-      <c r="E681" s="6" t="inlineStr">
-        <is>
-          <t>410-3: Algebra I - 3</t>
+      <c r="D681" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E681" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F681" s="2" t="n"/>
@@ -19338,10 +19338,10 @@
       </c>
       <c r="C683" s="2" t="n"/>
       <c r="D683" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E683" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F683" s="2" t="n"/>
       <c r="G683" s="7" t="n">
@@ -20081,9 +20081,9 @@
           <t>2024-1-F: TV/Film Process and Principles - 1</t>
         </is>
       </c>
-      <c r="E711" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="E711" s="6" t="inlineStr">
+        <is>
+          <t>2044-2-S: TV/Film Production II - 2</t>
         </is>
       </c>
       <c r="F711" s="2" t="n"/>
@@ -20178,14 +20178,14 @@
         </is>
       </c>
       <c r="C714" s="2" t="n"/>
-      <c r="D714" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E714" s="6" t="inlineStr">
-        <is>
-          <t>2054-2-S: Digital Media - 2</t>
+      <c r="D714" s="6" t="inlineStr">
+        <is>
+          <t>2054-1-F: Digital Media - 1</t>
+        </is>
+      </c>
+      <c r="E714" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F714" s="2" t="n"/>
@@ -20253,7 +20253,7 @@
       </c>
       <c r="E716" s="6" t="inlineStr">
         <is>
-          <t>2044-2-S: TV/Film Production II - 2</t>
+          <t>2054-2-S: Digital Media - 2</t>
         </is>
       </c>
       <c r="F716" s="2" t="n"/>
@@ -20280,9 +20280,9 @@
         </is>
       </c>
       <c r="C717" s="2" t="n"/>
-      <c r="D717" s="6" t="inlineStr">
-        <is>
-          <t>2054-1-F: Digital Media - 1</t>
+      <c r="D717" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="E717" s="6" t="inlineStr">
@@ -20330,11 +20330,11 @@
         </is>
       </c>
       <c r="C719" s="2" t="n"/>
-      <c r="D719" s="7" t="n">
+      <c r="D719" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E719" s="7" t="n">
         <v>3</v>
-      </c>
-      <c r="E719" s="9" t="n">
-        <v>4</v>
       </c>
       <c r="F719" s="2" t="n"/>
       <c r="G719" s="7" t="n">
@@ -20409,12 +20409,12 @@
       <c r="C723" s="2" t="n"/>
       <c r="D723" s="6" t="inlineStr">
         <is>
-          <t>713-2: AP World History - 2</t>
+          <t>711-2: World History H - 2</t>
         </is>
       </c>
       <c r="E723" s="6" t="inlineStr">
         <is>
-          <t>713-2: AP World History - 2</t>
+          <t>711-2: World History H - 2</t>
         </is>
       </c>
       <c r="F723" s="2" t="n"/>
@@ -20443,12 +20443,12 @@
       <c r="C724" s="2" t="n"/>
       <c r="D724" s="6" t="inlineStr">
         <is>
-          <t>711-2: World History H - 2</t>
+          <t>711-1: World History H - 1</t>
         </is>
       </c>
       <c r="E724" s="6" t="inlineStr">
         <is>
-          <t>711-2: World History H - 2</t>
+          <t>711-1: World History H - 1</t>
         </is>
       </c>
       <c r="F724" s="2" t="n"/>
@@ -20475,14 +20475,14 @@
         </is>
       </c>
       <c r="C725" s="2" t="n"/>
-      <c r="D725" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D725" s="6" t="inlineStr">
+        <is>
+          <t>713-2: AP World History - 2</t>
         </is>
       </c>
       <c r="E725" s="6" t="inlineStr">
         <is>
-          <t>744-2-S: Sociology - 2</t>
+          <t>713-2: AP World History - 2</t>
         </is>
       </c>
       <c r="F725" s="2" t="n"/>
@@ -20511,12 +20511,12 @@
       <c r="C726" s="2" t="n"/>
       <c r="D726" s="6" t="inlineStr">
         <is>
-          <t>711-1: World History H - 1</t>
+          <t>744-1-F: Sociology - 1</t>
         </is>
       </c>
       <c r="E726" s="6" t="inlineStr">
         <is>
-          <t>711-1: World History H - 1</t>
+          <t>744-2-S: Sociology - 2</t>
         </is>
       </c>
       <c r="F726" s="2" t="n"/>
@@ -20611,9 +20611,9 @@
         </is>
       </c>
       <c r="C729" s="2" t="n"/>
-      <c r="D729" s="6" t="inlineStr">
-        <is>
-          <t>744-1-F: Sociology - 1</t>
+      <c r="D729" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="E729" s="7" t="inlineStr">
@@ -20662,7 +20662,7 @@
       </c>
       <c r="C731" s="2" t="n"/>
       <c r="D731" s="9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E731" s="9" t="n">
         <v>6</v>
@@ -21405,9 +21405,9 @@
           <t>751-1-F: American Government &amp; Politics - 1</t>
         </is>
       </c>
-      <c r="E759" s="6" t="inlineStr">
-        <is>
-          <t>741-2-S: Psychology - 2</t>
+      <c r="E759" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F759" s="2" t="n"/>
@@ -21468,14 +21468,14 @@
         </is>
       </c>
       <c r="C761" s="2" t="n"/>
-      <c r="D761" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E761" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D761" s="6" t="inlineStr">
+        <is>
+          <t>710-3: World History - 3</t>
+        </is>
+      </c>
+      <c r="E761" s="6" t="inlineStr">
+        <is>
+          <t>710-3: World History - 3</t>
         </is>
       </c>
       <c r="F761" s="2" t="n"/>
@@ -21504,12 +21504,12 @@
       <c r="C762" s="2" t="n"/>
       <c r="D762" s="6" t="inlineStr">
         <is>
-          <t>710-2: World History - 2</t>
-        </is>
-      </c>
-      <c r="E762" s="6" t="inlineStr">
-        <is>
-          <t>710-2: World History - 2</t>
+          <t>741-3-F: Psychology - 3</t>
+        </is>
+      </c>
+      <c r="E762" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F762" s="2" t="n"/>
@@ -21536,14 +21536,14 @@
         </is>
       </c>
       <c r="C763" s="2" t="n"/>
-      <c r="D763" s="6" t="inlineStr">
-        <is>
-          <t>741-3-F: Psychology - 3</t>
-        </is>
-      </c>
-      <c r="E763" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D763" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E763" s="6" t="inlineStr">
+        <is>
+          <t>741-2-S: Psychology - 2</t>
         </is>
       </c>
       <c r="F763" s="2" t="n"/>
@@ -21572,12 +21572,12 @@
       <c r="C764" s="2" t="n"/>
       <c r="D764" s="6" t="inlineStr">
         <is>
-          <t>710-3: World History - 3</t>
+          <t>710-2: World History - 2</t>
         </is>
       </c>
       <c r="E764" s="6" t="inlineStr">
         <is>
-          <t>710-3: World History - 3</t>
+          <t>710-2: World History - 2</t>
         </is>
       </c>
       <c r="F764" s="2" t="n"/>
@@ -21658,7 +21658,7 @@
         <v>4</v>
       </c>
       <c r="E767" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F767" s="2" t="n"/>
       <c r="G767" s="7" t="n">
@@ -21733,12 +21733,12 @@
       <c r="C771" s="2" t="n"/>
       <c r="D771" s="6" t="inlineStr">
         <is>
-          <t>110-5: Composition &amp; Literature - 5</t>
+          <t>110-4: Composition &amp; Literature - 4</t>
         </is>
       </c>
       <c r="E771" s="6" t="inlineStr">
         <is>
-          <t>110-5: Composition &amp; Literature - 5</t>
+          <t>110-4: Composition &amp; Literature - 4</t>
         </is>
       </c>
       <c r="F771" s="2" t="n"/>
@@ -21767,12 +21767,12 @@
       <c r="C772" s="2" t="n"/>
       <c r="D772" s="6" t="inlineStr">
         <is>
-          <t>110-4: Composition &amp; Literature - 4</t>
+          <t>110-5: Composition &amp; Literature - 5</t>
         </is>
       </c>
       <c r="E772" s="6" t="inlineStr">
         <is>
-          <t>110-4: Composition &amp; Literature - 4</t>
+          <t>110-5: Composition &amp; Literature - 5</t>
         </is>
       </c>
       <c r="F772" s="2" t="n"/>
@@ -21799,14 +21799,14 @@
         </is>
       </c>
       <c r="C773" s="2" t="n"/>
-      <c r="D773" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E773" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D773" s="6" t="inlineStr">
+        <is>
+          <t>110-2: Composition &amp; Literature - 2</t>
+        </is>
+      </c>
+      <c r="E773" s="6" t="inlineStr">
+        <is>
+          <t>110-2: Composition &amp; Literature - 2</t>
         </is>
       </c>
       <c r="F773" s="2" t="n"/>
@@ -21867,14 +21867,14 @@
         </is>
       </c>
       <c r="C775" s="2" t="n"/>
-      <c r="D775" s="6" t="inlineStr">
-        <is>
-          <t>110-2: Composition &amp; Literature - 2</t>
-        </is>
-      </c>
-      <c r="E775" s="6" t="inlineStr">
-        <is>
-          <t>110-2: Composition &amp; Literature - 2</t>
+      <c r="D775" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E775" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F775" s="2" t="n"/>
@@ -21985,11 +21985,11 @@
         </is>
       </c>
       <c r="C779" s="2" t="n"/>
-      <c r="D779" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="E779" s="7" t="n">
-        <v>3</v>
+      <c r="D779" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E779" s="9" t="n">
+        <v>4</v>
       </c>
       <c r="F779" s="2" t="n"/>
       <c r="G779" s="9" t="n">
@@ -22461,14 +22461,14 @@
         </is>
       </c>
       <c r="C797" s="2" t="n"/>
-      <c r="D797" s="6" t="inlineStr">
-        <is>
-          <t>556-2: AP Physics - 2</t>
-        </is>
-      </c>
-      <c r="E797" s="6" t="inlineStr">
-        <is>
-          <t>556-2: AP Physics - 2</t>
+      <c r="D797" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E797" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F797" s="2" t="n"/>
@@ -22565,12 +22565,12 @@
       <c r="C800" s="2" t="n"/>
       <c r="D800" s="6" t="inlineStr">
         <is>
-          <t>556-1: AP Physics - 1</t>
+          <t>556-2: AP Physics - 2</t>
         </is>
       </c>
       <c r="E800" s="6" t="inlineStr">
         <is>
-          <t>556-1: AP Physics - 1</t>
+          <t>556-2: AP Physics - 2</t>
         </is>
       </c>
       <c r="F800" s="2" t="n"/>
@@ -22597,14 +22597,14 @@
         </is>
       </c>
       <c r="C801" s="2" t="n"/>
-      <c r="D801" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E801" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D801" s="6" t="inlineStr">
+        <is>
+          <t>556-1: AP Physics - 1</t>
+        </is>
+      </c>
+      <c r="E801" s="6" t="inlineStr">
+        <is>
+          <t>556-1: AP Physics - 1</t>
         </is>
       </c>
       <c r="F801" s="2" t="n"/>
@@ -22726,12 +22726,12 @@
       <c r="C807" s="2" t="n"/>
       <c r="D807" s="6" t="inlineStr">
         <is>
-          <t>310-5: Spanish I - 5</t>
+          <t>310-3: Spanish I - 3</t>
         </is>
       </c>
       <c r="E807" s="6" t="inlineStr">
         <is>
-          <t>310-5: Spanish I - 5</t>
+          <t>310-3: Spanish I - 3</t>
         </is>
       </c>
       <c r="F807" s="2" t="n"/>
@@ -22760,12 +22760,12 @@
       <c r="C808" s="2" t="n"/>
       <c r="D808" s="6" t="inlineStr">
         <is>
-          <t>310-4: Spanish I - 4</t>
+          <t>310-5: Spanish I - 5</t>
         </is>
       </c>
       <c r="E808" s="6" t="inlineStr">
         <is>
-          <t>310-4: Spanish I - 4</t>
+          <t>310-5: Spanish I - 5</t>
         </is>
       </c>
       <c r="F808" s="2" t="n"/>
@@ -22828,12 +22828,12 @@
       <c r="C810" s="2" t="n"/>
       <c r="D810" s="6" t="inlineStr">
         <is>
-          <t>310-3: Spanish I - 3</t>
+          <t>310-4: Spanish I - 4</t>
         </is>
       </c>
       <c r="E810" s="6" t="inlineStr">
         <is>
-          <t>310-3: Spanish I - 3</t>
+          <t>310-4: Spanish I - 4</t>
         </is>
       </c>
       <c r="F810" s="2" t="n"/>
@@ -22928,14 +22928,14 @@
         </is>
       </c>
       <c r="C813" s="2" t="n"/>
-      <c r="D813" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E813" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D813" s="6" t="inlineStr">
+        <is>
+          <t>310-6: Spanish I - 6</t>
+        </is>
+      </c>
+      <c r="E813" s="6" t="inlineStr">
+        <is>
+          <t>310-6: Spanish I - 6</t>
         </is>
       </c>
       <c r="F813" s="2" t="n"/>
@@ -22958,10 +22958,10 @@
       </c>
       <c r="C814" s="2" t="n"/>
       <c r="D814" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E814" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F814" s="2" t="n"/>
       <c r="G814" s="9" t="n">
@@ -23157,14 +23157,14 @@
         </is>
       </c>
       <c r="C822" s="2" t="n"/>
-      <c r="D822" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E822" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D822" s="6" t="inlineStr">
+        <is>
+          <t>130-5: British Literature - 5</t>
+        </is>
+      </c>
+      <c r="E822" s="6" t="inlineStr">
+        <is>
+          <t>130-5: British Literature - 5</t>
         </is>
       </c>
       <c r="F822" s="2" t="n"/>
@@ -23193,12 +23193,12 @@
       <c r="C823" s="2" t="n"/>
       <c r="D823" s="6" t="inlineStr">
         <is>
-          <t>130-4: British Literature - 4</t>
+          <t>130-3: British Literature - 3</t>
         </is>
       </c>
       <c r="E823" s="6" t="inlineStr">
         <is>
-          <t>130-4: British Literature - 4</t>
+          <t>130-3: British Literature - 3</t>
         </is>
       </c>
       <c r="F823" s="2" t="n"/>
@@ -23225,14 +23225,14 @@
         </is>
       </c>
       <c r="C824" s="2" t="n"/>
-      <c r="D824" s="6" t="inlineStr">
-        <is>
-          <t>130-5: British Literature - 5</t>
-        </is>
-      </c>
-      <c r="E824" s="6" t="inlineStr">
-        <is>
-          <t>130-5: British Literature - 5</t>
+      <c r="D824" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E824" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F824" s="2" t="n"/>
@@ -23261,12 +23261,12 @@
       <c r="C825" s="2" t="n"/>
       <c r="D825" s="6" t="inlineStr">
         <is>
-          <t>130-3: British Literature - 3</t>
+          <t>130-4: British Literature - 4</t>
         </is>
       </c>
       <c r="E825" s="6" t="inlineStr">
         <is>
-          <t>130-3: British Literature - 3</t>
+          <t>130-4: British Literature - 4</t>
         </is>
       </c>
       <c r="F825" s="2" t="n"/>
@@ -23309,11 +23309,11 @@
         </is>
       </c>
       <c r="C827" s="2" t="n"/>
-      <c r="D827" s="7" t="n">
-        <v>3</v>
+      <c r="D827" s="9" t="n">
+        <v>5</v>
       </c>
       <c r="E827" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F827" s="2" t="n"/>
       <c r="G827" s="7" t="n">
@@ -23785,14 +23785,14 @@
         </is>
       </c>
       <c r="C845" s="2" t="n"/>
-      <c r="D845" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E845" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D845" s="6" t="inlineStr">
+        <is>
+          <t>410-5: Algebra I - 5</t>
+        </is>
+      </c>
+      <c r="E845" s="6" t="inlineStr">
+        <is>
+          <t>410-5: Algebra I - 5</t>
         </is>
       </c>
       <c r="F845" s="2" t="n"/>
@@ -23819,14 +23819,14 @@
         </is>
       </c>
       <c r="C846" s="2" t="n"/>
-      <c r="D846" s="6" t="inlineStr">
-        <is>
-          <t>410-6: Algebra I - 6</t>
-        </is>
-      </c>
-      <c r="E846" s="6" t="inlineStr">
-        <is>
-          <t>410-6: Algebra I - 6</t>
+      <c r="D846" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E846" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F846" s="2" t="n"/>
@@ -23853,14 +23853,14 @@
         </is>
       </c>
       <c r="C847" s="2" t="n"/>
-      <c r="D847" s="6" t="inlineStr">
-        <is>
-          <t>410-5: Algebra I - 5</t>
-        </is>
-      </c>
-      <c r="E847" s="6" t="inlineStr">
-        <is>
-          <t>410-5: Algebra I - 5</t>
+      <c r="D847" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E847" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F847" s="2" t="n"/>
@@ -23921,14 +23921,14 @@
         </is>
       </c>
       <c r="C849" s="2" t="n"/>
-      <c r="D849" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E849" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D849" s="6" t="inlineStr">
+        <is>
+          <t>410-6: Algebra I - 6</t>
+        </is>
+      </c>
+      <c r="E849" s="6" t="inlineStr">
+        <is>
+          <t>410-6: Algebra I - 6</t>
         </is>
       </c>
       <c r="F849" s="2" t="n"/>
@@ -24150,14 +24150,14 @@
         </is>
       </c>
       <c r="C858" s="2" t="n"/>
-      <c r="D858" s="6" t="inlineStr">
-        <is>
-          <t>731-3: U.S. History II H - 3</t>
-        </is>
-      </c>
-      <c r="E858" s="6" t="inlineStr">
-        <is>
-          <t>731-3: U.S. History II H - 3</t>
+      <c r="D858" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E858" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F858" s="2" t="n"/>
@@ -24218,14 +24218,14 @@
         </is>
       </c>
       <c r="C860" s="2" t="n"/>
-      <c r="D860" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E860" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D860" s="6" t="inlineStr">
+        <is>
+          <t>710-6: World History - 6</t>
+        </is>
+      </c>
+      <c r="E860" s="6" t="inlineStr">
+        <is>
+          <t>710-6: World History - 6</t>
         </is>
       </c>
       <c r="F860" s="2" t="n"/>
@@ -24254,12 +24254,12 @@
       <c r="C861" s="2" t="n"/>
       <c r="D861" s="6" t="inlineStr">
         <is>
-          <t>710-6: World History - 6</t>
+          <t>731-3: U.S. History II H - 3</t>
         </is>
       </c>
       <c r="E861" s="6" t="inlineStr">
         <is>
-          <t>710-6: World History - 6</t>
+          <t>731-3: U.S. History II H - 3</t>
         </is>
       </c>
       <c r="F861" s="2" t="n"/>
@@ -24302,11 +24302,11 @@
         </is>
       </c>
       <c r="C863" s="2" t="n"/>
-      <c r="D863" s="9" t="n">
-        <v>5</v>
+      <c r="D863" s="7" t="n">
+        <v>3</v>
       </c>
       <c r="E863" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F863" s="2" t="n"/>
       <c r="G863" s="9" t="n">
@@ -24483,12 +24483,12 @@
       <c r="C870" s="2" t="n"/>
       <c r="D870" s="6" t="inlineStr">
         <is>
-          <t>742-2: Economics - 2</t>
+          <t>742-1: Economics - 1</t>
         </is>
       </c>
       <c r="E870" s="6" t="inlineStr">
         <is>
-          <t>742-2: Economics - 2</t>
+          <t>742-1: Economics - 1</t>
         </is>
       </c>
       <c r="F870" s="2" t="n"/>
@@ -24517,12 +24517,12 @@
       <c r="C871" s="2" t="n"/>
       <c r="D871" s="6" t="inlineStr">
         <is>
-          <t>742-1: Economics - 1</t>
+          <t>742-2: Economics - 2</t>
         </is>
       </c>
       <c r="E871" s="6" t="inlineStr">
         <is>
-          <t>742-1: Economics - 1</t>
+          <t>742-2: Economics - 2</t>
         </is>
       </c>
       <c r="F871" s="2" t="n"/>
@@ -24710,14 +24710,14 @@
         </is>
       </c>
       <c r="C879" s="2" t="n"/>
-      <c r="D879" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E879" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D879" s="6" t="inlineStr">
+        <is>
+          <t>327-1: Latin II H - 1</t>
+        </is>
+      </c>
+      <c r="E879" s="6" t="inlineStr">
+        <is>
+          <t>327-1: Latin II H - 1</t>
         </is>
       </c>
       <c r="F879" s="2" t="n"/>
@@ -24914,14 +24914,14 @@
         </is>
       </c>
       <c r="C885" s="2" t="n"/>
-      <c r="D885" s="6" t="inlineStr">
-        <is>
-          <t>327-1: Latin II H - 1</t>
-        </is>
-      </c>
-      <c r="E885" s="6" t="inlineStr">
-        <is>
-          <t>327-1: Latin II H - 1</t>
+      <c r="D885" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E885" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F885" s="2" t="n"/>

--- a/Teacher_Schedule_Review_and_Tally.xlsx
+++ b/Teacher_Schedule_Review_and_Tally.xlsx
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H887"/>
+  <dimension ref="A1:H899"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -717,14 +717,14 @@
         </is>
       </c>
       <c r="C8" s="2" t="n"/>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>421-3: Geometry H - 3</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>421-3: Geometry H - 3</t>
         </is>
       </c>
       <c r="F8" s="2" t="n"/>
@@ -751,14 +751,14 @@
         </is>
       </c>
       <c r="C9" s="2" t="n"/>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>421-3: Geometry H - 3</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>421-3: Geometry H - 3</t>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F9" s="2" t="n"/>
@@ -1939,14 +1939,14 @@
         </is>
       </c>
       <c r="C53" s="2" t="n"/>
-      <c r="D53" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>610-3-F: Health/PE - 3</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>610-4-S: Health/PE - 4</t>
+          <t>610-10-S: Health/PE - 10</t>
         </is>
       </c>
       <c r="F53" s="2" t="n"/>
@@ -1973,14 +1973,14 @@
         </is>
       </c>
       <c r="C54" s="2" t="n"/>
-      <c r="D54" s="6" t="inlineStr">
-        <is>
-          <t>610-3-F: Health/PE - 3</t>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>610-10-S: Health/PE - 10</t>
+          <t>610-4-S: Health/PE - 4</t>
         </is>
       </c>
       <c r="F54" s="2" t="n"/>
@@ -2968,12 +2968,12 @@
       <c r="C90" s="2" t="n"/>
       <c r="D90" s="6" t="inlineStr">
         <is>
-          <t>431-1: Algebra II/Trig H - 1</t>
+          <t>431-2: Algebra II/Trig H - 2</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
         <is>
-          <t>431-1: Algebra II/Trig H - 1</t>
+          <t>431-2: Algebra II/Trig H - 2</t>
         </is>
       </c>
       <c r="F90" s="2" t="n"/>
@@ -3002,12 +3002,12 @@
       <c r="C91" s="2" t="n"/>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>431-2: Algebra II/Trig H - 2</t>
+          <t>431-1: Algebra II/Trig H - 1</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>431-2: Algebra II/Trig H - 2</t>
+          <t>431-1: Algebra II/Trig H - 1</t>
         </is>
       </c>
       <c r="F91" s="2" t="n"/>
@@ -3195,14 +3195,14 @@
         </is>
       </c>
       <c r="C99" s="2" t="n"/>
-      <c r="D99" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E99" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D99" s="6" t="inlineStr">
+        <is>
+          <t>321-1: Spanish II H - 1</t>
+        </is>
+      </c>
+      <c r="E99" s="6" t="inlineStr">
+        <is>
+          <t>321-1: Spanish II H - 1</t>
         </is>
       </c>
       <c r="F99" s="2" t="n"/>
@@ -3263,14 +3263,14 @@
         </is>
       </c>
       <c r="C101" s="2" t="n"/>
-      <c r="D101" s="6" t="inlineStr">
-        <is>
-          <t>321-1: Spanish II H - 1</t>
-        </is>
-      </c>
-      <c r="E101" s="6" t="inlineStr">
-        <is>
-          <t>321-1: Spanish II H - 1</t>
+      <c r="D101" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E101" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F101" s="2" t="n"/>
@@ -3449,11 +3449,11 @@
         </is>
       </c>
       <c r="C107" s="2" t="n"/>
-      <c r="D107" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="E107" s="9" t="n">
-        <v>5</v>
+      <c r="D107" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E107" s="7" t="n">
+        <v>3</v>
       </c>
       <c r="F107" s="2" t="n"/>
       <c r="G107" s="9" t="n">
@@ -3528,12 +3528,12 @@
       <c r="C111" s="2" t="n"/>
       <c r="D111" s="6" t="inlineStr">
         <is>
-          <t>631-3-F: CPR-AED Training/PE - 3</t>
+          <t>642-3-F: Nutrition &amp; Fitness/PE - 3</t>
         </is>
       </c>
       <c r="E111" s="6" t="inlineStr">
         <is>
-          <t>642-2-S: Nutrition &amp; Fitness/PE - 2</t>
+          <t>631-2-S: CPR-AED Training/PE - 2</t>
         </is>
       </c>
       <c r="F111" s="2" t="n"/>
@@ -3562,12 +3562,12 @@
       <c r="C112" s="2" t="n"/>
       <c r="D112" s="6" t="inlineStr">
         <is>
-          <t>642-3-F: Nutrition &amp; Fitness/PE - 3</t>
-        </is>
-      </c>
-      <c r="E112" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+          <t>631-1-F: CPR-AED Training/PE - 1</t>
+        </is>
+      </c>
+      <c r="E112" s="6" t="inlineStr">
+        <is>
+          <t>642-2-S: Nutrition &amp; Fitness/PE - 2</t>
         </is>
       </c>
       <c r="F112" s="2" t="n"/>
@@ -3633,9 +3633,9 @@
           <t>642-5-F: Nutrition &amp; Fitness/PE - 5</t>
         </is>
       </c>
-      <c r="E114" s="6" t="inlineStr">
-        <is>
-          <t>631-4-S: CPR-AED Training/PE - 4</t>
+      <c r="E114" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F114" s="2" t="n"/>
@@ -3698,7 +3698,7 @@
       <c r="C116" s="2" t="n"/>
       <c r="D116" s="6" t="inlineStr">
         <is>
-          <t>631-1-F: CPR-AED Training/PE - 1</t>
+          <t>631-3-F: CPR-AED Training/PE - 3</t>
         </is>
       </c>
       <c r="E116" s="6" t="inlineStr">
@@ -3737,7 +3737,7 @@
       </c>
       <c r="E117" s="6" t="inlineStr">
         <is>
-          <t>631-2-S: CPR-AED Training/PE - 2</t>
+          <t>631-4-S: CPR-AED Training/PE - 4</t>
         </is>
       </c>
       <c r="F117" s="2" t="n"/>
@@ -3784,7 +3784,7 @@
         <v>2</v>
       </c>
       <c r="E119" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F119" s="2" t="n"/>
       <c r="G119" s="7" t="n">
@@ -3961,12 +3961,12 @@
       <c r="C126" s="2" t="n"/>
       <c r="D126" s="6" t="inlineStr">
         <is>
-          <t>510-2: Biology - 2</t>
+          <t>544-1: Sports Medicine - 1</t>
         </is>
       </c>
       <c r="E126" s="6" t="inlineStr">
         <is>
-          <t>510-2: Biology - 2</t>
+          <t>544-1: Sports Medicine - 1</t>
         </is>
       </c>
       <c r="F126" s="2" t="n"/>
@@ -3995,12 +3995,12 @@
       <c r="C127" s="2" t="n"/>
       <c r="D127" s="6" t="inlineStr">
         <is>
-          <t>544-1: Sports Medicine - 1</t>
+          <t>510-2: Biology - 2</t>
         </is>
       </c>
       <c r="E127" s="6" t="inlineStr">
         <is>
-          <t>544-1: Sports Medicine - 1</t>
+          <t>510-2: Biology - 2</t>
         </is>
       </c>
       <c r="F127" s="2" t="n"/>
@@ -4029,12 +4029,12 @@
       <c r="C128" s="2" t="n"/>
       <c r="D128" s="6" t="inlineStr">
         <is>
-          <t>546-2: Forensics - 2</t>
+          <t>546-1: Forensics - 1</t>
         </is>
       </c>
       <c r="E128" s="6" t="inlineStr">
         <is>
-          <t>546-2: Forensics - 2</t>
+          <t>546-1: Forensics - 1</t>
         </is>
       </c>
       <c r="F128" s="2" t="n"/>
@@ -4063,12 +4063,12 @@
       <c r="C129" s="2" t="n"/>
       <c r="D129" s="6" t="inlineStr">
         <is>
-          <t>546-1: Forensics - 1</t>
+          <t>546-2: Forensics - 2</t>
         </is>
       </c>
       <c r="E129" s="6" t="inlineStr">
         <is>
-          <t>546-1: Forensics - 1</t>
+          <t>546-2: Forensics - 2</t>
         </is>
       </c>
       <c r="F129" s="2" t="n"/>
@@ -4193,9 +4193,9 @@
           <t>UNASSIGNED</t>
         </is>
       </c>
-      <c r="E135" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="E135" s="6" t="inlineStr">
+        <is>
+          <t>758-2-S: Bloomberg Market Concepts - 2</t>
         </is>
       </c>
       <c r="F135" s="2" t="n"/>
@@ -4224,12 +4224,12 @@
       <c r="C136" s="2" t="n"/>
       <c r="D136" s="6" t="inlineStr">
         <is>
-          <t>757-2: International Business Strategies - 2</t>
-        </is>
-      </c>
-      <c r="E136" s="6" t="inlineStr">
-        <is>
-          <t>757-2: International Business Strategies - 2</t>
+          <t>727-1-F: Sports and Entertainment Marketing - 1</t>
+        </is>
+      </c>
+      <c r="E136" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F136" s="2" t="n"/>
@@ -4258,12 +4258,12 @@
       <c r="C137" s="2" t="n"/>
       <c r="D137" s="6" t="inlineStr">
         <is>
-          <t>757-1: International Business Strategies - 1</t>
+          <t>757-2: International Business Strategies - 2</t>
         </is>
       </c>
       <c r="E137" s="6" t="inlineStr">
         <is>
-          <t>757-1: International Business Strategies - 1</t>
+          <t>757-2: International Business Strategies - 2</t>
         </is>
       </c>
       <c r="F137" s="2" t="n"/>
@@ -4292,12 +4292,12 @@
       <c r="C138" s="2" t="n"/>
       <c r="D138" s="6" t="inlineStr">
         <is>
-          <t>727-1-F: Sports and Entertainment Marketing - 1</t>
-        </is>
-      </c>
-      <c r="E138" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+          <t>757-3: International Business Strategies - 3</t>
+        </is>
+      </c>
+      <c r="E138" s="6" t="inlineStr">
+        <is>
+          <t>757-3: International Business Strategies - 3</t>
         </is>
       </c>
       <c r="F138" s="2" t="n"/>
@@ -4326,12 +4326,12 @@
       <c r="C139" s="2" t="n"/>
       <c r="D139" s="6" t="inlineStr">
         <is>
-          <t>727-3-F: Sports and Entertainment Marketing - 3</t>
+          <t>757-1: International Business Strategies - 1</t>
         </is>
       </c>
       <c r="E139" s="6" t="inlineStr">
         <is>
-          <t>727-2-S: Sports and Entertainment Marketing - 2</t>
+          <t>757-1: International Business Strategies - 1</t>
         </is>
       </c>
       <c r="F139" s="2" t="n"/>
@@ -4360,12 +4360,12 @@
       <c r="C140" s="2" t="n"/>
       <c r="D140" s="6" t="inlineStr">
         <is>
-          <t>757-3: International Business Strategies - 3</t>
+          <t>732-1-F: Business Law - 1</t>
         </is>
       </c>
       <c r="E140" s="6" t="inlineStr">
         <is>
-          <t>758-2-S: Bloomberg Market Concepts - 2; 757-3: International Business Strategies - 3</t>
+          <t>727-2-S: Sports and Entertainment Marketing - 2</t>
         </is>
       </c>
       <c r="F140" s="2" t="n"/>
@@ -4394,7 +4394,7 @@
       <c r="C141" s="2" t="n"/>
       <c r="D141" s="6" t="inlineStr">
         <is>
-          <t>732-1-F: Business Law - 1</t>
+          <t>727-3-F: Sports and Entertainment Marketing - 3</t>
         </is>
       </c>
       <c r="E141" s="6" t="inlineStr">
@@ -4445,8 +4445,8 @@
       <c r="D143" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="E143" s="7" t="n">
-        <v>3</v>
+      <c r="E143" s="9" t="n">
+        <v>5</v>
       </c>
       <c r="F143" s="2" t="n"/>
       <c r="G143" s="9" t="n">
@@ -4519,14 +4519,14 @@
         </is>
       </c>
       <c r="C147" s="2" t="n"/>
-      <c r="D147" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E147" s="6" t="inlineStr">
-        <is>
-          <t>620-2-S: Driver's Ed/PE - 2</t>
+      <c r="D147" s="6" t="inlineStr">
+        <is>
+          <t>620-3-F: Driver's Ed/PE - 3</t>
+        </is>
+      </c>
+      <c r="E147" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F147" s="2" t="n"/>
@@ -4560,7 +4560,7 @@
       </c>
       <c r="E148" s="6" t="inlineStr">
         <is>
-          <t>620-4-S: Driver's Ed/PE - 4</t>
+          <t>620-2-S: Driver's Ed/PE - 2</t>
         </is>
       </c>
       <c r="F148" s="2" t="n"/>
@@ -4689,14 +4689,14 @@
         </is>
       </c>
       <c r="C152" s="2" t="n"/>
-      <c r="D152" s="6" t="inlineStr">
-        <is>
-          <t>620-3-F: Driver's Ed/PE - 3</t>
-        </is>
-      </c>
-      <c r="E152" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D152" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E152" s="6" t="inlineStr">
+        <is>
+          <t>620-4-S: Driver's Ed/PE - 4</t>
         </is>
       </c>
       <c r="F152" s="2" t="n"/>
@@ -4773,11 +4773,11 @@
         </is>
       </c>
       <c r="C155" s="2" t="n"/>
-      <c r="D155" s="9" t="n">
-        <v>5</v>
+      <c r="D155" s="7" t="n">
+        <v>3</v>
       </c>
       <c r="E155" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F155" s="2" t="n"/>
       <c r="G155" s="9" t="n">
@@ -5249,14 +5249,14 @@
         </is>
       </c>
       <c r="C173" s="2" t="n"/>
-      <c r="D173" s="6" t="inlineStr">
-        <is>
-          <t>111-3: Composition &amp; Literature H - 3</t>
-        </is>
-      </c>
-      <c r="E173" s="6" t="inlineStr">
-        <is>
-          <t>111-3: Composition &amp; Literature H - 3</t>
+      <c r="D173" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E173" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F173" s="2" t="n"/>
@@ -5285,12 +5285,12 @@
       <c r="C174" s="2" t="n"/>
       <c r="D174" s="6" t="inlineStr">
         <is>
-          <t>111-1: Composition &amp; Literature H - 1</t>
+          <t>111-2: Composition &amp; Literature H - 2</t>
         </is>
       </c>
       <c r="E174" s="6" t="inlineStr">
         <is>
-          <t>111-1: Composition &amp; Literature H - 1</t>
+          <t>111-2: Composition &amp; Literature H - 2</t>
         </is>
       </c>
       <c r="F174" s="2" t="n"/>
@@ -5317,14 +5317,14 @@
         </is>
       </c>
       <c r="C175" s="2" t="n"/>
-      <c r="D175" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E175" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D175" s="6" t="inlineStr">
+        <is>
+          <t>129-2: AP Seminar - 2</t>
+        </is>
+      </c>
+      <c r="E175" s="6" t="inlineStr">
+        <is>
+          <t>129-2: AP Seminar - 2</t>
         </is>
       </c>
       <c r="F175" s="2" t="n"/>
@@ -5353,12 +5353,12 @@
       <c r="C176" s="2" t="n"/>
       <c r="D176" s="6" t="inlineStr">
         <is>
-          <t>111-2: Composition &amp; Literature H - 2</t>
+          <t>111-3: Composition &amp; Literature H - 3</t>
         </is>
       </c>
       <c r="E176" s="6" t="inlineStr">
         <is>
-          <t>111-2: Composition &amp; Literature H - 2</t>
+          <t>111-3: Composition &amp; Literature H - 3</t>
         </is>
       </c>
       <c r="F176" s="2" t="n"/>
@@ -5387,12 +5387,12 @@
       <c r="C177" s="2" t="n"/>
       <c r="D177" s="6" t="inlineStr">
         <is>
-          <t>129-2: AP Seminar - 2</t>
+          <t>111-1: Composition &amp; Literature H - 1</t>
         </is>
       </c>
       <c r="E177" s="6" t="inlineStr">
         <is>
-          <t>129-2: AP Seminar - 2</t>
+          <t>111-1: Composition &amp; Literature H - 1</t>
         </is>
       </c>
       <c r="F177" s="2" t="n"/>
@@ -5435,11 +5435,11 @@
         </is>
       </c>
       <c r="C179" s="2" t="n"/>
-      <c r="D179" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="E179" s="7" t="n">
-        <v>3</v>
+      <c r="D179" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E179" s="9" t="n">
+        <v>4</v>
       </c>
       <c r="F179" s="2" t="n"/>
       <c r="G179" s="7" t="n">
@@ -5548,7 +5548,7 @@
       <c r="C184" s="2" t="n"/>
       <c r="D184" s="6" t="inlineStr">
         <is>
-          <t>241-1-F: Studio Art I - 1</t>
+          <t>249-1-F: Adv Painting - 1</t>
         </is>
       </c>
       <c r="E184" s="6" t="inlineStr">
@@ -5582,12 +5582,12 @@
       <c r="C185" s="2" t="n"/>
       <c r="D185" s="6" t="inlineStr">
         <is>
-          <t>249-1-F: Adv Painting - 1</t>
-        </is>
-      </c>
-      <c r="E185" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+          <t>241-1-F: Studio Art I - 1</t>
+        </is>
+      </c>
+      <c r="E185" s="6" t="inlineStr">
+        <is>
+          <t>249-2-S: Adv Painting - 2</t>
         </is>
       </c>
       <c r="F185" s="2" t="n"/>
@@ -5614,9 +5614,9 @@
         </is>
       </c>
       <c r="C186" s="2" t="n"/>
-      <c r="D186" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D186" s="6" t="inlineStr">
+        <is>
+          <t>248-1-F: Adv Drawing - 1</t>
         </is>
       </c>
       <c r="E186" s="7" t="inlineStr">
@@ -5721,9 +5721,9 @@
           <t>UNASSIGNED</t>
         </is>
       </c>
-      <c r="E189" s="6" t="inlineStr">
-        <is>
-          <t>249-2-S: Adv Painting - 2</t>
+      <c r="E189" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F189" s="2" t="n"/>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="C190" s="2" t="n"/>
       <c r="D190" s="9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E190" s="9" t="n">
         <v>8</v>
@@ -5766,11 +5766,11 @@
         </is>
       </c>
       <c r="C191" s="2" t="n"/>
-      <c r="D191" s="7" t="n">
+      <c r="D191" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E191" s="7" t="n">
         <v>3</v>
-      </c>
-      <c r="E191" s="7" t="n">
-        <v>2</v>
       </c>
       <c r="F191" s="2" t="n"/>
       <c r="G191" s="9" t="n">
@@ -5845,12 +5845,12 @@
       <c r="C195" s="2" t="n"/>
       <c r="D195" s="6" t="inlineStr">
         <is>
-          <t>520-4: Chemistry - 4</t>
+          <t>520-3: Chemistry - 3</t>
         </is>
       </c>
       <c r="E195" s="6" t="inlineStr">
         <is>
-          <t>520-4: Chemistry - 4</t>
+          <t>520-3: Chemistry - 3</t>
         </is>
       </c>
       <c r="F195" s="2" t="n"/>
@@ -5913,12 +5913,12 @@
       <c r="C197" s="2" t="n"/>
       <c r="D197" s="6" t="inlineStr">
         <is>
-          <t>520-2: Chemistry - 2</t>
+          <t>520-4: Chemistry - 4</t>
         </is>
       </c>
       <c r="E197" s="6" t="inlineStr">
         <is>
-          <t>520-2: Chemistry - 2</t>
+          <t>520-4: Chemistry - 4</t>
         </is>
       </c>
       <c r="F197" s="2" t="n"/>
@@ -6015,12 +6015,12 @@
       <c r="C200" s="2" t="n"/>
       <c r="D200" s="6" t="inlineStr">
         <is>
-          <t>520-3: Chemistry - 3</t>
+          <t>520-2: Chemistry - 2</t>
         </is>
       </c>
       <c r="E200" s="6" t="inlineStr">
         <is>
-          <t>520-3: Chemistry - 3</t>
+          <t>520-2: Chemistry - 2</t>
         </is>
       </c>
       <c r="F200" s="2" t="n"/>
@@ -6507,12 +6507,12 @@
       <c r="C219" s="2" t="n"/>
       <c r="D219" s="6" t="inlineStr">
         <is>
-          <t>729-2: AP Business with Personal Finance - 2</t>
+          <t>729-1: AP Business with Personal Finance - 1</t>
         </is>
       </c>
       <c r="E219" s="6" t="inlineStr">
         <is>
-          <t>729-2: AP Business with Personal Finance - 2</t>
+          <t>729-1: AP Business with Personal Finance - 1</t>
         </is>
       </c>
       <c r="F219" s="2" t="n"/>
@@ -6541,12 +6541,12 @@
       <c r="C220" s="2" t="n"/>
       <c r="D220" s="6" t="inlineStr">
         <is>
-          <t>729-1: AP Business with Personal Finance - 1</t>
+          <t>729-2: AP Business with Personal Finance - 2</t>
         </is>
       </c>
       <c r="E220" s="6" t="inlineStr">
         <is>
-          <t>729-1: AP Business with Personal Finance - 1</t>
+          <t>729-2: AP Business with Personal Finance - 2</t>
         </is>
       </c>
       <c r="F220" s="2" t="n"/>
@@ -6906,7 +6906,7 @@
       <c r="C233" s="2" t="n"/>
       <c r="D233" s="6" t="inlineStr">
         <is>
-          <t>144-1-F: Public Speaking - 1</t>
+          <t>144-3-F: Public Speaking - 3</t>
         </is>
       </c>
       <c r="E233" s="7" t="inlineStr">
@@ -6974,7 +6974,7 @@
       <c r="C235" s="2" t="n"/>
       <c r="D235" s="6" t="inlineStr">
         <is>
-          <t>144-3-F: Public Speaking - 3</t>
+          <t>144-1-F: Public Speaking - 1</t>
         </is>
       </c>
       <c r="E235" s="7" t="inlineStr">
@@ -8194,14 +8194,14 @@
         </is>
       </c>
       <c r="C280" s="2" t="n"/>
-      <c r="D280" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E280" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D280" s="6" t="inlineStr">
+        <is>
+          <t>422-2: Geometry - 2</t>
+        </is>
+      </c>
+      <c r="E280" s="6" t="inlineStr">
+        <is>
+          <t>422-2: Geometry - 2</t>
         </is>
       </c>
       <c r="F280" s="2" t="n"/>
@@ -8230,12 +8230,12 @@
       <c r="C281" s="2" t="n"/>
       <c r="D281" s="6" t="inlineStr">
         <is>
-          <t>422-2: Geometry - 2</t>
+          <t>422-1: Geometry - 1</t>
         </is>
       </c>
       <c r="E281" s="6" t="inlineStr">
         <is>
-          <t>422-2: Geometry - 2</t>
+          <t>422-1: Geometry - 1</t>
         </is>
       </c>
       <c r="F281" s="2" t="n"/>
@@ -8298,12 +8298,12 @@
       <c r="C283" s="2" t="n"/>
       <c r="D283" s="6" t="inlineStr">
         <is>
-          <t>422-1: Geometry - 1</t>
+          <t>450-2: Calculus H - 2</t>
         </is>
       </c>
       <c r="E283" s="6" t="inlineStr">
         <is>
-          <t>422-1: Geometry - 1</t>
+          <t>450-2: Calculus H - 2</t>
         </is>
       </c>
       <c r="F283" s="2" t="n"/>
@@ -8364,14 +8364,14 @@
         </is>
       </c>
       <c r="C285" s="2" t="n"/>
-      <c r="D285" s="6" t="inlineStr">
-        <is>
-          <t>450-2: Calculus H - 2</t>
-        </is>
-      </c>
-      <c r="E285" s="6" t="inlineStr">
-        <is>
-          <t>450-2: Calculus H - 2</t>
+      <c r="D285" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E285" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F285" s="2" t="n"/>
@@ -8960,12 +8960,12 @@
       <c r="C307" s="2" t="n"/>
       <c r="D307" s="6" t="inlineStr">
         <is>
-          <t>120-1: American Literature - 1</t>
+          <t>120-2: American Literature - 2</t>
         </is>
       </c>
       <c r="E307" s="6" t="inlineStr">
         <is>
-          <t>120-1: American Literature - 1</t>
+          <t>120-2: American Literature - 2</t>
         </is>
       </c>
       <c r="F307" s="2" t="n"/>
@@ -8994,12 +8994,12 @@
       <c r="C308" s="2" t="n"/>
       <c r="D308" s="6" t="inlineStr">
         <is>
-          <t>120-2: American Literature - 2</t>
+          <t>120-1: American Literature - 1</t>
         </is>
       </c>
       <c r="E308" s="6" t="inlineStr">
         <is>
-          <t>120-2: American Literature - 2</t>
+          <t>120-1: American Literature - 1</t>
         </is>
       </c>
       <c r="F308" s="2" t="n"/>
@@ -9486,12 +9486,12 @@
       <c r="C327" s="2" t="n"/>
       <c r="D327" s="6" t="inlineStr">
         <is>
-          <t>830-1: Theology 11 - 1</t>
-        </is>
-      </c>
-      <c r="E327" s="6" t="inlineStr">
-        <is>
-          <t>830-1: Theology 11 - 1</t>
+          <t>849-3-F: Catholic Social Teaching - 3</t>
+        </is>
+      </c>
+      <c r="E327" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F327" s="2" t="n"/>
@@ -9518,14 +9518,14 @@
         </is>
       </c>
       <c r="C328" s="2" t="n"/>
-      <c r="D328" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E328" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D328" s="6" t="inlineStr">
+        <is>
+          <t>849-1-F: Catholic Social Teaching - 1</t>
+        </is>
+      </c>
+      <c r="E328" s="6" t="inlineStr">
+        <is>
+          <t>849-8-S: Catholic Social Teaching - 8</t>
         </is>
       </c>
       <c r="F328" s="2" t="n"/>
@@ -9552,14 +9552,14 @@
         </is>
       </c>
       <c r="C329" s="2" t="n"/>
-      <c r="D329" s="6" t="inlineStr">
-        <is>
-          <t>820-2: Theology 10 - 2</t>
+      <c r="D329" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="E329" s="6" t="inlineStr">
         <is>
-          <t>820-2: Theology 10 - 2</t>
+          <t>849-7-S: Catholic Social Teaching - 7</t>
         </is>
       </c>
       <c r="F329" s="2" t="n"/>
@@ -9586,14 +9586,14 @@
         </is>
       </c>
       <c r="C330" s="2" t="n"/>
-      <c r="D330" s="6" t="inlineStr">
-        <is>
-          <t>810-1: Theology 9 - 1</t>
+      <c r="D330" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="E330" s="6" t="inlineStr">
         <is>
-          <t>810-1: Theology 9 - 1</t>
+          <t>849-5-S: Catholic Social Teaching - 5</t>
         </is>
       </c>
       <c r="F330" s="2" t="n"/>
@@ -9620,14 +9620,14 @@
         </is>
       </c>
       <c r="C331" s="2" t="n"/>
-      <c r="D331" s="6" t="inlineStr">
-        <is>
-          <t>810-3: Theology 9 - 3</t>
+      <c r="D331" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="E331" s="6" t="inlineStr">
         <is>
-          <t>810-3: Theology 9 - 3</t>
+          <t>849-6-S: Catholic Social Teaching - 6</t>
         </is>
       </c>
       <c r="F331" s="2" t="n"/>
@@ -9656,12 +9656,12 @@
       <c r="C332" s="2" t="n"/>
       <c r="D332" s="6" t="inlineStr">
         <is>
-          <t>820-1: Theology 10 - 1</t>
+          <t>849-4-F: Catholic Social Teaching - 4; 830-9: Theology 11 - 9</t>
         </is>
       </c>
       <c r="E332" s="6" t="inlineStr">
         <is>
-          <t>820-1: Theology 10 - 1</t>
+          <t>830-9: Theology 11 - 9</t>
         </is>
       </c>
       <c r="F332" s="2" t="n"/>
@@ -9690,12 +9690,12 @@
       <c r="C333" s="2" t="n"/>
       <c r="D333" s="6" t="inlineStr">
         <is>
-          <t>810-2: Theology 9 - 2</t>
-        </is>
-      </c>
-      <c r="E333" s="6" t="inlineStr">
-        <is>
-          <t>810-2: Theology 9 - 2</t>
+          <t>849-2-F: Catholic Social Teaching - 2</t>
+        </is>
+      </c>
+      <c r="E333" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F333" s="2" t="n"/>
@@ -9718,10 +9718,10 @@
       </c>
       <c r="C334" s="2" t="n"/>
       <c r="D334" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E334" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F334" s="2" t="n"/>
       <c r="G334" s="9" t="n">
@@ -9738,8 +9738,8 @@
         </is>
       </c>
       <c r="C335" s="2" t="n"/>
-      <c r="D335" s="9" t="n">
-        <v>5</v>
+      <c r="D335" s="7" t="n">
+        <v>2</v>
       </c>
       <c r="E335" s="9" t="n">
         <v>5</v>
@@ -10148,12 +10148,12 @@
       <c r="C351" s="2" t="n"/>
       <c r="D351" s="6" t="inlineStr">
         <is>
-          <t>443-2: AP Precalculus - 2</t>
+          <t>443-1: AP Precalculus - 1</t>
         </is>
       </c>
       <c r="E351" s="6" t="inlineStr">
         <is>
-          <t>443-2: AP Precalculus - 2</t>
+          <t>443-1: AP Precalculus - 1</t>
         </is>
       </c>
       <c r="F351" s="2" t="n"/>
@@ -10182,12 +10182,12 @@
       <c r="C352" s="2" t="n"/>
       <c r="D352" s="6" t="inlineStr">
         <is>
-          <t>443-1: AP Precalculus - 1</t>
+          <t>443-2: AP Precalculus - 2</t>
         </is>
       </c>
       <c r="E352" s="6" t="inlineStr">
         <is>
-          <t>443-1: AP Precalculus - 1</t>
+          <t>443-2: AP Precalculus - 2</t>
         </is>
       </c>
       <c r="F352" s="2" t="n"/>
@@ -10649,12 +10649,12 @@
       <c r="C368" s="2" t="n"/>
       <c r="D368" s="6" t="inlineStr">
         <is>
-          <t>730-1: U.S. History II - 1</t>
+          <t>730-2: U.S. History II - 2</t>
         </is>
       </c>
       <c r="E368" s="6" t="inlineStr">
         <is>
-          <t>730-1: U.S. History II - 1</t>
+          <t>730-2: U.S. History II - 2</t>
         </is>
       </c>
       <c r="F368" s="2" t="n"/>
@@ -10683,12 +10683,12 @@
       <c r="C369" s="2" t="n"/>
       <c r="D369" s="6" t="inlineStr">
         <is>
-          <t>730-2: U.S. History II - 2</t>
+          <t>730-1: U.S. History II - 1</t>
         </is>
       </c>
       <c r="E369" s="6" t="inlineStr">
         <is>
-          <t>730-2: U.S. History II - 2</t>
+          <t>730-1: U.S. History II - 1</t>
         </is>
       </c>
       <c r="F369" s="2" t="n"/>
@@ -11173,14 +11173,14 @@
         </is>
       </c>
       <c r="C388" s="2" t="n"/>
-      <c r="D388" s="6" t="inlineStr">
-        <is>
-          <t>412-3: Algebra I - 3</t>
-        </is>
-      </c>
-      <c r="E388" s="6" t="inlineStr">
-        <is>
-          <t>412-3: Algebra I - 3</t>
+      <c r="D388" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E388" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F388" s="2" t="n"/>
@@ -11309,14 +11309,14 @@
         </is>
       </c>
       <c r="C392" s="2" t="n"/>
-      <c r="D392" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E392" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D392" s="6" t="inlineStr">
+        <is>
+          <t>412-3: Algebra I - 3</t>
+        </is>
+      </c>
+      <c r="E392" s="6" t="inlineStr">
+        <is>
+          <t>412-3: Algebra I - 3</t>
         </is>
       </c>
       <c r="F392" s="2" t="n"/>
@@ -11394,10 +11394,10 @@
       </c>
       <c r="C395" s="2" t="n"/>
       <c r="D395" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E395" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F395" s="2" t="n"/>
       <c r="G395" s="7" t="n">
@@ -12168,12 +12168,12 @@
       <c r="C424" s="2" t="n"/>
       <c r="D424" s="6" t="inlineStr">
         <is>
-          <t>955-2: Academic Support - 2</t>
+          <t>955-3: Academic Support - 3</t>
         </is>
       </c>
       <c r="E424" s="6" t="inlineStr">
         <is>
-          <t>955-2: Academic Support - 2</t>
+          <t>955-3: Academic Support - 3</t>
         </is>
       </c>
       <c r="F424" s="2" t="n"/>
@@ -12236,12 +12236,12 @@
       <c r="C426" s="2" t="n"/>
       <c r="D426" s="6" t="inlineStr">
         <is>
-          <t>955-1: Academic Support - 1</t>
+          <t>955-2: Academic Support - 2</t>
         </is>
       </c>
       <c r="E426" s="6" t="inlineStr">
         <is>
-          <t>955-1: Academic Support - 1</t>
+          <t>955-2: Academic Support - 2</t>
         </is>
       </c>
       <c r="F426" s="2" t="n"/>
@@ -12270,12 +12270,12 @@
       <c r="C427" s="2" t="n"/>
       <c r="D427" s="6" t="inlineStr">
         <is>
-          <t>955-3: Academic Support - 3</t>
+          <t>955-1: Academic Support - 1</t>
         </is>
       </c>
       <c r="E427" s="6" t="inlineStr">
         <is>
-          <t>955-3: Academic Support - 3</t>
+          <t>955-1: Academic Support - 1</t>
         </is>
       </c>
       <c r="F427" s="2" t="n"/>
@@ -12531,14 +12531,14 @@
         </is>
       </c>
       <c r="C437" s="2" t="n"/>
-      <c r="D437" s="6" t="inlineStr">
-        <is>
-          <t>810-4: Theology 9 - 4</t>
-        </is>
-      </c>
-      <c r="E437" s="6" t="inlineStr">
-        <is>
-          <t>810-4: Theology 9 - 4</t>
+      <c r="D437" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E437" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F437" s="2" t="n"/>
@@ -12567,12 +12567,12 @@
       <c r="C438" s="2" t="n"/>
       <c r="D438" s="6" t="inlineStr">
         <is>
-          <t>810-8: Theology 9 - 8</t>
+          <t>810-6: Theology 9 - 6</t>
         </is>
       </c>
       <c r="E438" s="6" t="inlineStr">
         <is>
-          <t>810-8: Theology 9 - 8</t>
+          <t>810-6: Theology 9 - 6</t>
         </is>
       </c>
       <c r="F438" s="2" t="n"/>
@@ -12635,12 +12635,12 @@
       <c r="C440" s="2" t="n"/>
       <c r="D440" s="6" t="inlineStr">
         <is>
-          <t>810-6: Theology 9 - 6</t>
+          <t>810-4: Theology 9 - 4</t>
         </is>
       </c>
       <c r="E440" s="6" t="inlineStr">
         <is>
-          <t>810-6: Theology 9 - 6</t>
+          <t>810-4: Theology 9 - 4</t>
         </is>
       </c>
       <c r="F440" s="2" t="n"/>
@@ -12667,14 +12667,14 @@
         </is>
       </c>
       <c r="C441" s="2" t="n"/>
-      <c r="D441" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E441" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D441" s="6" t="inlineStr">
+        <is>
+          <t>810-8: Theology 9 - 8</t>
+        </is>
+      </c>
+      <c r="E441" s="6" t="inlineStr">
+        <is>
+          <t>810-8: Theology 9 - 8</t>
         </is>
       </c>
       <c r="F441" s="2" t="n"/>
@@ -12717,11 +12717,11 @@
         </is>
       </c>
       <c r="C443" s="2" t="n"/>
-      <c r="D443" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="E443" s="9" t="n">
-        <v>4</v>
+      <c r="D443" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E443" s="7" t="n">
+        <v>2</v>
       </c>
       <c r="F443" s="2" t="n"/>
       <c r="G443" s="7" t="n">
@@ -13127,12 +13127,12 @@
       <c r="C459" s="2" t="n"/>
       <c r="D459" s="6" t="inlineStr">
         <is>
-          <t>511-4: Biology H - 4</t>
+          <t>511-3: Biology H - 3</t>
         </is>
       </c>
       <c r="E459" s="6" t="inlineStr">
         <is>
-          <t>511-4: Biology H - 4</t>
+          <t>511-3: Biology H - 3</t>
         </is>
       </c>
       <c r="F459" s="2" t="n"/>
@@ -13161,12 +13161,12 @@
       <c r="C460" s="2" t="n"/>
       <c r="D460" s="6" t="inlineStr">
         <is>
-          <t>511-3: Biology H - 3</t>
+          <t>511-4: Biology H - 4</t>
         </is>
       </c>
       <c r="E460" s="6" t="inlineStr">
         <is>
-          <t>511-3: Biology H - 3</t>
+          <t>511-4: Biology H - 4</t>
         </is>
       </c>
       <c r="F460" s="2" t="n"/>
@@ -13456,9 +13456,9 @@
         </is>
       </c>
       <c r="C471" s="2" t="n"/>
-      <c r="D471" s="6" t="inlineStr">
-        <is>
-          <t>766-2-F: AP Microeconomics - 2</t>
+      <c r="D471" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="E471" s="6" t="inlineStr">
@@ -13490,9 +13490,9 @@
         </is>
       </c>
       <c r="C472" s="2" t="n"/>
-      <c r="D472" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D472" s="6" t="inlineStr">
+        <is>
+          <t>766-2-F: AP Microeconomics - 2</t>
         </is>
       </c>
       <c r="E472" s="7" t="inlineStr">
@@ -13857,12 +13857,12 @@
       <c r="C485" s="2" t="n"/>
       <c r="D485" s="6" t="inlineStr">
         <is>
-          <t>530-2: Physics - 2</t>
+          <t>530-3: Physics - 3</t>
         </is>
       </c>
       <c r="E485" s="6" t="inlineStr">
         <is>
-          <t>530-2: Physics - 2</t>
+          <t>530-3: Physics - 3</t>
         </is>
       </c>
       <c r="F485" s="2" t="n"/>
@@ -13891,12 +13891,12 @@
       <c r="C486" s="2" t="n"/>
       <c r="D486" s="6" t="inlineStr">
         <is>
-          <t>530-3: Physics - 3</t>
+          <t>530-2: Physics - 2</t>
         </is>
       </c>
       <c r="E486" s="6" t="inlineStr">
         <is>
-          <t>530-3: Physics - 3</t>
+          <t>530-2: Physics - 2</t>
         </is>
       </c>
       <c r="F486" s="2" t="n"/>
@@ -13962,9 +13962,9 @@
           <t>UNASSIGNED</t>
         </is>
       </c>
-      <c r="E488" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="E488" s="6" t="inlineStr">
+        <is>
+          <t>595-2-S: Engineering Design - 2</t>
         </is>
       </c>
       <c r="F488" s="2" t="n"/>
@@ -13996,9 +13996,9 @@
           <t>595-1-F: Engineering Design - 1</t>
         </is>
       </c>
-      <c r="E489" s="6" t="inlineStr">
-        <is>
-          <t>595-2-S: Engineering Design - 2</t>
+      <c r="E489" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F489" s="2" t="n"/>
@@ -14045,7 +14045,7 @@
         <v>4</v>
       </c>
       <c r="E491" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F491" s="2" t="n"/>
       <c r="G491" s="9" t="n">
@@ -14120,12 +14120,12 @@
       <c r="C495" s="2" t="n"/>
       <c r="D495" s="6" t="inlineStr">
         <is>
-          <t>820-4: Theology 10 - 4</t>
+          <t>830-1: Theology 11 - 1</t>
         </is>
       </c>
       <c r="E495" s="6" t="inlineStr">
         <is>
-          <t>820-4: Theology 10 - 4</t>
+          <t>830-1: Theology 11 - 1</t>
         </is>
       </c>
       <c r="F495" s="2" t="n"/>
@@ -14186,14 +14186,14 @@
         </is>
       </c>
       <c r="C497" s="2" t="n"/>
-      <c r="D497" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E497" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D497" s="6" t="inlineStr">
+        <is>
+          <t>820-4: Theology 10 - 4</t>
+        </is>
+      </c>
+      <c r="E497" s="6" t="inlineStr">
+        <is>
+          <t>820-4: Theology 10 - 4</t>
         </is>
       </c>
       <c r="F497" s="2" t="n"/>
@@ -14288,14 +14288,14 @@
         </is>
       </c>
       <c r="C500" s="2" t="n"/>
-      <c r="D500" s="6" t="inlineStr">
-        <is>
-          <t>830-3: Theology 11 - 3</t>
-        </is>
-      </c>
-      <c r="E500" s="6" t="inlineStr">
-        <is>
-          <t>830-3: Theology 11 - 3</t>
+      <c r="D500" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E500" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F500" s="2" t="n"/>
@@ -14372,11 +14372,11 @@
         </is>
       </c>
       <c r="C503" s="2" t="n"/>
-      <c r="D503" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="E503" s="7" t="n">
-        <v>3</v>
+      <c r="D503" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E503" s="9" t="n">
+        <v>5</v>
       </c>
       <c r="F503" s="2" t="n"/>
       <c r="G503" s="7" t="n">
@@ -14551,14 +14551,14 @@
         </is>
       </c>
       <c r="C510" s="2" t="n"/>
-      <c r="D510" s="6" t="inlineStr">
-        <is>
-          <t>851-3-F: Spirituality of Vocation - 3</t>
-        </is>
-      </c>
-      <c r="E510" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D510" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E510" s="6" t="inlineStr">
+        <is>
+          <t>851-5-S: Spirituality of Vocation - 5</t>
         </is>
       </c>
       <c r="F510" s="2" t="n"/>
@@ -14592,7 +14592,7 @@
       </c>
       <c r="E511" s="6" t="inlineStr">
         <is>
-          <t>851-5-S: Spirituality of Vocation - 5</t>
+          <t>851-6-S: Spirituality of Vocation - 6</t>
         </is>
       </c>
       <c r="F511" s="2" t="n"/>
@@ -14621,12 +14621,12 @@
       <c r="C512" s="2" t="n"/>
       <c r="D512" s="6" t="inlineStr">
         <is>
-          <t>830-4: Theology 11 - 4; 851-2-F: Spirituality of Vocation - 2</t>
+          <t>830-3: Theology 11 - 3; 851-2-F: Spirituality of Vocation - 2</t>
         </is>
       </c>
       <c r="E512" s="6" t="inlineStr">
         <is>
-          <t>830-4: Theology 11 - 4</t>
+          <t>830-3: Theology 11 - 3</t>
         </is>
       </c>
       <c r="F512" s="2" t="n"/>
@@ -14653,14 +14653,14 @@
         </is>
       </c>
       <c r="C513" s="2" t="n"/>
-      <c r="D513" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E513" s="6" t="inlineStr">
-        <is>
-          <t>851-6-S: Spirituality of Vocation - 6</t>
+      <c r="D513" s="6" t="inlineStr">
+        <is>
+          <t>851-3-F: Spirituality of Vocation - 3</t>
+        </is>
+      </c>
+      <c r="E513" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F513" s="2" t="n"/>
@@ -14706,8 +14706,8 @@
       <c r="D515" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E515" s="7" t="n">
-        <v>3</v>
+      <c r="E515" s="9" t="n">
+        <v>5</v>
       </c>
       <c r="F515" s="2" t="n"/>
       <c r="G515" s="9" t="n">
@@ -14782,12 +14782,12 @@
       <c r="C519" s="2" t="n"/>
       <c r="D519" s="6" t="inlineStr">
         <is>
-          <t>820-7: Theology 10 - 7</t>
+          <t>820-8: Theology 10 - 8</t>
         </is>
       </c>
       <c r="E519" s="6" t="inlineStr">
         <is>
-          <t>820-7: Theology 10 - 7</t>
+          <t>820-8: Theology 10 - 8</t>
         </is>
       </c>
       <c r="F519" s="2" t="n"/>
@@ -14850,12 +14850,12 @@
       <c r="C521" s="2" t="n"/>
       <c r="D521" s="6" t="inlineStr">
         <is>
-          <t>820-8: Theology 10 - 8</t>
+          <t>820-7: Theology 10 - 7</t>
         </is>
       </c>
       <c r="E521" s="6" t="inlineStr">
         <is>
-          <t>820-8: Theology 10 - 8</t>
+          <t>820-7: Theology 10 - 7</t>
         </is>
       </c>
       <c r="F521" s="2" t="n"/>
@@ -16109,9 +16109,9 @@
           <t>570-1-F: Introduction to Robotics - 1</t>
         </is>
       </c>
-      <c r="E567" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="E567" s="6" t="inlineStr">
+        <is>
+          <t>580-4-S: Robotics Engineering - 4</t>
         </is>
       </c>
       <c r="F567" s="2" t="n"/>
@@ -16172,14 +16172,14 @@
         </is>
       </c>
       <c r="C569" s="2" t="n"/>
-      <c r="D569" s="6" t="inlineStr">
-        <is>
-          <t>580-1-F: Robotics Engineering - 1</t>
-        </is>
-      </c>
-      <c r="E569" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D569" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E569" s="6" t="inlineStr">
+        <is>
+          <t>580-2-S: Robotics Engineering - 2</t>
         </is>
       </c>
       <c r="F569" s="2" t="n"/>
@@ -16208,7 +16208,7 @@
       <c r="C570" s="2" t="n"/>
       <c r="D570" s="6" t="inlineStr">
         <is>
-          <t>580-3-F: Robotics Engineering - 3</t>
+          <t>580-1-F: Robotics Engineering - 1</t>
         </is>
       </c>
       <c r="E570" s="6" t="inlineStr">
@@ -16240,14 +16240,14 @@
         </is>
       </c>
       <c r="C571" s="2" t="n"/>
-      <c r="D571" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E571" s="6" t="inlineStr">
-        <is>
-          <t>585-2-S: Robotics Design - 2</t>
+      <c r="D571" s="6" t="inlineStr">
+        <is>
+          <t>580-3-F: Robotics Engineering - 3</t>
+        </is>
+      </c>
+      <c r="E571" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F571" s="2" t="n"/>
@@ -16279,9 +16279,9 @@
           <t>585-1-F: Robotics Design - 1</t>
         </is>
       </c>
-      <c r="E572" s="6" t="inlineStr">
-        <is>
-          <t>580-4-S: Robotics Engineering - 4</t>
+      <c r="E572" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F572" s="2" t="n"/>
@@ -16315,7 +16315,7 @@
       </c>
       <c r="E573" s="6" t="inlineStr">
         <is>
-          <t>580-2-S: Robotics Engineering - 2</t>
+          <t>585-2-S: Robotics Design - 2</t>
         </is>
       </c>
       <c r="F573" s="2" t="n"/>
@@ -16358,8 +16358,8 @@
         </is>
       </c>
       <c r="C575" s="2" t="n"/>
-      <c r="D575" s="9" t="n">
-        <v>4</v>
+      <c r="D575" s="7" t="n">
+        <v>3</v>
       </c>
       <c r="E575" s="9" t="n">
         <v>4</v>
@@ -16435,14 +16435,14 @@
         </is>
       </c>
       <c r="C579" s="2" t="n"/>
-      <c r="D579" s="6" t="inlineStr">
-        <is>
-          <t>521-4: Chemistry H - 4</t>
-        </is>
-      </c>
-      <c r="E579" s="6" t="inlineStr">
-        <is>
-          <t>521-4: Chemistry H - 4</t>
+      <c r="D579" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E579" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F579" s="2" t="n"/>
@@ -16537,14 +16537,14 @@
         </is>
       </c>
       <c r="C582" s="2" t="n"/>
-      <c r="D582" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E582" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D582" s="6" t="inlineStr">
+        <is>
+          <t>521-4: Chemistry H - 4</t>
+        </is>
+      </c>
+      <c r="E582" s="6" t="inlineStr">
+        <is>
+          <t>521-4: Chemistry H - 4</t>
         </is>
       </c>
       <c r="F582" s="2" t="n"/>
@@ -16607,12 +16607,12 @@
       <c r="C584" s="2" t="n"/>
       <c r="D584" s="6" t="inlineStr">
         <is>
-          <t>521-2: Chemistry H - 2</t>
+          <t>521-3: Chemistry H - 3</t>
         </is>
       </c>
       <c r="E584" s="6" t="inlineStr">
         <is>
-          <t>521-2: Chemistry H - 2</t>
+          <t>521-3: Chemistry H - 3</t>
         </is>
       </c>
       <c r="F584" s="2" t="n"/>
@@ -16641,12 +16641,12 @@
       <c r="C585" s="2" t="n"/>
       <c r="D585" s="6" t="inlineStr">
         <is>
-          <t>521-3: Chemistry H - 3</t>
+          <t>521-2: Chemistry H - 2</t>
         </is>
       </c>
       <c r="E585" s="6" t="inlineStr">
         <is>
-          <t>521-3: Chemistry H - 3</t>
+          <t>521-2: Chemistry H - 2</t>
         </is>
       </c>
       <c r="F585" s="2" t="n"/>
@@ -16689,11 +16689,11 @@
         </is>
       </c>
       <c r="C587" s="2" t="n"/>
-      <c r="D587" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="E587" s="7" t="n">
-        <v>3</v>
+      <c r="D587" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E587" s="9" t="n">
+        <v>5</v>
       </c>
       <c r="F587" s="2" t="n"/>
       <c r="G587" s="9" t="n">
@@ -16836,12 +16836,12 @@
       <c r="C593" s="2" t="n"/>
       <c r="D593" s="6" t="inlineStr">
         <is>
-          <t>720-1: U.S. History I - 1</t>
+          <t>720-2: U.S. History I - 2</t>
         </is>
       </c>
       <c r="E593" s="6" t="inlineStr">
         <is>
-          <t>720-1: U.S. History I - 1</t>
+          <t>720-2: U.S. History I - 2</t>
         </is>
       </c>
       <c r="F593" s="2" t="n"/>
@@ -16870,12 +16870,12 @@
       <c r="C594" s="2" t="n"/>
       <c r="D594" s="6" t="inlineStr">
         <is>
-          <t>720-2: U.S. History I - 2</t>
+          <t>720-1: U.S. History I - 1</t>
         </is>
       </c>
       <c r="E594" s="6" t="inlineStr">
         <is>
-          <t>720-2: U.S. History I - 2</t>
+          <t>720-1: U.S. History I - 1</t>
         </is>
       </c>
       <c r="F594" s="2" t="n"/>
@@ -17827,14 +17827,14 @@
         </is>
       </c>
       <c r="C629" s="2" t="n"/>
-      <c r="D629" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E629" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D629" s="6" t="inlineStr">
+        <is>
+          <t>322-2: Italian II - 2</t>
+        </is>
+      </c>
+      <c r="E629" s="6" t="inlineStr">
+        <is>
+          <t>322-2: Italian II - 2</t>
         </is>
       </c>
       <c r="F629" s="2" t="n"/>
@@ -17861,14 +17861,14 @@
         </is>
       </c>
       <c r="C630" s="2" t="n"/>
-      <c r="D630" s="6" t="inlineStr">
-        <is>
-          <t>332-1: Italian III - 1</t>
-        </is>
-      </c>
-      <c r="E630" s="6" t="inlineStr">
-        <is>
-          <t>332-1: Italian III - 1</t>
+      <c r="D630" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E630" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F630" s="2" t="n"/>
@@ -17931,12 +17931,12 @@
       <c r="C632" s="2" t="n"/>
       <c r="D632" s="6" t="inlineStr">
         <is>
-          <t>322-2: Italian II - 2</t>
+          <t>332-1: Italian III - 1</t>
         </is>
       </c>
       <c r="E632" s="6" t="inlineStr">
         <is>
-          <t>322-2: Italian II - 2</t>
+          <t>332-1: Italian III - 1</t>
         </is>
       </c>
       <c r="F632" s="2" t="n"/>
@@ -18013,11 +18013,11 @@
         </is>
       </c>
       <c r="C635" s="2" t="n"/>
-      <c r="D635" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="E635" s="9" t="n">
-        <v>4</v>
+      <c r="D635" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E635" s="7" t="n">
+        <v>3</v>
       </c>
       <c r="F635" s="2" t="n"/>
       <c r="G635" s="9" t="n">
@@ -18126,12 +18126,12 @@
       <c r="C640" s="2" t="n"/>
       <c r="D640" s="6" t="inlineStr">
         <is>
-          <t>733-3: AP U.S. History - 3</t>
+          <t>733-2: AP U.S. History - 2</t>
         </is>
       </c>
       <c r="E640" s="6" t="inlineStr">
         <is>
-          <t>733-3: AP U.S. History - 3</t>
+          <t>733-2: AP U.S. History - 2</t>
         </is>
       </c>
       <c r="F640" s="2" t="n"/>
@@ -18296,12 +18296,12 @@
       <c r="C645" s="2" t="n"/>
       <c r="D645" s="6" t="inlineStr">
         <is>
-          <t>733-2: AP U.S. History - 2</t>
+          <t>733-3: AP U.S. History - 3</t>
         </is>
       </c>
       <c r="E645" s="6" t="inlineStr">
         <is>
-          <t>733-2: AP U.S. History - 2</t>
+          <t>733-3: AP U.S. History - 3</t>
         </is>
       </c>
       <c r="F645" s="2" t="n"/>
@@ -18423,12 +18423,12 @@
       <c r="C651" s="2" t="n"/>
       <c r="D651" s="6" t="inlineStr">
         <is>
-          <t>140-1: World Literature - 1</t>
+          <t>140-2: World Literature - 2</t>
         </is>
       </c>
       <c r="E651" s="6" t="inlineStr">
         <is>
-          <t>140-1: World Literature - 1</t>
+          <t>140-2: World Literature - 2</t>
         </is>
       </c>
       <c r="F651" s="2" t="n"/>
@@ -18627,12 +18627,12 @@
       <c r="C657" s="2" t="n"/>
       <c r="D657" s="6" t="inlineStr">
         <is>
-          <t>140-2: World Literature - 2</t>
+          <t>140-1: World Literature - 1</t>
         </is>
       </c>
       <c r="E657" s="6" t="inlineStr">
         <is>
-          <t>140-2: World Literature - 2</t>
+          <t>140-1: World Literature - 1</t>
         </is>
       </c>
       <c r="F657" s="2" t="n"/>
@@ -18820,14 +18820,14 @@
         </is>
       </c>
       <c r="C665" s="2" t="n"/>
-      <c r="D665" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E665" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D665" s="6" t="inlineStr">
+        <is>
+          <t>110-1: Composition &amp; Literature - 1</t>
+        </is>
+      </c>
+      <c r="E665" s="6" t="inlineStr">
+        <is>
+          <t>110-1: Composition &amp; Literature - 1</t>
         </is>
       </c>
       <c r="F665" s="2" t="n"/>
@@ -18856,12 +18856,12 @@
       <c r="C666" s="2" t="n"/>
       <c r="D666" s="6" t="inlineStr">
         <is>
-          <t>121-1: American Literature H - 1</t>
+          <t>121-2: American Literature H - 2</t>
         </is>
       </c>
       <c r="E666" s="6" t="inlineStr">
         <is>
-          <t>121-1: American Literature H - 1</t>
+          <t>121-2: American Literature H - 2</t>
         </is>
       </c>
       <c r="F666" s="2" t="n"/>
@@ -18890,12 +18890,12 @@
       <c r="C667" s="2" t="n"/>
       <c r="D667" s="6" t="inlineStr">
         <is>
-          <t>110-1: Composition &amp; Literature - 1</t>
+          <t>121-1: American Literature H - 1</t>
         </is>
       </c>
       <c r="E667" s="6" t="inlineStr">
         <is>
-          <t>110-1: Composition &amp; Literature - 1</t>
+          <t>121-1: American Literature H - 1</t>
         </is>
       </c>
       <c r="F667" s="2" t="n"/>
@@ -18922,14 +18922,14 @@
         </is>
       </c>
       <c r="C668" s="2" t="n"/>
-      <c r="D668" s="6" t="inlineStr">
-        <is>
-          <t>121-2: American Literature H - 2</t>
-        </is>
-      </c>
-      <c r="E668" s="6" t="inlineStr">
-        <is>
-          <t>121-2: American Literature H - 2</t>
+      <c r="D668" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E668" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F668" s="2" t="n"/>
@@ -19006,11 +19006,11 @@
         </is>
       </c>
       <c r="C671" s="2" t="n"/>
-      <c r="D671" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="E671" s="9" t="n">
-        <v>4</v>
+      <c r="D671" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E671" s="7" t="n">
+        <v>3</v>
       </c>
       <c r="F671" s="2" t="n"/>
       <c r="G671" s="9" t="n">
@@ -19185,14 +19185,14 @@
         </is>
       </c>
       <c r="C678" s="2" t="n"/>
-      <c r="D678" s="6" t="inlineStr">
-        <is>
-          <t>410-3: Algebra I - 3</t>
-        </is>
-      </c>
-      <c r="E678" s="6" t="inlineStr">
-        <is>
-          <t>410-3: Algebra I - 3</t>
+      <c r="D678" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E678" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F678" s="2" t="n"/>
@@ -19287,14 +19287,14 @@
         </is>
       </c>
       <c r="C681" s="2" t="n"/>
-      <c r="D681" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E681" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D681" s="6" t="inlineStr">
+        <is>
+          <t>410-3: Algebra I - 3</t>
+        </is>
+      </c>
+      <c r="E681" s="6" t="inlineStr">
+        <is>
+          <t>410-3: Algebra I - 3</t>
         </is>
       </c>
       <c r="F681" s="2" t="n"/>
@@ -19337,11 +19337,11 @@
         </is>
       </c>
       <c r="C683" s="2" t="n"/>
-      <c r="D683" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="E683" s="9" t="n">
-        <v>5</v>
+      <c r="D683" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E683" s="7" t="n">
+        <v>3</v>
       </c>
       <c r="F683" s="2" t="n"/>
       <c r="G683" s="7" t="n">
@@ -19416,12 +19416,12 @@
       <c r="C687" s="2" t="n"/>
       <c r="D687" s="6" t="inlineStr">
         <is>
-          <t>830-9: Theology 11 - 9</t>
+          <t>830-8: Theology 11 - 8</t>
         </is>
       </c>
       <c r="E687" s="6" t="inlineStr">
         <is>
-          <t>830-9: Theology 11 - 9</t>
+          <t>830-8: Theology 11 - 8</t>
         </is>
       </c>
       <c r="F687" s="2" t="n"/>
@@ -19484,12 +19484,12 @@
       <c r="C689" s="2" t="n"/>
       <c r="D689" s="6" t="inlineStr">
         <is>
-          <t>830-8: Theology 11 - 8</t>
+          <t>830-6: Theology 11 - 6</t>
         </is>
       </c>
       <c r="E689" s="6" t="inlineStr">
         <is>
-          <t>830-8: Theology 11 - 8</t>
+          <t>830-6: Theology 11 - 6</t>
         </is>
       </c>
       <c r="F689" s="2" t="n"/>
@@ -19552,12 +19552,12 @@
       <c r="C691" s="2" t="n"/>
       <c r="D691" s="6" t="inlineStr">
         <is>
-          <t>830-6: Theology 11 - 6</t>
+          <t>830-5: Theology 11 - 5</t>
         </is>
       </c>
       <c r="E691" s="6" t="inlineStr">
         <is>
-          <t>830-6: Theology 11 - 6</t>
+          <t>830-5: Theology 11 - 5</t>
         </is>
       </c>
       <c r="F691" s="2" t="n"/>
@@ -19620,12 +19620,12 @@
       <c r="C693" s="2" t="n"/>
       <c r="D693" s="6" t="inlineStr">
         <is>
-          <t>830-5: Theology 11 - 5</t>
+          <t>830-4: Theology 11 - 4</t>
         </is>
       </c>
       <c r="E693" s="6" t="inlineStr">
         <is>
-          <t>830-5: Theology 11 - 5</t>
+          <t>830-4: Theology 11 - 4</t>
         </is>
       </c>
       <c r="F693" s="2" t="n"/>
@@ -20081,9 +20081,9 @@
           <t>2024-1-F: TV/Film Process and Principles - 1</t>
         </is>
       </c>
-      <c r="E711" s="6" t="inlineStr">
-        <is>
-          <t>2044-2-S: TV/Film Production II - 2</t>
+      <c r="E711" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F711" s="2" t="n"/>
@@ -20115,9 +20115,9 @@
           <t>2034-1-F: TV/Film Production &amp; Editing I - 1</t>
         </is>
       </c>
-      <c r="E712" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="E712" s="6" t="inlineStr">
+        <is>
+          <t>2044-2-S: TV/Film Production II - 2</t>
         </is>
       </c>
       <c r="F712" s="2" t="n"/>
@@ -20178,9 +20178,9 @@
         </is>
       </c>
       <c r="C714" s="2" t="n"/>
-      <c r="D714" s="6" t="inlineStr">
-        <is>
-          <t>2054-1-F: Digital Media - 1</t>
+      <c r="D714" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="E714" s="7" t="inlineStr">
@@ -20212,9 +20212,9 @@
         </is>
       </c>
       <c r="C715" s="2" t="n"/>
-      <c r="D715" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D715" s="6" t="inlineStr">
+        <is>
+          <t>2054-1-F: Digital Media - 1</t>
         </is>
       </c>
       <c r="E715" s="6" t="inlineStr">
@@ -20330,8 +20330,8 @@
         </is>
       </c>
       <c r="C719" s="2" t="n"/>
-      <c r="D719" s="9" t="n">
-        <v>4</v>
+      <c r="D719" s="7" t="n">
+        <v>3</v>
       </c>
       <c r="E719" s="7" t="n">
         <v>3</v>
@@ -20509,14 +20509,14 @@
         </is>
       </c>
       <c r="C726" s="2" t="n"/>
-      <c r="D726" s="6" t="inlineStr">
-        <is>
-          <t>744-1-F: Sociology - 1</t>
-        </is>
-      </c>
-      <c r="E726" s="6" t="inlineStr">
-        <is>
-          <t>744-2-S: Sociology - 2</t>
+      <c r="D726" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E726" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F726" s="2" t="n"/>
@@ -20611,14 +20611,14 @@
         </is>
       </c>
       <c r="C729" s="2" t="n"/>
-      <c r="D729" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E729" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D729" s="6" t="inlineStr">
+        <is>
+          <t>744-1-F: Sociology - 1</t>
+        </is>
+      </c>
+      <c r="E729" s="6" t="inlineStr">
+        <is>
+          <t>744-2-S: Sociology - 2</t>
         </is>
       </c>
       <c r="F729" s="2" t="n"/>
@@ -20661,11 +20661,11 @@
         </is>
       </c>
       <c r="C731" s="2" t="n"/>
-      <c r="D731" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="E731" s="9" t="n">
-        <v>6</v>
+      <c r="D731" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E731" s="7" t="n">
+        <v>3</v>
       </c>
       <c r="F731" s="2" t="n"/>
       <c r="G731" s="7" t="n">
@@ -20738,14 +20738,14 @@
         </is>
       </c>
       <c r="C735" s="2" t="n"/>
-      <c r="D735" s="6" t="inlineStr">
-        <is>
-          <t>331-3: Spanish III H - 3</t>
-        </is>
-      </c>
-      <c r="E735" s="6" t="inlineStr">
-        <is>
-          <t>331-3: Spanish III H - 3</t>
+      <c r="D735" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E735" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F735" s="2" t="n"/>
@@ -20806,14 +20806,14 @@
         </is>
       </c>
       <c r="C737" s="2" t="n"/>
-      <c r="D737" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E737" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D737" s="6" t="inlineStr">
+        <is>
+          <t>330-3: Spanish III - 3</t>
+        </is>
+      </c>
+      <c r="E737" s="6" t="inlineStr">
+        <is>
+          <t>330-3: Spanish III - 3</t>
         </is>
       </c>
       <c r="F737" s="2" t="n"/>
@@ -20842,12 +20842,12 @@
       <c r="C738" s="2" t="n"/>
       <c r="D738" s="6" t="inlineStr">
         <is>
-          <t>330-3: Spanish III - 3</t>
+          <t>330-2: Spanish III - 2</t>
         </is>
       </c>
       <c r="E738" s="6" t="inlineStr">
         <is>
-          <t>330-3: Spanish III - 3</t>
+          <t>330-2: Spanish III - 2</t>
         </is>
       </c>
       <c r="F738" s="2" t="n"/>
@@ -20876,12 +20876,12 @@
       <c r="C739" s="2" t="n"/>
       <c r="D739" s="6" t="inlineStr">
         <is>
-          <t>330-2: Spanish III - 2</t>
+          <t>331-3: Spanish III H - 3</t>
         </is>
       </c>
       <c r="E739" s="6" t="inlineStr">
         <is>
-          <t>330-2: Spanish III - 2</t>
+          <t>331-3: Spanish III H - 3</t>
         </is>
       </c>
       <c r="F739" s="2" t="n"/>
@@ -20910,12 +20910,12 @@
       <c r="C740" s="2" t="n"/>
       <c r="D740" s="6" t="inlineStr">
         <is>
-          <t>331-1: Spanish III H - 1</t>
+          <t>331-2: Spanish III H - 2</t>
         </is>
       </c>
       <c r="E740" s="6" t="inlineStr">
         <is>
-          <t>331-1: Spanish III H - 1</t>
+          <t>331-2: Spanish III H - 2</t>
         </is>
       </c>
       <c r="F740" s="2" t="n"/>
@@ -20944,12 +20944,12 @@
       <c r="C741" s="2" t="n"/>
       <c r="D741" s="6" t="inlineStr">
         <is>
-          <t>331-2: Spanish III H - 2</t>
+          <t>331-1: Spanish III H - 1</t>
         </is>
       </c>
       <c r="E741" s="6" t="inlineStr">
         <is>
-          <t>331-2: Spanish III H - 2</t>
+          <t>331-1: Spanish III H - 1</t>
         </is>
       </c>
       <c r="F741" s="2" t="n"/>
@@ -20993,10 +20993,10 @@
       </c>
       <c r="C743" s="2" t="n"/>
       <c r="D743" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E743" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F743" s="2" t="n"/>
       <c r="G743" s="9" t="n">
@@ -21103,14 +21103,14 @@
         </is>
       </c>
       <c r="C748" s="2" t="n"/>
-      <c r="D748" s="6" t="inlineStr">
-        <is>
-          <t>708-3-F: Introduction to Business - 3</t>
-        </is>
-      </c>
-      <c r="E748" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D748" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E748" s="6" t="inlineStr">
+        <is>
+          <t>708-2-S: Introduction to Business - 2</t>
         </is>
       </c>
       <c r="F748" s="2" t="n"/>
@@ -21171,9 +21171,9 @@
         </is>
       </c>
       <c r="C750" s="2" t="n"/>
-      <c r="D750" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D750" s="6" t="inlineStr">
+        <is>
+          <t>708-5-F: Introduction to Business - 5</t>
         </is>
       </c>
       <c r="E750" s="7" t="inlineStr">
@@ -21205,9 +21205,9 @@
         </is>
       </c>
       <c r="C751" s="2" t="n"/>
-      <c r="D751" s="6" t="inlineStr">
-        <is>
-          <t>708-5-F: Introduction to Business - 5</t>
+      <c r="D751" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="E751" s="7" t="inlineStr">
@@ -21273,14 +21273,14 @@
         </is>
       </c>
       <c r="C753" s="2" t="n"/>
-      <c r="D753" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E753" s="6" t="inlineStr">
-        <is>
-          <t>708-2-S: Introduction to Business - 2</t>
+      <c r="D753" s="6" t="inlineStr">
+        <is>
+          <t>708-3-F: Introduction to Business - 3</t>
+        </is>
+      </c>
+      <c r="E753" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F753" s="2" t="n"/>
@@ -21324,10 +21324,10 @@
       </c>
       <c r="C755" s="2" t="n"/>
       <c r="D755" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E755" s="7" t="n">
         <v>2</v>
-      </c>
-      <c r="E755" s="7" t="n">
-        <v>1</v>
       </c>
       <c r="F755" s="2" t="n"/>
       <c r="G755" s="7" t="n">
@@ -21405,9 +21405,9 @@
           <t>751-1-F: American Government &amp; Politics - 1</t>
         </is>
       </c>
-      <c r="E759" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="E759" s="6" t="inlineStr">
+        <is>
+          <t>741-2-S: Psychology - 2</t>
         </is>
       </c>
       <c r="F759" s="2" t="n"/>
@@ -21468,14 +21468,14 @@
         </is>
       </c>
       <c r="C761" s="2" t="n"/>
-      <c r="D761" s="6" t="inlineStr">
-        <is>
-          <t>710-3: World History - 3</t>
-        </is>
-      </c>
-      <c r="E761" s="6" t="inlineStr">
-        <is>
-          <t>710-3: World History - 3</t>
+      <c r="D761" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E761" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F761" s="2" t="n"/>
@@ -21504,12 +21504,12 @@
       <c r="C762" s="2" t="n"/>
       <c r="D762" s="6" t="inlineStr">
         <is>
-          <t>741-3-F: Psychology - 3</t>
-        </is>
-      </c>
-      <c r="E762" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+          <t>710-3: World History - 3</t>
+        </is>
+      </c>
+      <c r="E762" s="6" t="inlineStr">
+        <is>
+          <t>710-3: World History - 3</t>
         </is>
       </c>
       <c r="F762" s="2" t="n"/>
@@ -21536,14 +21536,14 @@
         </is>
       </c>
       <c r="C763" s="2" t="n"/>
-      <c r="D763" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E763" s="6" t="inlineStr">
-        <is>
-          <t>741-2-S: Psychology - 2</t>
+      <c r="D763" s="6" t="inlineStr">
+        <is>
+          <t>741-3-F: Psychology - 3</t>
+        </is>
+      </c>
+      <c r="E763" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F763" s="2" t="n"/>
@@ -21606,7 +21606,7 @@
       <c r="C765" s="2" t="n"/>
       <c r="D765" s="6" t="inlineStr">
         <is>
-          <t>710-1: World History - 1</t>
+          <t>710-1: World History - 1; 723-1-F: Introduction to Political Science - 1</t>
         </is>
       </c>
       <c r="E765" s="6" t="inlineStr">
@@ -21634,7 +21634,7 @@
       </c>
       <c r="C766" s="2" t="n"/>
       <c r="D766" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E766" s="9" t="n">
         <v>4</v>
@@ -21658,7 +21658,7 @@
         <v>4</v>
       </c>
       <c r="E767" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F767" s="2" t="n"/>
       <c r="G767" s="7" t="n">
@@ -21733,12 +21733,12 @@
       <c r="C771" s="2" t="n"/>
       <c r="D771" s="6" t="inlineStr">
         <is>
-          <t>110-4: Composition &amp; Literature - 4</t>
+          <t>110-3: Composition &amp; Literature - 3</t>
         </is>
       </c>
       <c r="E771" s="6" t="inlineStr">
         <is>
-          <t>110-4: Composition &amp; Literature - 4</t>
+          <t>110-3: Composition &amp; Literature - 3</t>
         </is>
       </c>
       <c r="F771" s="2" t="n"/>
@@ -21799,14 +21799,14 @@
         </is>
       </c>
       <c r="C773" s="2" t="n"/>
-      <c r="D773" s="6" t="inlineStr">
-        <is>
-          <t>110-2: Composition &amp; Literature - 2</t>
-        </is>
-      </c>
-      <c r="E773" s="6" t="inlineStr">
-        <is>
-          <t>110-2: Composition &amp; Literature - 2</t>
+      <c r="D773" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E773" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F773" s="2" t="n"/>
@@ -21835,12 +21835,12 @@
       <c r="C774" s="2" t="n"/>
       <c r="D774" s="6" t="inlineStr">
         <is>
-          <t>110-3: Composition &amp; Literature - 3</t>
+          <t>110-4: Composition &amp; Literature - 4</t>
         </is>
       </c>
       <c r="E774" s="6" t="inlineStr">
         <is>
-          <t>110-3: Composition &amp; Literature - 3</t>
+          <t>110-4: Composition &amp; Literature - 4</t>
         </is>
       </c>
       <c r="F774" s="2" t="n"/>
@@ -21867,14 +21867,14 @@
         </is>
       </c>
       <c r="C775" s="2" t="n"/>
-      <c r="D775" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E775" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D775" s="6" t="inlineStr">
+        <is>
+          <t>110-2: Composition &amp; Literature - 2</t>
+        </is>
+      </c>
+      <c r="E775" s="6" t="inlineStr">
+        <is>
+          <t>110-2: Composition &amp; Literature - 2</t>
         </is>
       </c>
       <c r="F775" s="2" t="n"/>
@@ -21901,14 +21901,14 @@
         </is>
       </c>
       <c r="C776" s="2" t="n"/>
-      <c r="D776" s="6" t="inlineStr">
-        <is>
-          <t>110-6: Composition &amp; Literature - 6</t>
-        </is>
-      </c>
-      <c r="E776" s="6" t="inlineStr">
-        <is>
-          <t>110-6: Composition &amp; Literature - 6</t>
+      <c r="D776" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E776" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F776" s="2" t="n"/>
@@ -21935,14 +21935,14 @@
         </is>
       </c>
       <c r="C777" s="2" t="n"/>
-      <c r="D777" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E777" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D777" s="6" t="inlineStr">
+        <is>
+          <t>110-6: Composition &amp; Literature - 6</t>
+        </is>
+      </c>
+      <c r="E777" s="6" t="inlineStr">
+        <is>
+          <t>110-6: Composition &amp; Literature - 6</t>
         </is>
       </c>
       <c r="F777" s="2" t="n"/>
@@ -21985,11 +21985,11 @@
         </is>
       </c>
       <c r="C779" s="2" t="n"/>
-      <c r="D779" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="E779" s="9" t="n">
-        <v>4</v>
+      <c r="D779" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E779" s="7" t="n">
+        <v>2</v>
       </c>
       <c r="F779" s="2" t="n"/>
       <c r="G779" s="9" t="n">
@@ -22356,7 +22356,7 @@
     <row r="794">
       <c r="A794" s="3" t="inlineStr">
         <is>
-          <t>ID: 105746</t>
+          <t>ID: 999999</t>
         </is>
       </c>
       <c r="D794" s="1" t="inlineStr">
@@ -22384,7 +22384,7 @@
     <row r="795">
       <c r="A795" s="4" t="inlineStr">
         <is>
-          <t>Tranate, John</t>
+          <t>TBD Theology, New</t>
         </is>
       </c>
       <c r="B795" s="5" t="inlineStr">
@@ -22395,30 +22395,30 @@
       <c r="C795" s="2" t="n"/>
       <c r="D795" s="6" t="inlineStr">
         <is>
-          <t>531-3: Physics H - 3</t>
+          <t>820-2: Theology 10 - 2</t>
         </is>
       </c>
       <c r="E795" s="6" t="inlineStr">
         <is>
-          <t>531-3: Physics H - 3</t>
+          <t>820-2: Theology 10 - 2</t>
         </is>
       </c>
       <c r="F795" s="2" t="n"/>
-      <c r="G795" s="6" t="inlineStr">
-        <is>
-          <t>557-1: AP Physics 1 - 1</t>
-        </is>
-      </c>
-      <c r="H795" s="6" t="inlineStr">
-        <is>
-          <t>557-1: AP Physics 1 - 1</t>
+      <c r="G795" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="H795" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
     </row>
     <row r="796">
       <c r="A796" s="4" t="inlineStr">
         <is>
-          <t>Tranate, John</t>
+          <t>TBD Theology, New</t>
         </is>
       </c>
       <c r="B796" s="5" t="inlineStr">
@@ -22427,32 +22427,32 @@
         </is>
       </c>
       <c r="C796" s="2" t="n"/>
-      <c r="D796" s="6" t="inlineStr">
-        <is>
-          <t>531-2: Physics H - 2</t>
-        </is>
-      </c>
-      <c r="E796" s="6" t="inlineStr">
-        <is>
-          <t>531-2: Physics H - 2</t>
+      <c r="D796" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E796" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F796" s="2" t="n"/>
-      <c r="G796" s="6" t="inlineStr">
-        <is>
-          <t>531-3: Physics H - 3</t>
-        </is>
-      </c>
-      <c r="H796" s="6" t="inlineStr">
-        <is>
-          <t>531-3: Physics H - 3</t>
+      <c r="G796" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="H796" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
     </row>
     <row r="797">
       <c r="A797" s="4" t="inlineStr">
         <is>
-          <t>Tranate, John</t>
+          <t>TBD Theology, New</t>
         </is>
       </c>
       <c r="B797" s="5" t="inlineStr">
@@ -22461,32 +22461,32 @@
         </is>
       </c>
       <c r="C797" s="2" t="n"/>
-      <c r="D797" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E797" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D797" s="6" t="inlineStr">
+        <is>
+          <t>810-3: Theology 9 - 3</t>
+        </is>
+      </c>
+      <c r="E797" s="6" t="inlineStr">
+        <is>
+          <t>810-3: Theology 9 - 3</t>
         </is>
       </c>
       <c r="F797" s="2" t="n"/>
-      <c r="G797" s="6" t="inlineStr">
-        <is>
-          <t>558-1: AP Physics C - 1</t>
-        </is>
-      </c>
-      <c r="H797" s="6" t="inlineStr">
-        <is>
-          <t>558-1: AP Physics C - 1</t>
+      <c r="G797" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="H797" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
     </row>
     <row r="798">
       <c r="A798" s="4" t="inlineStr">
         <is>
-          <t>Tranate, John</t>
+          <t>TBD Theology, New</t>
         </is>
       </c>
       <c r="B798" s="5" t="inlineStr">
@@ -22520,7 +22520,7 @@
     <row r="799">
       <c r="A799" s="4" t="inlineStr">
         <is>
-          <t>Tranate, John</t>
+          <t>TBD Theology, New</t>
         </is>
       </c>
       <c r="B799" s="5" t="inlineStr">
@@ -22531,30 +22531,30 @@
       <c r="C799" s="2" t="n"/>
       <c r="D799" s="6" t="inlineStr">
         <is>
-          <t>558-1: AP Physics C - 1</t>
+          <t>810-2: Theology 9 - 2</t>
         </is>
       </c>
       <c r="E799" s="6" t="inlineStr">
         <is>
-          <t>558-1: AP Physics C - 1</t>
+          <t>810-2: Theology 9 - 2</t>
         </is>
       </c>
       <c r="F799" s="2" t="n"/>
-      <c r="G799" s="6" t="inlineStr">
-        <is>
-          <t>531-1: Physics H - 1</t>
-        </is>
-      </c>
-      <c r="H799" s="6" t="inlineStr">
-        <is>
-          <t>531-1: Physics H - 1</t>
+      <c r="G799" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="H799" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
     </row>
     <row r="800">
       <c r="A800" s="4" t="inlineStr">
         <is>
-          <t>Tranate, John</t>
+          <t>TBD Theology, New</t>
         </is>
       </c>
       <c r="B800" s="5" t="inlineStr">
@@ -22565,30 +22565,30 @@
       <c r="C800" s="2" t="n"/>
       <c r="D800" s="6" t="inlineStr">
         <is>
-          <t>556-2: AP Physics - 2</t>
+          <t>820-1: Theology 10 - 1</t>
         </is>
       </c>
       <c r="E800" s="6" t="inlineStr">
         <is>
-          <t>556-2: AP Physics - 2</t>
+          <t>820-1: Theology 10 - 1</t>
         </is>
       </c>
       <c r="F800" s="2" t="n"/>
-      <c r="G800" s="6" t="inlineStr">
-        <is>
-          <t>531-2: Physics H - 2</t>
-        </is>
-      </c>
-      <c r="H800" s="6" t="inlineStr">
-        <is>
-          <t>531-2: Physics H - 2</t>
+      <c r="G800" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="H800" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
     </row>
     <row r="801">
       <c r="A801" s="4" t="inlineStr">
         <is>
-          <t>Tranate, John</t>
+          <t>TBD Theology, New</t>
         </is>
       </c>
       <c r="B801" s="5" t="inlineStr">
@@ -22599,12 +22599,12 @@
       <c r="C801" s="2" t="n"/>
       <c r="D801" s="6" t="inlineStr">
         <is>
-          <t>556-1: AP Physics - 1</t>
+          <t>810-1: Theology 9 - 1</t>
         </is>
       </c>
       <c r="E801" s="6" t="inlineStr">
         <is>
-          <t>556-1: AP Physics - 1</t>
+          <t>810-1: Theology 9 - 1</t>
         </is>
       </c>
       <c r="F801" s="2" t="n"/>
@@ -22634,10 +22634,10 @@
       </c>
       <c r="F802" s="2" t="n"/>
       <c r="G802" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H802" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="803">
@@ -22655,10 +22655,10 @@
       </c>
       <c r="F803" s="2" t="n"/>
       <c r="G803" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H803" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="805">
@@ -22687,7 +22687,7 @@
     <row r="806">
       <c r="A806" s="3" t="inlineStr">
         <is>
-          <t>ID: 106765</t>
+          <t>ID: 105746</t>
         </is>
       </c>
       <c r="D806" s="1" t="inlineStr">
@@ -22715,7 +22715,7 @@
     <row r="807">
       <c r="A807" s="4" t="inlineStr">
         <is>
-          <t>Tuesta, David</t>
+          <t>Tranate, John</t>
         </is>
       </c>
       <c r="B807" s="5" t="inlineStr">
@@ -22726,30 +22726,30 @@
       <c r="C807" s="2" t="n"/>
       <c r="D807" s="6" t="inlineStr">
         <is>
-          <t>310-3: Spanish I - 3</t>
+          <t>531-3: Physics H - 3</t>
         </is>
       </c>
       <c r="E807" s="6" t="inlineStr">
         <is>
-          <t>310-3: Spanish I - 3</t>
+          <t>531-3: Physics H - 3</t>
         </is>
       </c>
       <c r="F807" s="2" t="n"/>
       <c r="G807" s="6" t="inlineStr">
         <is>
-          <t>310-1: Spanish I - 1</t>
+          <t>557-1: AP Physics 1 - 1</t>
         </is>
       </c>
       <c r="H807" s="6" t="inlineStr">
         <is>
-          <t>310-1: Spanish I - 1</t>
+          <t>557-1: AP Physics 1 - 1</t>
         </is>
       </c>
     </row>
     <row r="808">
       <c r="A808" s="4" t="inlineStr">
         <is>
-          <t>Tuesta, David</t>
+          <t>Tranate, John</t>
         </is>
       </c>
       <c r="B808" s="5" t="inlineStr">
@@ -22760,30 +22760,30 @@
       <c r="C808" s="2" t="n"/>
       <c r="D808" s="6" t="inlineStr">
         <is>
-          <t>310-5: Spanish I - 5</t>
+          <t>531-2: Physics H - 2</t>
         </is>
       </c>
       <c r="E808" s="6" t="inlineStr">
         <is>
-          <t>310-5: Spanish I - 5</t>
+          <t>531-2: Physics H - 2</t>
         </is>
       </c>
       <c r="F808" s="2" t="n"/>
-      <c r="G808" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="H808" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="G808" s="6" t="inlineStr">
+        <is>
+          <t>531-3: Physics H - 3</t>
+        </is>
+      </c>
+      <c r="H808" s="6" t="inlineStr">
+        <is>
+          <t>531-3: Physics H - 3</t>
         </is>
       </c>
     </row>
     <row r="809">
       <c r="A809" s="4" t="inlineStr">
         <is>
-          <t>Tuesta, David</t>
+          <t>Tranate, John</t>
         </is>
       </c>
       <c r="B809" s="5" t="inlineStr">
@@ -22792,32 +22792,32 @@
         </is>
       </c>
       <c r="C809" s="2" t="n"/>
-      <c r="D809" s="6" t="inlineStr">
-        <is>
-          <t>310-2: Spanish I - 2</t>
-        </is>
-      </c>
-      <c r="E809" s="6" t="inlineStr">
-        <is>
-          <t>310-2: Spanish I - 2</t>
+      <c r="D809" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E809" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F809" s="2" t="n"/>
       <c r="G809" s="6" t="inlineStr">
         <is>
-          <t>310-2: Spanish I - 2</t>
+          <t>558-1: AP Physics C - 1</t>
         </is>
       </c>
       <c r="H809" s="6" t="inlineStr">
         <is>
-          <t>310-2: Spanish I - 2</t>
+          <t>558-1: AP Physics C - 1</t>
         </is>
       </c>
     </row>
     <row r="810">
       <c r="A810" s="4" t="inlineStr">
         <is>
-          <t>Tuesta, David</t>
+          <t>Tranate, John</t>
         </is>
       </c>
       <c r="B810" s="5" t="inlineStr">
@@ -22828,30 +22828,30 @@
       <c r="C810" s="2" t="n"/>
       <c r="D810" s="6" t="inlineStr">
         <is>
-          <t>310-4: Spanish I - 4</t>
+          <t>557-1: AP Physics 1 - 1</t>
         </is>
       </c>
       <c r="E810" s="6" t="inlineStr">
         <is>
-          <t>310-4: Spanish I - 4</t>
+          <t>557-1: AP Physics 1 - 1</t>
         </is>
       </c>
       <c r="F810" s="2" t="n"/>
-      <c r="G810" s="6" t="inlineStr">
-        <is>
-          <t>310-3: Spanish I - 3</t>
-        </is>
-      </c>
-      <c r="H810" s="6" t="inlineStr">
-        <is>
-          <t>310-3: Spanish I - 3</t>
+      <c r="G810" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="H810" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
     </row>
     <row r="811">
       <c r="A811" s="4" t="inlineStr">
         <is>
-          <t>Tuesta, David</t>
+          <t>Tranate, John</t>
         </is>
       </c>
       <c r="B811" s="5" t="inlineStr">
@@ -22862,30 +22862,30 @@
       <c r="C811" s="2" t="n"/>
       <c r="D811" s="6" t="inlineStr">
         <is>
-          <t>310-1: Spanish I - 1</t>
+          <t>558-1: AP Physics C - 1</t>
         </is>
       </c>
       <c r="E811" s="6" t="inlineStr">
         <is>
-          <t>310-1: Spanish I - 1</t>
+          <t>558-1: AP Physics C - 1</t>
         </is>
       </c>
       <c r="F811" s="2" t="n"/>
       <c r="G811" s="6" t="inlineStr">
         <is>
-          <t>310-4: Spanish I - 4</t>
+          <t>531-1: Physics H - 1</t>
         </is>
       </c>
       <c r="H811" s="6" t="inlineStr">
         <is>
-          <t>310-4: Spanish I - 4</t>
+          <t>531-1: Physics H - 1</t>
         </is>
       </c>
     </row>
     <row r="812">
       <c r="A812" s="4" t="inlineStr">
         <is>
-          <t>Tuesta, David</t>
+          <t>Tranate, John</t>
         </is>
       </c>
       <c r="B812" s="5" t="inlineStr">
@@ -22905,21 +22905,21 @@
         </is>
       </c>
       <c r="F812" s="2" t="n"/>
-      <c r="G812" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="H812" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="G812" s="6" t="inlineStr">
+        <is>
+          <t>531-2: Physics H - 2</t>
+        </is>
+      </c>
+      <c r="H812" s="6" t="inlineStr">
+        <is>
+          <t>531-2: Physics H - 2</t>
         </is>
       </c>
     </row>
     <row r="813">
       <c r="A813" s="4" t="inlineStr">
         <is>
-          <t>Tuesta, David</t>
+          <t>Tranate, John</t>
         </is>
       </c>
       <c r="B813" s="5" t="inlineStr">
@@ -22930,23 +22930,23 @@
       <c r="C813" s="2" t="n"/>
       <c r="D813" s="6" t="inlineStr">
         <is>
-          <t>310-6: Spanish I - 6</t>
+          <t>557-2: AP Physics 1 - 2</t>
         </is>
       </c>
       <c r="E813" s="6" t="inlineStr">
         <is>
-          <t>310-6: Spanish I - 6</t>
+          <t>557-2: AP Physics 1 - 2</t>
         </is>
       </c>
       <c r="F813" s="2" t="n"/>
-      <c r="G813" s="6" t="inlineStr">
-        <is>
-          <t>310-6: Spanish I - 6</t>
-        </is>
-      </c>
-      <c r="H813" s="6" t="inlineStr">
-        <is>
-          <t>310-6: Spanish I - 6</t>
+      <c r="G813" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="H813" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
     </row>
@@ -22958,10 +22958,10 @@
       </c>
       <c r="C814" s="2" t="n"/>
       <c r="D814" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E814" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F814" s="2" t="n"/>
       <c r="G814" s="9" t="n">
@@ -22978,11 +22978,11 @@
         </is>
       </c>
       <c r="C815" s="2" t="n"/>
-      <c r="D815" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="E815" s="9" t="n">
-        <v>5</v>
+      <c r="D815" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E815" s="7" t="n">
+        <v>2</v>
       </c>
       <c r="F815" s="2" t="n"/>
       <c r="G815" s="7" t="n">
@@ -23018,7 +23018,7 @@
     <row r="818">
       <c r="A818" s="3" t="inlineStr">
         <is>
-          <t>ID: 105768</t>
+          <t>ID: 106765</t>
         </is>
       </c>
       <c r="D818" s="1" t="inlineStr">
@@ -23046,7 +23046,7 @@
     <row r="819">
       <c r="A819" s="4" t="inlineStr">
         <is>
-          <t>Umbrino, Philip</t>
+          <t>Tuesta, David</t>
         </is>
       </c>
       <c r="B819" s="5" t="inlineStr">
@@ -23057,30 +23057,30 @@
       <c r="C819" s="2" t="n"/>
       <c r="D819" s="6" t="inlineStr">
         <is>
-          <t>145-1-F: Journalism - 1</t>
-        </is>
-      </c>
-      <c r="E819" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+          <t>310-3: Spanish I - 3</t>
+        </is>
+      </c>
+      <c r="E819" s="6" t="inlineStr">
+        <is>
+          <t>310-3: Spanish I - 3</t>
         </is>
       </c>
       <c r="F819" s="2" t="n"/>
-      <c r="G819" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="H819" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="G819" s="6" t="inlineStr">
+        <is>
+          <t>310-1: Spanish I - 1</t>
+        </is>
+      </c>
+      <c r="H819" s="6" t="inlineStr">
+        <is>
+          <t>310-1: Spanish I - 1</t>
         </is>
       </c>
     </row>
     <row r="820">
       <c r="A820" s="4" t="inlineStr">
         <is>
-          <t>Umbrino, Philip</t>
+          <t>Tuesta, David</t>
         </is>
       </c>
       <c r="B820" s="5" t="inlineStr">
@@ -23091,12 +23091,12 @@
       <c r="C820" s="2" t="n"/>
       <c r="D820" s="6" t="inlineStr">
         <is>
-          <t>132-1: British Literature - 1</t>
+          <t>310-5: Spanish I - 5</t>
         </is>
       </c>
       <c r="E820" s="6" t="inlineStr">
         <is>
-          <t>132-1: British Literature - 1</t>
+          <t>310-5: Spanish I - 5</t>
         </is>
       </c>
       <c r="F820" s="2" t="n"/>
@@ -23114,7 +23114,7 @@
     <row r="821">
       <c r="A821" s="4" t="inlineStr">
         <is>
-          <t>Umbrino, Philip</t>
+          <t>Tuesta, David</t>
         </is>
       </c>
       <c r="B821" s="5" t="inlineStr">
@@ -23125,30 +23125,30 @@
       <c r="C821" s="2" t="n"/>
       <c r="D821" s="6" t="inlineStr">
         <is>
-          <t>143-1-F: Creative Writing - 1</t>
-        </is>
-      </c>
-      <c r="E821" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+          <t>310-2: Spanish I - 2</t>
+        </is>
+      </c>
+      <c r="E821" s="6" t="inlineStr">
+        <is>
+          <t>310-2: Spanish I - 2</t>
         </is>
       </c>
       <c r="F821" s="2" t="n"/>
-      <c r="G821" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="H821" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="G821" s="6" t="inlineStr">
+        <is>
+          <t>310-2: Spanish I - 2</t>
+        </is>
+      </c>
+      <c r="H821" s="6" t="inlineStr">
+        <is>
+          <t>310-2: Spanish I - 2</t>
         </is>
       </c>
     </row>
     <row r="822">
       <c r="A822" s="4" t="inlineStr">
         <is>
-          <t>Umbrino, Philip</t>
+          <t>Tuesta, David</t>
         </is>
       </c>
       <c r="B822" s="5" t="inlineStr">
@@ -23159,30 +23159,30 @@
       <c r="C822" s="2" t="n"/>
       <c r="D822" s="6" t="inlineStr">
         <is>
-          <t>130-5: British Literature - 5</t>
+          <t>310-4: Spanish I - 4</t>
         </is>
       </c>
       <c r="E822" s="6" t="inlineStr">
         <is>
-          <t>130-5: British Literature - 5</t>
+          <t>310-4: Spanish I - 4</t>
         </is>
       </c>
       <c r="F822" s="2" t="n"/>
-      <c r="G822" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="H822" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="G822" s="6" t="inlineStr">
+        <is>
+          <t>310-3: Spanish I - 3</t>
+        </is>
+      </c>
+      <c r="H822" s="6" t="inlineStr">
+        <is>
+          <t>310-3: Spanish I - 3</t>
         </is>
       </c>
     </row>
     <row r="823">
       <c r="A823" s="4" t="inlineStr">
         <is>
-          <t>Umbrino, Philip</t>
+          <t>Tuesta, David</t>
         </is>
       </c>
       <c r="B823" s="5" t="inlineStr">
@@ -23193,30 +23193,30 @@
       <c r="C823" s="2" t="n"/>
       <c r="D823" s="6" t="inlineStr">
         <is>
-          <t>130-3: British Literature - 3</t>
+          <t>310-1: Spanish I - 1</t>
         </is>
       </c>
       <c r="E823" s="6" t="inlineStr">
         <is>
-          <t>130-3: British Literature - 3</t>
+          <t>310-1: Spanish I - 1</t>
         </is>
       </c>
       <c r="F823" s="2" t="n"/>
-      <c r="G823" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="H823" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="G823" s="6" t="inlineStr">
+        <is>
+          <t>310-4: Spanish I - 4</t>
+        </is>
+      </c>
+      <c r="H823" s="6" t="inlineStr">
+        <is>
+          <t>310-4: Spanish I - 4</t>
         </is>
       </c>
     </row>
     <row r="824">
       <c r="A824" s="4" t="inlineStr">
         <is>
-          <t>Umbrino, Philip</t>
+          <t>Tuesta, David</t>
         </is>
       </c>
       <c r="B824" s="5" t="inlineStr">
@@ -23250,7 +23250,7 @@
     <row r="825">
       <c r="A825" s="4" t="inlineStr">
         <is>
-          <t>Umbrino, Philip</t>
+          <t>Tuesta, David</t>
         </is>
       </c>
       <c r="B825" s="5" t="inlineStr">
@@ -23261,23 +23261,23 @@
       <c r="C825" s="2" t="n"/>
       <c r="D825" s="6" t="inlineStr">
         <is>
-          <t>130-4: British Literature - 4</t>
+          <t>310-6: Spanish I - 6</t>
         </is>
       </c>
       <c r="E825" s="6" t="inlineStr">
         <is>
-          <t>130-4: British Literature - 4</t>
+          <t>310-6: Spanish I - 6</t>
         </is>
       </c>
       <c r="F825" s="2" t="n"/>
-      <c r="G825" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="H825" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="G825" s="6" t="inlineStr">
+        <is>
+          <t>310-6: Spanish I - 6</t>
+        </is>
+      </c>
+      <c r="H825" s="6" t="inlineStr">
+        <is>
+          <t>310-6: Spanish I - 6</t>
         </is>
       </c>
     </row>
@@ -23292,14 +23292,14 @@
         <v>6</v>
       </c>
       <c r="E826" s="9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F826" s="2" t="n"/>
       <c r="G826" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H826" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="827">
@@ -23312,15 +23312,15 @@
       <c r="D827" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="E827" s="7" t="n">
-        <v>2</v>
+      <c r="E827" s="9" t="n">
+        <v>5</v>
       </c>
       <c r="F827" s="2" t="n"/>
       <c r="G827" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H827" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="829">
@@ -23349,7 +23349,7 @@
     <row r="830">
       <c r="A830" s="3" t="inlineStr">
         <is>
-          <t>ID: 105812</t>
+          <t>ID: 105768</t>
         </is>
       </c>
       <c r="D830" s="1" t="inlineStr">
@@ -23377,7 +23377,7 @@
     <row r="831">
       <c r="A831" s="4" t="inlineStr">
         <is>
-          <t>Walters, Brooke</t>
+          <t>Umbrino, Philip</t>
         </is>
       </c>
       <c r="B831" s="5" t="inlineStr">
@@ -23386,9 +23386,9 @@
         </is>
       </c>
       <c r="C831" s="2" t="n"/>
-      <c r="D831" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D831" s="6" t="inlineStr">
+        <is>
+          <t>145-1-F: Journalism - 1</t>
         </is>
       </c>
       <c r="E831" s="7" t="inlineStr">
@@ -23411,7 +23411,7 @@
     <row r="832">
       <c r="A832" s="4" t="inlineStr">
         <is>
-          <t>Walters, Brooke</t>
+          <t>Umbrino, Philip</t>
         </is>
       </c>
       <c r="B832" s="5" t="inlineStr">
@@ -23431,9 +23431,9 @@
         </is>
       </c>
       <c r="F832" s="2" t="n"/>
-      <c r="G832" s="6" t="inlineStr">
-        <is>
-          <t>144-1-F: Public Speaking - 1</t>
+      <c r="G832" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="H832" s="7" t="inlineStr">
@@ -23445,7 +23445,7 @@
     <row r="833">
       <c r="A833" s="4" t="inlineStr">
         <is>
-          <t>Walters, Brooke</t>
+          <t>Umbrino, Philip</t>
         </is>
       </c>
       <c r="B833" s="5" t="inlineStr">
@@ -23454,9 +23454,9 @@
         </is>
       </c>
       <c r="C833" s="2" t="n"/>
-      <c r="D833" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D833" s="6" t="inlineStr">
+        <is>
+          <t>143-1-F: Creative Writing - 1</t>
         </is>
       </c>
       <c r="E833" s="7" t="inlineStr">
@@ -23470,16 +23470,16 @@
           <t>UNASSIGNED</t>
         </is>
       </c>
-      <c r="H833" s="6" t="inlineStr">
-        <is>
-          <t>144-1-S: Public Speaking - 1</t>
+      <c r="H833" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
     </row>
     <row r="834">
       <c r="A834" s="4" t="inlineStr">
         <is>
-          <t>Walters, Brooke</t>
+          <t>Umbrino, Philip</t>
         </is>
       </c>
       <c r="B834" s="5" t="inlineStr">
@@ -23488,20 +23488,20 @@
         </is>
       </c>
       <c r="C834" s="2" t="n"/>
-      <c r="D834" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E834" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D834" s="6" t="inlineStr">
+        <is>
+          <t>130-5: British Literature - 5</t>
+        </is>
+      </c>
+      <c r="E834" s="6" t="inlineStr">
+        <is>
+          <t>130-5: British Literature - 5</t>
         </is>
       </c>
       <c r="F834" s="2" t="n"/>
-      <c r="G834" s="6" t="inlineStr">
-        <is>
-          <t>144-2-F: Public Speaking - 2</t>
+      <c r="G834" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="H834" s="7" t="inlineStr">
@@ -23513,7 +23513,7 @@
     <row r="835">
       <c r="A835" s="4" t="inlineStr">
         <is>
-          <t>Walters, Brooke</t>
+          <t>Umbrino, Philip</t>
         </is>
       </c>
       <c r="B835" s="5" t="inlineStr">
@@ -23522,14 +23522,14 @@
         </is>
       </c>
       <c r="C835" s="2" t="n"/>
-      <c r="D835" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E835" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D835" s="6" t="inlineStr">
+        <is>
+          <t>132-1: British Literature - 1</t>
+        </is>
+      </c>
+      <c r="E835" s="6" t="inlineStr">
+        <is>
+          <t>132-1: British Literature - 1</t>
         </is>
       </c>
       <c r="F835" s="2" t="n"/>
@@ -23547,7 +23547,7 @@
     <row r="836">
       <c r="A836" s="4" t="inlineStr">
         <is>
-          <t>Walters, Brooke</t>
+          <t>Umbrino, Philip</t>
         </is>
       </c>
       <c r="B836" s="5" t="inlineStr">
@@ -23556,14 +23556,14 @@
         </is>
       </c>
       <c r="C836" s="2" t="n"/>
-      <c r="D836" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E836" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D836" s="6" t="inlineStr">
+        <is>
+          <t>130-3: British Literature - 3</t>
+        </is>
+      </c>
+      <c r="E836" s="6" t="inlineStr">
+        <is>
+          <t>130-3: British Literature - 3</t>
         </is>
       </c>
       <c r="F836" s="2" t="n"/>
@@ -23581,7 +23581,7 @@
     <row r="837">
       <c r="A837" s="4" t="inlineStr">
         <is>
-          <t>Walters, Brooke</t>
+          <t>Umbrino, Philip</t>
         </is>
       </c>
       <c r="B837" s="5" t="inlineStr">
@@ -23590,14 +23590,14 @@
         </is>
       </c>
       <c r="C837" s="2" t="n"/>
-      <c r="D837" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E837" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D837" s="6" t="inlineStr">
+        <is>
+          <t>130-4: British Literature - 4</t>
+        </is>
+      </c>
+      <c r="E837" s="6" t="inlineStr">
+        <is>
+          <t>130-4: British Literature - 4</t>
         </is>
       </c>
       <c r="F837" s="2" t="n"/>
@@ -23606,9 +23606,9 @@
           <t>UNASSIGNED</t>
         </is>
       </c>
-      <c r="H837" s="6" t="inlineStr">
-        <is>
-          <t>228-1 S: Adv Theater Production - 1</t>
+      <c r="H837" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
     </row>
@@ -23620,17 +23620,17 @@
       </c>
       <c r="C838" s="2" t="n"/>
       <c r="D838" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E838" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F838" s="2" t="n"/>
       <c r="G838" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H838" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="839">
@@ -23640,18 +23640,18 @@
         </is>
       </c>
       <c r="C839" s="2" t="n"/>
-      <c r="D839" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E839" s="7" t="n">
-        <v>0</v>
+      <c r="D839" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E839" s="9" t="n">
+        <v>4</v>
       </c>
       <c r="F839" s="2" t="n"/>
       <c r="G839" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H839" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="841">
@@ -23680,7 +23680,7 @@
     <row r="842">
       <c r="A842" s="3" t="inlineStr">
         <is>
-          <t>ID: 106623</t>
+          <t>ID: 105812</t>
         </is>
       </c>
       <c r="D842" s="1" t="inlineStr">
@@ -23708,7 +23708,7 @@
     <row r="843">
       <c r="A843" s="4" t="inlineStr">
         <is>
-          <t>Willi, Mary</t>
+          <t>Walters, Brooke</t>
         </is>
       </c>
       <c r="B843" s="5" t="inlineStr">
@@ -23717,32 +23717,32 @@
         </is>
       </c>
       <c r="C843" s="2" t="n"/>
-      <c r="D843" s="6" t="inlineStr">
-        <is>
-          <t>410-4: Algebra I - 4</t>
-        </is>
-      </c>
-      <c r="E843" s="6" t="inlineStr">
-        <is>
-          <t>410-4: Algebra I - 4</t>
+      <c r="D843" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E843" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F843" s="2" t="n"/>
-      <c r="G843" s="6" t="inlineStr">
-        <is>
-          <t>420-1: Geometry - 1</t>
-        </is>
-      </c>
-      <c r="H843" s="6" t="inlineStr">
-        <is>
-          <t>420-1: Geometry - 1</t>
+      <c r="G843" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="H843" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
     </row>
     <row r="844">
       <c r="A844" s="4" t="inlineStr">
         <is>
-          <t>Willi, Mary</t>
+          <t>Walters, Brooke</t>
         </is>
       </c>
       <c r="B844" s="5" t="inlineStr">
@@ -23751,20 +23751,20 @@
         </is>
       </c>
       <c r="C844" s="2" t="n"/>
-      <c r="D844" s="6" t="inlineStr">
-        <is>
-          <t>420-5: Geometry - 5</t>
-        </is>
-      </c>
-      <c r="E844" s="6" t="inlineStr">
-        <is>
-          <t>420-5: Geometry - 5</t>
+      <c r="D844" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E844" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F844" s="2" t="n"/>
-      <c r="G844" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="G844" s="6" t="inlineStr">
+        <is>
+          <t>144-1-F: Public Speaking - 1</t>
         </is>
       </c>
       <c r="H844" s="7" t="inlineStr">
@@ -23776,7 +23776,7 @@
     <row r="845">
       <c r="A845" s="4" t="inlineStr">
         <is>
-          <t>Willi, Mary</t>
+          <t>Walters, Brooke</t>
         </is>
       </c>
       <c r="B845" s="5" t="inlineStr">
@@ -23785,32 +23785,32 @@
         </is>
       </c>
       <c r="C845" s="2" t="n"/>
-      <c r="D845" s="6" t="inlineStr">
-        <is>
-          <t>410-5: Algebra I - 5</t>
-        </is>
-      </c>
-      <c r="E845" s="6" t="inlineStr">
-        <is>
-          <t>410-5: Algebra I - 5</t>
+      <c r="D845" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E845" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F845" s="2" t="n"/>
-      <c r="G845" s="6" t="inlineStr">
-        <is>
-          <t>410-3: Algebra I - 3</t>
+      <c r="G845" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="H845" s="6" t="inlineStr">
         <is>
-          <t>410-3: Algebra I - 3</t>
+          <t>144-1-S: Public Speaking - 1</t>
         </is>
       </c>
     </row>
     <row r="846">
       <c r="A846" s="4" t="inlineStr">
         <is>
-          <t>Willi, Mary</t>
+          <t>Walters, Brooke</t>
         </is>
       </c>
       <c r="B846" s="5" t="inlineStr">
@@ -23832,19 +23832,19 @@
       <c r="F846" s="2" t="n"/>
       <c r="G846" s="6" t="inlineStr">
         <is>
-          <t>420-3: Geometry - 3</t>
-        </is>
-      </c>
-      <c r="H846" s="6" t="inlineStr">
-        <is>
-          <t>420-3: Geometry - 3</t>
+          <t>144-2-F: Public Speaking - 2</t>
+        </is>
+      </c>
+      <c r="H846" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
     </row>
     <row r="847">
       <c r="A847" s="4" t="inlineStr">
         <is>
-          <t>Willi, Mary</t>
+          <t>Walters, Brooke</t>
         </is>
       </c>
       <c r="B847" s="5" t="inlineStr">
@@ -23864,21 +23864,21 @@
         </is>
       </c>
       <c r="F847" s="2" t="n"/>
-      <c r="G847" s="6" t="inlineStr">
-        <is>
-          <t>410-5: Algebra I - 5</t>
-        </is>
-      </c>
-      <c r="H847" s="6" t="inlineStr">
-        <is>
-          <t>410-5: Algebra I - 5</t>
+      <c r="G847" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="H847" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
     </row>
     <row r="848">
       <c r="A848" s="4" t="inlineStr">
         <is>
-          <t>Willi, Mary</t>
+          <t>Walters, Brooke</t>
         </is>
       </c>
       <c r="B848" s="5" t="inlineStr">
@@ -23887,14 +23887,14 @@
         </is>
       </c>
       <c r="C848" s="2" t="n"/>
-      <c r="D848" s="6" t="inlineStr">
-        <is>
-          <t>411-1: Algebra I H - 1</t>
-        </is>
-      </c>
-      <c r="E848" s="6" t="inlineStr">
-        <is>
-          <t>411-1: Algebra I H - 1</t>
+      <c r="D848" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E848" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F848" s="2" t="n"/>
@@ -23912,7 +23912,7 @@
     <row r="849">
       <c r="A849" s="4" t="inlineStr">
         <is>
-          <t>Willi, Mary</t>
+          <t>Walters, Brooke</t>
         </is>
       </c>
       <c r="B849" s="5" t="inlineStr">
@@ -23921,25 +23921,25 @@
         </is>
       </c>
       <c r="C849" s="2" t="n"/>
-      <c r="D849" s="6" t="inlineStr">
-        <is>
-          <t>410-6: Algebra I - 6</t>
-        </is>
-      </c>
-      <c r="E849" s="6" t="inlineStr">
-        <is>
-          <t>410-6: Algebra I - 6</t>
+      <c r="D849" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E849" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F849" s="2" t="n"/>
-      <c r="G849" s="6" t="inlineStr">
-        <is>
-          <t>410-4: Algebra I - 4</t>
+      <c r="G849" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="H849" s="6" t="inlineStr">
         <is>
-          <t>410-4: Algebra I - 4</t>
+          <t>228-1 S: Adv Theater Production - 1</t>
         </is>
       </c>
     </row>
@@ -23951,17 +23951,17 @@
       </c>
       <c r="C850" s="2" t="n"/>
       <c r="D850" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E850" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F850" s="2" t="n"/>
       <c r="G850" s="9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H850" s="9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="851">
@@ -23972,17 +23972,17 @@
       </c>
       <c r="C851" s="2" t="n"/>
       <c r="D851" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E851" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F851" s="2" t="n"/>
       <c r="G851" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H851" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="853">
@@ -24011,7 +24011,7 @@
     <row r="854">
       <c r="A854" s="3" t="inlineStr">
         <is>
-          <t>ID: 105883</t>
+          <t>ID: 106623</t>
         </is>
       </c>
       <c r="D854" s="1" t="inlineStr">
@@ -24039,7 +24039,7 @@
     <row r="855">
       <c r="A855" s="4" t="inlineStr">
         <is>
-          <t>Winters, Jack</t>
+          <t>Willi, Mary</t>
         </is>
       </c>
       <c r="B855" s="5" t="inlineStr">
@@ -24050,30 +24050,30 @@
       <c r="C855" s="2" t="n"/>
       <c r="D855" s="6" t="inlineStr">
         <is>
-          <t>730-3: U.S. History II - 3</t>
+          <t>410-4: Algebra I - 4</t>
         </is>
       </c>
       <c r="E855" s="6" t="inlineStr">
         <is>
-          <t>730-3: U.S. History II - 3</t>
+          <t>410-4: Algebra I - 4</t>
         </is>
       </c>
       <c r="F855" s="2" t="n"/>
       <c r="G855" s="6" t="inlineStr">
         <is>
-          <t>756 -1-F: Introduction to Law-1</t>
-        </is>
-      </c>
-      <c r="H855" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+          <t>420-1: Geometry - 1</t>
+        </is>
+      </c>
+      <c r="H855" s="6" t="inlineStr">
+        <is>
+          <t>420-1: Geometry - 1</t>
         </is>
       </c>
     </row>
     <row r="856">
       <c r="A856" s="4" t="inlineStr">
         <is>
-          <t>Winters, Jack</t>
+          <t>Willi, Mary</t>
         </is>
       </c>
       <c r="B856" s="5" t="inlineStr">
@@ -24084,30 +24084,30 @@
       <c r="C856" s="2" t="n"/>
       <c r="D856" s="6" t="inlineStr">
         <is>
-          <t>710-5: World History - 5</t>
+          <t>420-5: Geometry - 5</t>
         </is>
       </c>
       <c r="E856" s="6" t="inlineStr">
         <is>
-          <t>710-5: World History - 5</t>
+          <t>420-5: Geometry - 5</t>
         </is>
       </c>
       <c r="F856" s="2" t="n"/>
-      <c r="G856" s="6" t="inlineStr">
-        <is>
-          <t>710-1: World History - 1</t>
-        </is>
-      </c>
-      <c r="H856" s="6" t="inlineStr">
-        <is>
-          <t>710-1: World History - 1</t>
+      <c r="G856" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="H856" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
     </row>
     <row r="857">
       <c r="A857" s="4" t="inlineStr">
         <is>
-          <t>Winters, Jack</t>
+          <t>Willi, Mary</t>
         </is>
       </c>
       <c r="B857" s="5" t="inlineStr">
@@ -24118,30 +24118,30 @@
       <c r="C857" s="2" t="n"/>
       <c r="D857" s="6" t="inlineStr">
         <is>
-          <t>756-1-F: Introduction to Law - 1</t>
-        </is>
-      </c>
-      <c r="E857" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+          <t>410-5: Algebra I - 5</t>
+        </is>
+      </c>
+      <c r="E857" s="6" t="inlineStr">
+        <is>
+          <t>410-5: Algebra I - 5</t>
         </is>
       </c>
       <c r="F857" s="2" t="n"/>
       <c r="G857" s="6" t="inlineStr">
         <is>
-          <t>710-2: World History - 2</t>
+          <t>410-3: Algebra I - 3</t>
         </is>
       </c>
       <c r="H857" s="6" t="inlineStr">
         <is>
-          <t>710-2: World History - 2</t>
+          <t>410-3: Algebra I - 3</t>
         </is>
       </c>
     </row>
     <row r="858">
       <c r="A858" s="4" t="inlineStr">
         <is>
-          <t>Winters, Jack</t>
+          <t>Willi, Mary</t>
         </is>
       </c>
       <c r="B858" s="5" t="inlineStr">
@@ -24150,32 +24150,32 @@
         </is>
       </c>
       <c r="C858" s="2" t="n"/>
-      <c r="D858" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E858" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D858" s="6" t="inlineStr">
+        <is>
+          <t>410-6: Algebra I - 6</t>
+        </is>
+      </c>
+      <c r="E858" s="6" t="inlineStr">
+        <is>
+          <t>410-6: Algebra I - 6</t>
         </is>
       </c>
       <c r="F858" s="2" t="n"/>
       <c r="G858" s="6" t="inlineStr">
         <is>
-          <t>710-3: World History - 3</t>
+          <t>420-3: Geometry - 3</t>
         </is>
       </c>
       <c r="H858" s="6" t="inlineStr">
         <is>
-          <t>710-3: World History - 3</t>
+          <t>420-3: Geometry - 3</t>
         </is>
       </c>
     </row>
     <row r="859">
       <c r="A859" s="4" t="inlineStr">
         <is>
-          <t>Winters, Jack</t>
+          <t>Willi, Mary</t>
         </is>
       </c>
       <c r="B859" s="5" t="inlineStr">
@@ -24184,32 +24184,32 @@
         </is>
       </c>
       <c r="C859" s="2" t="n"/>
-      <c r="D859" s="6" t="inlineStr">
-        <is>
-          <t>710-4: World History - 4</t>
-        </is>
-      </c>
-      <c r="E859" s="6" t="inlineStr">
-        <is>
-          <t>710-4: World History - 4</t>
+      <c r="D859" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E859" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F859" s="2" t="n"/>
       <c r="G859" s="6" t="inlineStr">
         <is>
-          <t>710-4: World History - 4</t>
+          <t>410-5: Algebra I - 5</t>
         </is>
       </c>
       <c r="H859" s="6" t="inlineStr">
         <is>
-          <t>710-4: World History - 4</t>
+          <t>410-5: Algebra I - 5</t>
         </is>
       </c>
     </row>
     <row r="860">
       <c r="A860" s="4" t="inlineStr">
         <is>
-          <t>Winters, Jack</t>
+          <t>Willi, Mary</t>
         </is>
       </c>
       <c r="B860" s="5" t="inlineStr">
@@ -24220,12 +24220,12 @@
       <c r="C860" s="2" t="n"/>
       <c r="D860" s="6" t="inlineStr">
         <is>
-          <t>710-6: World History - 6</t>
+          <t>411-1: Algebra I H - 1</t>
         </is>
       </c>
       <c r="E860" s="6" t="inlineStr">
         <is>
-          <t>710-6: World History - 6</t>
+          <t>411-1: Algebra I H - 1</t>
         </is>
       </c>
       <c r="F860" s="2" t="n"/>
@@ -24234,16 +24234,16 @@
           <t>UNASSIGNED</t>
         </is>
       </c>
-      <c r="H860" s="6" t="inlineStr">
-        <is>
-          <t>751-2: American Government &amp; Politics</t>
+      <c r="H860" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
     </row>
     <row r="861">
       <c r="A861" s="4" t="inlineStr">
         <is>
-          <t>Winters, Jack</t>
+          <t>Willi, Mary</t>
         </is>
       </c>
       <c r="B861" s="5" t="inlineStr">
@@ -24252,25 +24252,25 @@
         </is>
       </c>
       <c r="C861" s="2" t="n"/>
-      <c r="D861" s="6" t="inlineStr">
-        <is>
-          <t>731-3: U.S. History II H - 3</t>
-        </is>
-      </c>
-      <c r="E861" s="6" t="inlineStr">
-        <is>
-          <t>731-3: U.S. History II H - 3</t>
+      <c r="D861" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E861" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F861" s="2" t="n"/>
       <c r="G861" s="6" t="inlineStr">
         <is>
-          <t>730-5: U.S. History II - 5</t>
+          <t>410-4: Algebra I - 4</t>
         </is>
       </c>
       <c r="H861" s="6" t="inlineStr">
         <is>
-          <t>730-5: U.S. History II - 5</t>
+          <t>410-4: Algebra I - 4</t>
         </is>
       </c>
     </row>
@@ -24282,17 +24282,17 @@
       </c>
       <c r="C862" s="2" t="n"/>
       <c r="D862" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E862" s="9" t="n">
         <v>5</v>
       </c>
       <c r="F862" s="2" t="n"/>
       <c r="G862" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H862" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="863">
@@ -24302,18 +24302,18 @@
         </is>
       </c>
       <c r="C863" s="2" t="n"/>
-      <c r="D863" s="7" t="n">
+      <c r="D863" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E863" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F863" s="2" t="n"/>
+      <c r="G863" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="E863" s="7" t="n">
+      <c r="H863" s="7" t="n">
         <v>3</v>
-      </c>
-      <c r="F863" s="2" t="n"/>
-      <c r="G863" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="H863" s="9" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="865">
@@ -24342,7 +24342,7 @@
     <row r="866">
       <c r="A866" s="3" t="inlineStr">
         <is>
-          <t>ID: 105620</t>
+          <t>ID: 105883</t>
         </is>
       </c>
       <c r="D866" s="1" t="inlineStr">
@@ -24370,7 +24370,7 @@
     <row r="867">
       <c r="A867" s="4" t="inlineStr">
         <is>
-          <t>Zawacki, Richard</t>
+          <t>Winters, Jack</t>
         </is>
       </c>
       <c r="B867" s="5" t="inlineStr">
@@ -24381,30 +24381,30 @@
       <c r="C867" s="2" t="n"/>
       <c r="D867" s="6" t="inlineStr">
         <is>
-          <t>732-3-F: Business Law - 3</t>
-        </is>
-      </c>
-      <c r="E867" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+          <t>730-3: U.S. History II - 3</t>
+        </is>
+      </c>
+      <c r="E867" s="6" t="inlineStr">
+        <is>
+          <t>730-3: U.S. History II - 3</t>
         </is>
       </c>
       <c r="F867" s="2" t="n"/>
       <c r="G867" s="6" t="inlineStr">
         <is>
-          <t>742-1: Economics - 1</t>
-        </is>
-      </c>
-      <c r="H867" s="6" t="inlineStr">
-        <is>
-          <t>742-1: Economics - 1</t>
+          <t>756 -1-F: Introduction to Law-1</t>
+        </is>
+      </c>
+      <c r="H867" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
     </row>
     <row r="868">
       <c r="A868" s="4" t="inlineStr">
         <is>
-          <t>Zawacki, Richard</t>
+          <t>Winters, Jack</t>
         </is>
       </c>
       <c r="B868" s="5" t="inlineStr">
@@ -24413,32 +24413,32 @@
         </is>
       </c>
       <c r="C868" s="2" t="n"/>
-      <c r="D868" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E868" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D868" s="6" t="inlineStr">
+        <is>
+          <t>710-5: World History - 5</t>
+        </is>
+      </c>
+      <c r="E868" s="6" t="inlineStr">
+        <is>
+          <t>710-5: World History - 5</t>
         </is>
       </c>
       <c r="F868" s="2" t="n"/>
-      <c r="G868" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="H868" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="G868" s="6" t="inlineStr">
+        <is>
+          <t>710-1: World History - 1</t>
+        </is>
+      </c>
+      <c r="H868" s="6" t="inlineStr">
+        <is>
+          <t>710-1: World History - 1</t>
         </is>
       </c>
     </row>
     <row r="869">
       <c r="A869" s="4" t="inlineStr">
         <is>
-          <t>Zawacki, Richard</t>
+          <t>Winters, Jack</t>
         </is>
       </c>
       <c r="B869" s="5" t="inlineStr">
@@ -24447,32 +24447,32 @@
         </is>
       </c>
       <c r="C869" s="2" t="n"/>
-      <c r="D869" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E869" s="6" t="inlineStr">
-        <is>
-          <t>732-2-S: Business Law - 2</t>
+      <c r="D869" s="6" t="inlineStr">
+        <is>
+          <t>756-1-F: Introduction to Law - 1</t>
+        </is>
+      </c>
+      <c r="E869" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F869" s="2" t="n"/>
       <c r="G869" s="6" t="inlineStr">
         <is>
-          <t>752-1: Economics H - 1</t>
+          <t>710-2: World History - 2</t>
         </is>
       </c>
       <c r="H869" s="6" t="inlineStr">
         <is>
-          <t>752-1: Economics H - 1</t>
+          <t>710-2: World History - 2</t>
         </is>
       </c>
     </row>
     <row r="870">
       <c r="A870" s="4" t="inlineStr">
         <is>
-          <t>Zawacki, Richard</t>
+          <t>Winters, Jack</t>
         </is>
       </c>
       <c r="B870" s="5" t="inlineStr">
@@ -24483,30 +24483,30 @@
       <c r="C870" s="2" t="n"/>
       <c r="D870" s="6" t="inlineStr">
         <is>
-          <t>742-1: Economics - 1</t>
+          <t>731-3: U.S. History II H - 3</t>
         </is>
       </c>
       <c r="E870" s="6" t="inlineStr">
         <is>
-          <t>742-1: Economics - 1</t>
+          <t>731-3: U.S. History II H - 3</t>
         </is>
       </c>
       <c r="F870" s="2" t="n"/>
-      <c r="G870" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="H870" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="G870" s="6" t="inlineStr">
+        <is>
+          <t>710-3: World History - 3</t>
+        </is>
+      </c>
+      <c r="H870" s="6" t="inlineStr">
+        <is>
+          <t>710-3: World History - 3</t>
         </is>
       </c>
     </row>
     <row r="871">
       <c r="A871" s="4" t="inlineStr">
         <is>
-          <t>Zawacki, Richard</t>
+          <t>Winters, Jack</t>
         </is>
       </c>
       <c r="B871" s="5" t="inlineStr">
@@ -24517,30 +24517,30 @@
       <c r="C871" s="2" t="n"/>
       <c r="D871" s="6" t="inlineStr">
         <is>
-          <t>742-2: Economics - 2</t>
+          <t>710-4: World History - 4</t>
         </is>
       </c>
       <c r="E871" s="6" t="inlineStr">
         <is>
-          <t>742-2: Economics - 2</t>
+          <t>710-4: World History - 4</t>
         </is>
       </c>
       <c r="F871" s="2" t="n"/>
       <c r="G871" s="6" t="inlineStr">
         <is>
-          <t>752-2: Economics H - 2</t>
+          <t>710-4: World History - 4</t>
         </is>
       </c>
       <c r="H871" s="6" t="inlineStr">
         <is>
-          <t>752-2: Economics H - 2</t>
+          <t>710-4: World History - 4</t>
         </is>
       </c>
     </row>
     <row r="872">
       <c r="A872" s="4" t="inlineStr">
         <is>
-          <t>Zawacki, Richard</t>
+          <t>Winters, Jack</t>
         </is>
       </c>
       <c r="B872" s="5" t="inlineStr">
@@ -24551,30 +24551,30 @@
       <c r="C872" s="2" t="n"/>
       <c r="D872" s="6" t="inlineStr">
         <is>
-          <t>752-1: Economics H - 1</t>
+          <t>710-6: World History - 6</t>
         </is>
       </c>
       <c r="E872" s="6" t="inlineStr">
         <is>
-          <t>752-1: Economics H - 1</t>
+          <t>710-6: World History - 6</t>
         </is>
       </c>
       <c r="F872" s="2" t="n"/>
-      <c r="G872" s="6" t="inlineStr">
-        <is>
-          <t>742-2: Economics - 2</t>
+      <c r="G872" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="H872" s="6" t="inlineStr">
         <is>
-          <t>742-2: Economics - 2</t>
+          <t>751-2: American Government &amp; Politics</t>
         </is>
       </c>
     </row>
     <row r="873">
       <c r="A873" s="4" t="inlineStr">
         <is>
-          <t>Zawacki, Richard</t>
+          <t>Winters, Jack</t>
         </is>
       </c>
       <c r="B873" s="5" t="inlineStr">
@@ -24583,25 +24583,25 @@
         </is>
       </c>
       <c r="C873" s="2" t="n"/>
-      <c r="D873" s="6" t="inlineStr">
-        <is>
-          <t>752-2: Economics H - 2</t>
-        </is>
-      </c>
-      <c r="E873" s="6" t="inlineStr">
-        <is>
-          <t>752-2: Economics H - 2</t>
+      <c r="D873" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E873" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F873" s="2" t="n"/>
       <c r="G873" s="6" t="inlineStr">
         <is>
-          <t>752-3: Economics H - 3</t>
+          <t>730-5: U.S. History II - 5</t>
         </is>
       </c>
       <c r="H873" s="6" t="inlineStr">
         <is>
-          <t>752-3: Economics H - 3</t>
+          <t>730-5: U.S. History II - 5</t>
         </is>
       </c>
     </row>
@@ -24613,17 +24613,17 @@
       </c>
       <c r="C874" s="2" t="n"/>
       <c r="D874" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E874" s="9" t="n">
         <v>5</v>
       </c>
       <c r="F874" s="2" t="n"/>
       <c r="G874" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H874" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="875">
@@ -24634,17 +24634,17 @@
       </c>
       <c r="C875" s="2" t="n"/>
       <c r="D875" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="E875" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="E875" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F875" s="2" t="n"/>
+      <c r="G875" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="F875" s="2" t="n"/>
-      <c r="G875" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="H875" s="7" t="n">
-        <v>3</v>
+      <c r="H875" s="9" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="877">
@@ -24673,7 +24673,7 @@
     <row r="878">
       <c r="A878" s="3" t="inlineStr">
         <is>
-          <t>ID: 105729</t>
+          <t>ID: 105620</t>
         </is>
       </c>
       <c r="D878" s="1" t="inlineStr">
@@ -24701,7 +24701,7 @@
     <row r="879">
       <c r="A879" s="4" t="inlineStr">
         <is>
-          <t>Zawiski, Brian</t>
+          <t>Zawacki, Richard</t>
         </is>
       </c>
       <c r="B879" s="5" t="inlineStr">
@@ -24710,32 +24710,32 @@
         </is>
       </c>
       <c r="C879" s="2" t="n"/>
-      <c r="D879" s="6" t="inlineStr">
-        <is>
-          <t>327-1: Latin II H - 1</t>
+      <c r="D879" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="E879" s="6" t="inlineStr">
         <is>
-          <t>327-1: Latin II H - 1</t>
+          <t>732-2-S: Business Law - 2</t>
         </is>
       </c>
       <c r="F879" s="2" t="n"/>
       <c r="G879" s="6" t="inlineStr">
         <is>
-          <t>327-1: Latin II H - 1</t>
+          <t>742-1: Economics - 1</t>
         </is>
       </c>
       <c r="H879" s="6" t="inlineStr">
         <is>
-          <t>327-1: Latin II H - 1</t>
+          <t>742-1: Economics - 1</t>
         </is>
       </c>
     </row>
     <row r="880">
       <c r="A880" s="4" t="inlineStr">
         <is>
-          <t>Zawiski, Brian</t>
+          <t>Zawacki, Richard</t>
         </is>
       </c>
       <c r="B880" s="5" t="inlineStr">
@@ -24746,30 +24746,30 @@
       <c r="C880" s="2" t="n"/>
       <c r="D880" s="6" t="inlineStr">
         <is>
-          <t>359-1: AP Latin - 1</t>
-        </is>
-      </c>
-      <c r="E880" s="6" t="inlineStr">
-        <is>
-          <t>359-1: AP Latin - 1</t>
+          <t>732-3-F: Business Law - 3</t>
+        </is>
+      </c>
+      <c r="E880" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F880" s="2" t="n"/>
-      <c r="G880" s="6" t="inlineStr">
-        <is>
-          <t>359-1: AP Latin - 1</t>
-        </is>
-      </c>
-      <c r="H880" s="6" t="inlineStr">
-        <is>
-          <t>359-1: AP Latin - 1</t>
+      <c r="G880" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="H880" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
     </row>
     <row r="881">
       <c r="A881" s="4" t="inlineStr">
         <is>
-          <t>Zawiski, Brian</t>
+          <t>Zawacki, Richard</t>
         </is>
       </c>
       <c r="B881" s="5" t="inlineStr">
@@ -24778,32 +24778,32 @@
         </is>
       </c>
       <c r="C881" s="2" t="n"/>
-      <c r="D881" s="6" t="inlineStr">
-        <is>
-          <t>339-1: Latin III H - 1</t>
-        </is>
-      </c>
-      <c r="E881" s="6" t="inlineStr">
-        <is>
-          <t>339-1: Latin III H - 1</t>
+      <c r="D881" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E881" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F881" s="2" t="n"/>
       <c r="G881" s="6" t="inlineStr">
         <is>
-          <t>339-1: Latin III H - 1</t>
+          <t>752-1: Economics H - 1</t>
         </is>
       </c>
       <c r="H881" s="6" t="inlineStr">
         <is>
-          <t>339-1: Latin III H - 1</t>
+          <t>752-1: Economics H - 1</t>
         </is>
       </c>
     </row>
     <row r="882">
       <c r="A882" s="4" t="inlineStr">
         <is>
-          <t>Zawiski, Brian</t>
+          <t>Zawacki, Richard</t>
         </is>
       </c>
       <c r="B882" s="5" t="inlineStr">
@@ -24814,12 +24814,12 @@
       <c r="C882" s="2" t="n"/>
       <c r="D882" s="6" t="inlineStr">
         <is>
-          <t>312-2: Italian I - 2</t>
+          <t>742-1: Economics - 1</t>
         </is>
       </c>
       <c r="E882" s="6" t="inlineStr">
         <is>
-          <t>312-2: Italian I - 2</t>
+          <t>742-1: Economics - 1</t>
         </is>
       </c>
       <c r="F882" s="2" t="n"/>
@@ -24837,7 +24837,7 @@
     <row r="883">
       <c r="A883" s="4" t="inlineStr">
         <is>
-          <t>Zawiski, Brian</t>
+          <t>Zawacki, Richard</t>
         </is>
       </c>
       <c r="B883" s="5" t="inlineStr">
@@ -24848,30 +24848,30 @@
       <c r="C883" s="2" t="n"/>
       <c r="D883" s="6" t="inlineStr">
         <is>
-          <t>312-1: Italian I - 1</t>
+          <t>742-2: Economics - 2</t>
         </is>
       </c>
       <c r="E883" s="6" t="inlineStr">
         <is>
-          <t>312-1: Italian I - 1</t>
+          <t>742-2: Economics - 2</t>
         </is>
       </c>
       <c r="F883" s="2" t="n"/>
       <c r="G883" s="6" t="inlineStr">
         <is>
-          <t>315-2: Latin I H - 2; 334-1 E: French III - 1</t>
+          <t>752-2: Economics H - 2</t>
         </is>
       </c>
       <c r="H883" s="6" t="inlineStr">
         <is>
-          <t>315-2: Latin I H - 2; 334-1 E: French III - 1</t>
+          <t>752-2: Economics H - 2</t>
         </is>
       </c>
     </row>
     <row r="884">
       <c r="A884" s="4" t="inlineStr">
         <is>
-          <t>Zawiski, Brian</t>
+          <t>Zawacki, Richard</t>
         </is>
       </c>
       <c r="B884" s="5" t="inlineStr">
@@ -24882,30 +24882,30 @@
       <c r="C884" s="2" t="n"/>
       <c r="D884" s="6" t="inlineStr">
         <is>
-          <t>315-1: Latin I H - 1</t>
+          <t>752-1: Economics H - 1</t>
         </is>
       </c>
       <c r="E884" s="6" t="inlineStr">
         <is>
-          <t>315-1: Latin I H - 1</t>
+          <t>752-1: Economics H - 1</t>
         </is>
       </c>
       <c r="F884" s="2" t="n"/>
       <c r="G884" s="6" t="inlineStr">
         <is>
-          <t>339-2: Latin III H - 2</t>
+          <t>742-2: Economics - 2</t>
         </is>
       </c>
       <c r="H884" s="6" t="inlineStr">
         <is>
-          <t>339-2: Latin III H - 2</t>
+          <t>742-2: Economics - 2</t>
         </is>
       </c>
     </row>
     <row r="885">
       <c r="A885" s="4" t="inlineStr">
         <is>
-          <t>Zawiski, Brian</t>
+          <t>Zawacki, Richard</t>
         </is>
       </c>
       <c r="B885" s="5" t="inlineStr">
@@ -24914,25 +24914,25 @@
         </is>
       </c>
       <c r="C885" s="2" t="n"/>
-      <c r="D885" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E885" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D885" s="6" t="inlineStr">
+        <is>
+          <t>752-2: Economics H - 2</t>
+        </is>
+      </c>
+      <c r="E885" s="6" t="inlineStr">
+        <is>
+          <t>752-2: Economics H - 2</t>
         </is>
       </c>
       <c r="F885" s="2" t="n"/>
       <c r="G885" s="6" t="inlineStr">
         <is>
-          <t>327-2: Latin II H - 2</t>
+          <t>752-3: Economics H - 3</t>
         </is>
       </c>
       <c r="H885" s="6" t="inlineStr">
         <is>
-          <t>327-2: Latin II H - 2</t>
+          <t>752-3: Economics H - 3</t>
         </is>
       </c>
     </row>
@@ -24944,17 +24944,17 @@
       </c>
       <c r="C886" s="2" t="n"/>
       <c r="D886" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E886" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F886" s="2" t="n"/>
       <c r="G886" s="9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H886" s="9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="887">
@@ -24965,16 +24965,347 @@
       </c>
       <c r="C887" s="2" t="n"/>
       <c r="D887" s="9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E887" s="9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F887" s="2" t="n"/>
       <c r="G887" s="7" t="n">
         <v>3</v>
       </c>
       <c r="H887" s="7" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="889">
+      <c r="D889" s="1" t="inlineStr">
+        <is>
+          <t>2026-2027</t>
+        </is>
+      </c>
+      <c r="E889" s="1" t="inlineStr">
+        <is>
+          <t>2026-2027</t>
+        </is>
+      </c>
+      <c r="F889" s="2" t="n"/>
+      <c r="G889" s="1" t="inlineStr">
+        <is>
+          <t>2025-2026</t>
+        </is>
+      </c>
+      <c r="H889" s="1" t="inlineStr">
+        <is>
+          <t>2025-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" s="3" t="inlineStr">
+        <is>
+          <t>ID: 105729</t>
+        </is>
+      </c>
+      <c r="D890" s="1" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="E890" s="1" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="F890" s="2" t="n"/>
+      <c r="G890" s="1" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="H890" s="1" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" s="4" t="inlineStr">
+        <is>
+          <t>Zawiski, Brian</t>
+        </is>
+      </c>
+      <c r="B891" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C891" s="2" t="n"/>
+      <c r="D891" s="6" t="inlineStr">
+        <is>
+          <t>327-1: Latin II H - 1</t>
+        </is>
+      </c>
+      <c r="E891" s="6" t="inlineStr">
+        <is>
+          <t>327-1: Latin II H - 1</t>
+        </is>
+      </c>
+      <c r="F891" s="2" t="n"/>
+      <c r="G891" s="6" t="inlineStr">
+        <is>
+          <t>327-1: Latin II H - 1</t>
+        </is>
+      </c>
+      <c r="H891" s="6" t="inlineStr">
+        <is>
+          <t>327-1: Latin II H - 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" s="4" t="inlineStr">
+        <is>
+          <t>Zawiski, Brian</t>
+        </is>
+      </c>
+      <c r="B892" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C892" s="2" t="n"/>
+      <c r="D892" s="6" t="inlineStr">
+        <is>
+          <t>359-1: AP Latin - 1</t>
+        </is>
+      </c>
+      <c r="E892" s="6" t="inlineStr">
+        <is>
+          <t>359-1: AP Latin - 1</t>
+        </is>
+      </c>
+      <c r="F892" s="2" t="n"/>
+      <c r="G892" s="6" t="inlineStr">
+        <is>
+          <t>359-1: AP Latin - 1</t>
+        </is>
+      </c>
+      <c r="H892" s="6" t="inlineStr">
+        <is>
+          <t>359-1: AP Latin - 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" s="4" t="inlineStr">
+        <is>
+          <t>Zawiski, Brian</t>
+        </is>
+      </c>
+      <c r="B893" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C893" s="2" t="n"/>
+      <c r="D893" s="6" t="inlineStr">
+        <is>
+          <t>339-1: Latin III H - 1</t>
+        </is>
+      </c>
+      <c r="E893" s="6" t="inlineStr">
+        <is>
+          <t>339-1: Latin III H - 1</t>
+        </is>
+      </c>
+      <c r="F893" s="2" t="n"/>
+      <c r="G893" s="6" t="inlineStr">
+        <is>
+          <t>339-1: Latin III H - 1</t>
+        </is>
+      </c>
+      <c r="H893" s="6" t="inlineStr">
+        <is>
+          <t>339-1: Latin III H - 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" s="4" t="inlineStr">
+        <is>
+          <t>Zawiski, Brian</t>
+        </is>
+      </c>
+      <c r="B894" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C894" s="2" t="n"/>
+      <c r="D894" s="6" t="inlineStr">
+        <is>
+          <t>312-2: Italian I - 2</t>
+        </is>
+      </c>
+      <c r="E894" s="6" t="inlineStr">
+        <is>
+          <t>312-2: Italian I - 2</t>
+        </is>
+      </c>
+      <c r="F894" s="2" t="n"/>
+      <c r="G894" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="H894" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" s="4" t="inlineStr">
+        <is>
+          <t>Zawiski, Brian</t>
+        </is>
+      </c>
+      <c r="B895" s="5" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C895" s="2" t="n"/>
+      <c r="D895" s="6" t="inlineStr">
+        <is>
+          <t>312-1: Italian I - 1</t>
+        </is>
+      </c>
+      <c r="E895" s="6" t="inlineStr">
+        <is>
+          <t>312-1: Italian I - 1</t>
+        </is>
+      </c>
+      <c r="F895" s="2" t="n"/>
+      <c r="G895" s="6" t="inlineStr">
+        <is>
+          <t>315-2: Latin I H - 2; 334-1 E: French III - 1</t>
+        </is>
+      </c>
+      <c r="H895" s="6" t="inlineStr">
+        <is>
+          <t>315-2: Latin I H - 2; 334-1 E: French III - 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" s="4" t="inlineStr">
+        <is>
+          <t>Zawiski, Brian</t>
+        </is>
+      </c>
+      <c r="B896" s="5" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C896" s="2" t="n"/>
+      <c r="D896" s="6" t="inlineStr">
+        <is>
+          <t>315-1: Latin I H - 1</t>
+        </is>
+      </c>
+      <c r="E896" s="6" t="inlineStr">
+        <is>
+          <t>315-1: Latin I H - 1</t>
+        </is>
+      </c>
+      <c r="F896" s="2" t="n"/>
+      <c r="G896" s="6" t="inlineStr">
+        <is>
+          <t>339-2: Latin III H - 2</t>
+        </is>
+      </c>
+      <c r="H896" s="6" t="inlineStr">
+        <is>
+          <t>339-2: Latin III H - 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" s="4" t="inlineStr">
+        <is>
+          <t>Zawiski, Brian</t>
+        </is>
+      </c>
+      <c r="B897" s="5" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="C897" s="2" t="n"/>
+      <c r="D897" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E897" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="F897" s="2" t="n"/>
+      <c r="G897" s="6" t="inlineStr">
+        <is>
+          <t>327-2: Latin II H - 2</t>
+        </is>
+      </c>
+      <c r="H897" s="6" t="inlineStr">
+        <is>
+          <t>327-2: Latin II H - 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" s="8" t="inlineStr">
+        <is>
+          <t>TOTAL SECTIONS</t>
+        </is>
+      </c>
+      <c r="C898" s="2" t="n"/>
+      <c r="D898" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="E898" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="F898" s="2" t="n"/>
+      <c r="G898" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="H898" s="9" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" s="8" t="inlineStr">
+        <is>
+          <t>TOTAL CONSECUTIVE PERIODS</t>
+        </is>
+      </c>
+      <c r="C899" s="2" t="n"/>
+      <c r="D899" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="E899" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="F899" s="2" t="n"/>
+      <c r="G899" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="H899" s="7" t="n">
         <v>3</v>
       </c>
     </row>

--- a/Teacher_Schedule_Review_and_Tally.xlsx
+++ b/Teacher_Schedule_Review_and_Tally.xlsx
@@ -549,12 +549,12 @@
       <c r="C3" s="2" t="n"/>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>421-2: Geometry H - 2</t>
+          <t>421-3: Geometry H - 3</t>
         </is>
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>421-2: Geometry H - 2</t>
+          <t>421-3: Geometry H - 3</t>
         </is>
       </c>
       <c r="F3" s="2" t="n"/>
@@ -615,14 +615,14 @@
         </is>
       </c>
       <c r="C5" s="2" t="n"/>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>425-1: Adv Geometry H - 1</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>425-1: Adv Geometry H - 1</t>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F5" s="2" t="n"/>
@@ -651,12 +651,12 @@
       <c r="C6" s="2" t="n"/>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>445-1: Adv Precalculus H - 1</t>
+          <t>425-1: Adv Geometry H - 1</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>445-1: Adv Precalculus H - 1</t>
+          <t>425-1: Adv Geometry H - 1</t>
         </is>
       </c>
       <c r="F6" s="2" t="n"/>
@@ -719,12 +719,12 @@
       <c r="C8" s="2" t="n"/>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>421-3: Geometry H - 3</t>
+          <t>445-1: Adv Precalculus H - 1</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>421-3: Geometry H - 3</t>
+          <t>445-1: Adv Precalculus H - 1</t>
         </is>
       </c>
       <c r="F8" s="2" t="n"/>
@@ -751,14 +751,14 @@
         </is>
       </c>
       <c r="C9" s="2" t="n"/>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>421-2: Geometry H - 2</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>421-2: Geometry H - 2</t>
         </is>
       </c>
       <c r="F9" s="2" t="n"/>
@@ -801,11 +801,11 @@
         </is>
       </c>
       <c r="C11" s="2" t="n"/>
-      <c r="D11" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="E11" s="9" t="n">
-        <v>4</v>
+      <c r="D11" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" s="7" t="n">
+        <v>2</v>
       </c>
       <c r="F11" s="2" t="n"/>
       <c r="G11" s="9" t="n">
@@ -946,14 +946,14 @@
         </is>
       </c>
       <c r="C17" s="2" t="n"/>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>351-2: AP Spanish - 2</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>351-2: AP Spanish - 2</t>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F17" s="2" t="n"/>
@@ -980,14 +980,14 @@
         </is>
       </c>
       <c r="C18" s="2" t="n"/>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>351-2: AP Spanish - 2</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>351-2: AP Spanish - 2</t>
         </is>
       </c>
       <c r="F18" s="2" t="n"/>
@@ -1133,10 +1133,10 @@
       </c>
       <c r="C23" s="2" t="n"/>
       <c r="D23" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F23" s="2" t="n"/>
       <c r="G23" s="7" t="n">
@@ -1873,12 +1873,12 @@
       <c r="C51" s="2" t="n"/>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>610-9-F: Health/PE - 9</t>
+          <t>610-1-F: Health/PE - 1</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>610-2-S: Health/PE - 2</t>
+          <t>610-8-S: Health/PE - 8</t>
         </is>
       </c>
       <c r="F51" s="2" t="n"/>
@@ -1907,12 +1907,12 @@
       <c r="C52" s="2" t="n"/>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>610-1-F: Health/PE - 1</t>
+          <t>610-9-F: Health/PE - 9</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>610-8-S: Health/PE - 8</t>
+          <t>610-2-S: Health/PE - 2</t>
         </is>
       </c>
       <c r="F52" s="2" t="n"/>
@@ -2533,14 +2533,14 @@
         </is>
       </c>
       <c r="C75" s="2" t="n"/>
-      <c r="D75" s="6" t="inlineStr">
-        <is>
-          <t>491-1: AP Computer Science Principles - 1</t>
+      <c r="D75" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>491-1: AP Computer Science Principles - 1</t>
+          <t>472-2-S: Web Design - 2</t>
         </is>
       </c>
       <c r="F75" s="2" t="n"/>
@@ -2601,14 +2601,14 @@
         </is>
       </c>
       <c r="C77" s="2" t="n"/>
-      <c r="D77" s="6" t="inlineStr">
-        <is>
-          <t>496-1: AP Cybersecurity - 1</t>
-        </is>
-      </c>
-      <c r="E77" s="6" t="inlineStr">
-        <is>
-          <t>496-1: AP Cybersecurity - 1</t>
+      <c r="D77" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E77" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F77" s="2" t="n"/>
@@ -2637,12 +2637,12 @@
       <c r="C78" s="2" t="n"/>
       <c r="D78" s="6" t="inlineStr">
         <is>
-          <t>472-1-F: Web Design - 1</t>
-        </is>
-      </c>
-      <c r="E78" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+          <t>496-1: AP Cybersecurity - 1</t>
+        </is>
+      </c>
+      <c r="E78" s="6" t="inlineStr">
+        <is>
+          <t>496-1: AP Cybersecurity - 1</t>
         </is>
       </c>
       <c r="F78" s="2" t="n"/>
@@ -2669,14 +2669,14 @@
         </is>
       </c>
       <c r="C79" s="2" t="n"/>
-      <c r="D79" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E79" s="6" t="inlineStr">
-        <is>
-          <t>472-2-S: Web Design - 2</t>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>472-1-F: Web Design - 1</t>
+        </is>
+      </c>
+      <c r="E79" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F79" s="2" t="n"/>
@@ -2737,14 +2737,14 @@
         </is>
       </c>
       <c r="C81" s="2" t="n"/>
-      <c r="D81" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E81" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>491-1: AP Computer Science Principles - 1</t>
+        </is>
+      </c>
+      <c r="E81" s="6" t="inlineStr">
+        <is>
+          <t>491-1: AP Computer Science Principles - 1</t>
         </is>
       </c>
       <c r="F81" s="2" t="n"/>
@@ -2791,7 +2791,7 @@
         <v>4</v>
       </c>
       <c r="E83" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F83" s="2" t="n"/>
       <c r="G83" s="7" t="n">
@@ -2864,14 +2864,14 @@
         </is>
       </c>
       <c r="C87" s="2" t="n"/>
-      <c r="D87" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E87" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D87" s="6" t="inlineStr">
+        <is>
+          <t>453-1: AP Calc AB - 1</t>
+        </is>
+      </c>
+      <c r="E87" s="6" t="inlineStr">
+        <is>
+          <t>453-1: AP Calc AB - 1</t>
         </is>
       </c>
       <c r="F87" s="2" t="n"/>
@@ -2968,12 +2968,12 @@
       <c r="C90" s="2" t="n"/>
       <c r="D90" s="6" t="inlineStr">
         <is>
-          <t>431-2: Algebra II/Trig H - 2</t>
+          <t>431-1: Algebra II/Trig H - 1</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
         <is>
-          <t>431-2: Algebra II/Trig H - 2</t>
+          <t>431-1: Algebra II/Trig H - 1</t>
         </is>
       </c>
       <c r="F90" s="2" t="n"/>
@@ -3002,12 +3002,12 @@
       <c r="C91" s="2" t="n"/>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>431-1: Algebra II/Trig H - 1</t>
+          <t>431-2: Algebra II/Trig H - 2</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>431-1: Algebra II/Trig H - 1</t>
+          <t>431-2: Algebra II/Trig H - 2</t>
         </is>
       </c>
       <c r="F91" s="2" t="n"/>
@@ -3034,14 +3034,14 @@
         </is>
       </c>
       <c r="C92" s="2" t="n"/>
-      <c r="D92" s="6" t="inlineStr">
-        <is>
-          <t>453-1: AP Calc AB - 1</t>
-        </is>
-      </c>
-      <c r="E92" s="6" t="inlineStr">
-        <is>
-          <t>453-1: AP Calc AB - 1</t>
+      <c r="D92" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E92" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F92" s="2" t="n"/>
@@ -3118,11 +3118,11 @@
         </is>
       </c>
       <c r="C95" s="2" t="n"/>
-      <c r="D95" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="E95" s="9" t="n">
-        <v>5</v>
+      <c r="D95" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E95" s="7" t="n">
+        <v>3</v>
       </c>
       <c r="F95" s="2" t="n"/>
       <c r="G95" s="7" t="n">
@@ -3263,14 +3263,14 @@
         </is>
       </c>
       <c r="C101" s="2" t="n"/>
-      <c r="D101" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E101" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D101" s="6" t="inlineStr">
+        <is>
+          <t>320-4: Spanish II - 4</t>
+        </is>
+      </c>
+      <c r="E101" s="6" t="inlineStr">
+        <is>
+          <t>320-4: Spanish II - 4</t>
         </is>
       </c>
       <c r="F101" s="2" t="n"/>
@@ -3297,14 +3297,14 @@
         </is>
       </c>
       <c r="C102" s="2" t="n"/>
-      <c r="D102" s="6" t="inlineStr">
-        <is>
-          <t>320-4: Spanish II - 4</t>
-        </is>
-      </c>
-      <c r="E102" s="6" t="inlineStr">
-        <is>
-          <t>320-4: Spanish II - 4</t>
+      <c r="D102" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E102" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F102" s="2" t="n"/>
@@ -3528,12 +3528,12 @@
       <c r="C111" s="2" t="n"/>
       <c r="D111" s="6" t="inlineStr">
         <is>
-          <t>642-3-F: Nutrition &amp; Fitness/PE - 3</t>
+          <t>631-1-F: CPR-AED Training/PE - 1</t>
         </is>
       </c>
       <c r="E111" s="6" t="inlineStr">
         <is>
-          <t>631-2-S: CPR-AED Training/PE - 2</t>
+          <t>642-2-S: Nutrition &amp; Fitness/PE - 2</t>
         </is>
       </c>
       <c r="F111" s="2" t="n"/>
@@ -3562,12 +3562,12 @@
       <c r="C112" s="2" t="n"/>
       <c r="D112" s="6" t="inlineStr">
         <is>
-          <t>631-1-F: CPR-AED Training/PE - 1</t>
+          <t>642-3-F: Nutrition &amp; Fitness/PE - 3</t>
         </is>
       </c>
       <c r="E112" s="6" t="inlineStr">
         <is>
-          <t>642-2-S: Nutrition &amp; Fitness/PE - 2</t>
+          <t>631-4-S: CPR-AED Training/PE - 4</t>
         </is>
       </c>
       <c r="F112" s="2" t="n"/>
@@ -3667,9 +3667,9 @@
           <t>UNASSIGNED</t>
         </is>
       </c>
-      <c r="E115" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="E115" s="6" t="inlineStr">
+        <is>
+          <t>631-2-S: CPR-AED Training/PE - 2</t>
         </is>
       </c>
       <c r="F115" s="2" t="n"/>
@@ -3735,9 +3735,9 @@
           <t>642-1-F: Nutrition &amp; Fitness/PE - 1</t>
         </is>
       </c>
-      <c r="E117" s="6" t="inlineStr">
-        <is>
-          <t>631-4-S: CPR-AED Training/PE - 4</t>
+      <c r="E117" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F117" s="2" t="n"/>
@@ -3891,14 +3891,14 @@
         </is>
       </c>
       <c r="C124" s="2" t="n"/>
-      <c r="D124" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E124" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D124" s="6" t="inlineStr">
+        <is>
+          <t>546-2: Forensics - 2</t>
+        </is>
+      </c>
+      <c r="E124" s="6" t="inlineStr">
+        <is>
+          <t>546-2: Forensics - 2</t>
         </is>
       </c>
       <c r="F124" s="2" t="n"/>
@@ -3927,12 +3927,12 @@
       <c r="C125" s="2" t="n"/>
       <c r="D125" s="6" t="inlineStr">
         <is>
-          <t>510-1: Biology - 1</t>
+          <t>546-1: Forensics - 1</t>
         </is>
       </c>
       <c r="E125" s="6" t="inlineStr">
         <is>
-          <t>510-1: Biology - 1</t>
+          <t>546-1: Forensics - 1</t>
         </is>
       </c>
       <c r="F125" s="2" t="n"/>
@@ -3993,14 +3993,14 @@
         </is>
       </c>
       <c r="C127" s="2" t="n"/>
-      <c r="D127" s="6" t="inlineStr">
-        <is>
-          <t>510-2: Biology - 2</t>
-        </is>
-      </c>
-      <c r="E127" s="6" t="inlineStr">
-        <is>
-          <t>510-2: Biology - 2</t>
+      <c r="D127" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E127" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F127" s="2" t="n"/>
@@ -4029,12 +4029,12 @@
       <c r="C128" s="2" t="n"/>
       <c r="D128" s="6" t="inlineStr">
         <is>
-          <t>546-1: Forensics - 1</t>
+          <t>510-1: Biology - 1</t>
         </is>
       </c>
       <c r="E128" s="6" t="inlineStr">
         <is>
-          <t>546-1: Forensics - 1</t>
+          <t>510-1: Biology - 1</t>
         </is>
       </c>
       <c r="F128" s="2" t="n"/>
@@ -4063,12 +4063,12 @@
       <c r="C129" s="2" t="n"/>
       <c r="D129" s="6" t="inlineStr">
         <is>
-          <t>546-2: Forensics - 2</t>
+          <t>510-2: Biology - 2</t>
         </is>
       </c>
       <c r="E129" s="6" t="inlineStr">
         <is>
-          <t>546-2: Forensics - 2</t>
+          <t>510-2: Biology - 2</t>
         </is>
       </c>
       <c r="F129" s="2" t="n"/>
@@ -4111,11 +4111,11 @@
         </is>
       </c>
       <c r="C131" s="2" t="n"/>
-      <c r="D131" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="E131" s="9" t="n">
-        <v>5</v>
+      <c r="D131" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E131" s="7" t="n">
+        <v>3</v>
       </c>
       <c r="F131" s="2" t="n"/>
       <c r="G131" s="7" t="n">
@@ -4188,14 +4188,14 @@
         </is>
       </c>
       <c r="C135" s="2" t="n"/>
-      <c r="D135" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D135" s="6" t="inlineStr">
+        <is>
+          <t>757-2: International Business Strategies - 2</t>
         </is>
       </c>
       <c r="E135" s="6" t="inlineStr">
         <is>
-          <t>758-2-S: Bloomberg Market Concepts - 2</t>
+          <t>757-2: International Business Strategies - 2</t>
         </is>
       </c>
       <c r="F135" s="2" t="n"/>
@@ -4222,14 +4222,14 @@
         </is>
       </c>
       <c r="C136" s="2" t="n"/>
-      <c r="D136" s="6" t="inlineStr">
-        <is>
-          <t>727-1-F: Sports and Entertainment Marketing - 1</t>
-        </is>
-      </c>
-      <c r="E136" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D136" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E136" s="6" t="inlineStr">
+        <is>
+          <t>758-2-S: Bloomberg Market Concepts - 2</t>
         </is>
       </c>
       <c r="F136" s="2" t="n"/>
@@ -4258,12 +4258,12 @@
       <c r="C137" s="2" t="n"/>
       <c r="D137" s="6" t="inlineStr">
         <is>
-          <t>757-2: International Business Strategies - 2</t>
+          <t>757-1: International Business Strategies - 1</t>
         </is>
       </c>
       <c r="E137" s="6" t="inlineStr">
         <is>
-          <t>757-2: International Business Strategies - 2</t>
+          <t>757-1: International Business Strategies - 1</t>
         </is>
       </c>
       <c r="F137" s="2" t="n"/>
@@ -4292,12 +4292,12 @@
       <c r="C138" s="2" t="n"/>
       <c r="D138" s="6" t="inlineStr">
         <is>
-          <t>757-3: International Business Strategies - 3</t>
-        </is>
-      </c>
-      <c r="E138" s="6" t="inlineStr">
-        <is>
-          <t>757-3: International Business Strategies - 3</t>
+          <t>727-1-F: Sports and Entertainment Marketing - 1</t>
+        </is>
+      </c>
+      <c r="E138" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F138" s="2" t="n"/>
@@ -4324,14 +4324,14 @@
         </is>
       </c>
       <c r="C139" s="2" t="n"/>
-      <c r="D139" s="6" t="inlineStr">
-        <is>
-          <t>757-1: International Business Strategies - 1</t>
+      <c r="D139" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="E139" s="6" t="inlineStr">
         <is>
-          <t>757-1: International Business Strategies - 1</t>
+          <t>727-2-S: Sports and Entertainment Marketing - 2</t>
         </is>
       </c>
       <c r="F139" s="2" t="n"/>
@@ -4360,12 +4360,12 @@
       <c r="C140" s="2" t="n"/>
       <c r="D140" s="6" t="inlineStr">
         <is>
-          <t>732-1-F: Business Law - 1</t>
+          <t>732-1-F: Business Law - 1; 757-3: International Business Strategies - 3</t>
         </is>
       </c>
       <c r="E140" s="6" t="inlineStr">
         <is>
-          <t>727-2-S: Sports and Entertainment Marketing - 2</t>
+          <t>757-3: International Business Strategies - 3</t>
         </is>
       </c>
       <c r="F140" s="2" t="n"/>
@@ -4442,11 +4442,11 @@
         </is>
       </c>
       <c r="C143" s="2" t="n"/>
-      <c r="D143" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="E143" s="9" t="n">
-        <v>5</v>
+      <c r="D143" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E143" s="7" t="n">
+        <v>3</v>
       </c>
       <c r="F143" s="2" t="n"/>
       <c r="G143" s="9" t="n">
@@ -4521,12 +4521,12 @@
       <c r="C147" s="2" t="n"/>
       <c r="D147" s="6" t="inlineStr">
         <is>
-          <t>620-3-F: Driver's Ed/PE - 3</t>
-        </is>
-      </c>
-      <c r="E147" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+          <t>620-1-F: Driver's Ed/PE - 1</t>
+        </is>
+      </c>
+      <c r="E147" s="6" t="inlineStr">
+        <is>
+          <t>620-8-S: Driver's Ed/PE - 8</t>
         </is>
       </c>
       <c r="F147" s="2" t="n"/>
@@ -4553,14 +4553,14 @@
         </is>
       </c>
       <c r="C148" s="2" t="n"/>
-      <c r="D148" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E148" s="6" t="inlineStr">
-        <is>
-          <t>620-2-S: Driver's Ed/PE - 2</t>
+      <c r="D148" s="6" t="inlineStr">
+        <is>
+          <t>620-3-F: Driver's Ed/PE - 3</t>
+        </is>
+      </c>
+      <c r="E148" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F148" s="2" t="n"/>
@@ -4621,14 +4621,14 @@
         </is>
       </c>
       <c r="C150" s="2" t="n"/>
-      <c r="D150" s="6" t="inlineStr">
-        <is>
-          <t>620-5-F: Driver's Ed/PE - 5</t>
-        </is>
-      </c>
-      <c r="E150" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D150" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E150" s="6" t="inlineStr">
+        <is>
+          <t>620-4-S: Driver's Ed/PE - 4</t>
         </is>
       </c>
       <c r="F150" s="2" t="n"/>
@@ -4689,14 +4689,14 @@
         </is>
       </c>
       <c r="C152" s="2" t="n"/>
-      <c r="D152" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E152" s="6" t="inlineStr">
-        <is>
-          <t>620-4-S: Driver's Ed/PE - 4</t>
+      <c r="D152" s="6" t="inlineStr">
+        <is>
+          <t>620-5-F: Driver's Ed/PE - 5</t>
+        </is>
+      </c>
+      <c r="E152" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F152" s="2" t="n"/>
@@ -4723,14 +4723,14 @@
         </is>
       </c>
       <c r="C153" s="2" t="n"/>
-      <c r="D153" s="6" t="inlineStr">
-        <is>
-          <t>620-1-F: Driver's Ed/PE - 1</t>
+      <c r="D153" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="E153" s="6" t="inlineStr">
         <is>
-          <t>620-8-S: Driver's Ed/PE - 8</t>
+          <t>620-2-S: Driver's Ed/PE - 2</t>
         </is>
       </c>
       <c r="F153" s="2" t="n"/>
@@ -5249,14 +5249,14 @@
         </is>
       </c>
       <c r="C173" s="2" t="n"/>
-      <c r="D173" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E173" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D173" s="6" t="inlineStr">
+        <is>
+          <t>111-2: Composition &amp; Literature H - 2</t>
+        </is>
+      </c>
+      <c r="E173" s="6" t="inlineStr">
+        <is>
+          <t>111-2: Composition &amp; Literature H - 2</t>
         </is>
       </c>
       <c r="F173" s="2" t="n"/>
@@ -5283,14 +5283,14 @@
         </is>
       </c>
       <c r="C174" s="2" t="n"/>
-      <c r="D174" s="6" t="inlineStr">
-        <is>
-          <t>111-2: Composition &amp; Literature H - 2</t>
-        </is>
-      </c>
-      <c r="E174" s="6" t="inlineStr">
-        <is>
-          <t>111-2: Composition &amp; Literature H - 2</t>
+      <c r="D174" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E174" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F174" s="2" t="n"/>
@@ -5319,12 +5319,12 @@
       <c r="C175" s="2" t="n"/>
       <c r="D175" s="6" t="inlineStr">
         <is>
-          <t>129-2: AP Seminar - 2</t>
+          <t>111-1: Composition &amp; Literature H - 1</t>
         </is>
       </c>
       <c r="E175" s="6" t="inlineStr">
         <is>
-          <t>129-2: AP Seminar - 2</t>
+          <t>111-1: Composition &amp; Literature H - 1</t>
         </is>
       </c>
       <c r="F175" s="2" t="n"/>
@@ -5353,12 +5353,12 @@
       <c r="C176" s="2" t="n"/>
       <c r="D176" s="6" t="inlineStr">
         <is>
-          <t>111-3: Composition &amp; Literature H - 3</t>
+          <t>129-2: AP Seminar - 2</t>
         </is>
       </c>
       <c r="E176" s="6" t="inlineStr">
         <is>
-          <t>111-3: Composition &amp; Literature H - 3</t>
+          <t>129-2: AP Seminar - 2</t>
         </is>
       </c>
       <c r="F176" s="2" t="n"/>
@@ -5387,12 +5387,12 @@
       <c r="C177" s="2" t="n"/>
       <c r="D177" s="6" t="inlineStr">
         <is>
-          <t>111-1: Composition &amp; Literature H - 1</t>
+          <t>111-3: Composition &amp; Literature H - 3</t>
         </is>
       </c>
       <c r="E177" s="6" t="inlineStr">
         <is>
-          <t>111-1: Composition &amp; Literature H - 1</t>
+          <t>111-3: Composition &amp; Literature H - 3</t>
         </is>
       </c>
       <c r="F177" s="2" t="n"/>
@@ -5435,11 +5435,11 @@
         </is>
       </c>
       <c r="C179" s="2" t="n"/>
-      <c r="D179" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="E179" s="9" t="n">
-        <v>4</v>
+      <c r="D179" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E179" s="7" t="n">
+        <v>3</v>
       </c>
       <c r="F179" s="2" t="n"/>
       <c r="G179" s="7" t="n">
@@ -5546,14 +5546,14 @@
         </is>
       </c>
       <c r="C184" s="2" t="n"/>
-      <c r="D184" s="6" t="inlineStr">
-        <is>
-          <t>249-1-F: Adv Painting - 1</t>
-        </is>
-      </c>
-      <c r="E184" s="6" t="inlineStr">
-        <is>
-          <t>241-2-S: Studio Art I - 2</t>
+      <c r="D184" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E184" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F184" s="2" t="n"/>
@@ -5619,9 +5619,9 @@
           <t>248-1-F: Adv Drawing - 1</t>
         </is>
       </c>
-      <c r="E186" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="E186" s="6" t="inlineStr">
+        <is>
+          <t>241-2-S: Studio Art I - 2</t>
         </is>
       </c>
       <c r="F186" s="2" t="n"/>
@@ -5716,9 +5716,9 @@
         </is>
       </c>
       <c r="C189" s="2" t="n"/>
-      <c r="D189" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D189" s="6" t="inlineStr">
+        <is>
+          <t>249-1-F: Adv Painting - 1</t>
         </is>
       </c>
       <c r="E189" s="7" t="inlineStr">
@@ -5766,8 +5766,8 @@
         </is>
       </c>
       <c r="C191" s="2" t="n"/>
-      <c r="D191" s="9" t="n">
-        <v>5</v>
+      <c r="D191" s="7" t="n">
+        <v>3</v>
       </c>
       <c r="E191" s="7" t="n">
         <v>3</v>
@@ -5845,12 +5845,12 @@
       <c r="C195" s="2" t="n"/>
       <c r="D195" s="6" t="inlineStr">
         <is>
-          <t>520-3: Chemistry - 3</t>
+          <t>520-4: Chemistry - 4</t>
         </is>
       </c>
       <c r="E195" s="6" t="inlineStr">
         <is>
-          <t>520-3: Chemistry - 3</t>
+          <t>520-4: Chemistry - 4</t>
         </is>
       </c>
       <c r="F195" s="2" t="n"/>
@@ -5913,12 +5913,12 @@
       <c r="C197" s="2" t="n"/>
       <c r="D197" s="6" t="inlineStr">
         <is>
-          <t>520-4: Chemistry - 4</t>
+          <t>520-3: Chemistry - 3</t>
         </is>
       </c>
       <c r="E197" s="6" t="inlineStr">
         <is>
-          <t>520-4: Chemistry - 4</t>
+          <t>520-3: Chemistry - 3</t>
         </is>
       </c>
       <c r="F197" s="2" t="n"/>
@@ -6278,12 +6278,12 @@
       <c r="C210" s="2" t="n"/>
       <c r="D210" s="6" t="inlineStr">
         <is>
-          <t>141-1: College English Honors - 1</t>
+          <t>141-2: College English Honors - 2</t>
         </is>
       </c>
       <c r="E210" s="6" t="inlineStr">
         <is>
-          <t>141-1: College English Honors - 1</t>
+          <t>141-2: College English Honors - 2</t>
         </is>
       </c>
       <c r="F210" s="2" t="n"/>
@@ -6312,12 +6312,12 @@
       <c r="C211" s="2" t="n"/>
       <c r="D211" s="6" t="inlineStr">
         <is>
-          <t>141-2: College English Honors - 2</t>
+          <t>141-1: College English Honors - 1</t>
         </is>
       </c>
       <c r="E211" s="6" t="inlineStr">
         <is>
-          <t>141-2: College English Honors - 2</t>
+          <t>141-1: College English Honors - 1</t>
         </is>
       </c>
       <c r="F211" s="2" t="n"/>
@@ -6539,14 +6539,14 @@
         </is>
       </c>
       <c r="C220" s="2" t="n"/>
-      <c r="D220" s="6" t="inlineStr">
-        <is>
-          <t>729-2: AP Business with Personal Finance - 2</t>
-        </is>
-      </c>
-      <c r="E220" s="6" t="inlineStr">
-        <is>
-          <t>729-2: AP Business with Personal Finance - 2</t>
+      <c r="D220" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E220" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F220" s="2" t="n"/>
@@ -6709,14 +6709,14 @@
         </is>
       </c>
       <c r="C225" s="2" t="n"/>
-      <c r="D225" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E225" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D225" s="6" t="inlineStr">
+        <is>
+          <t>729-2: AP Business with Personal Finance - 2</t>
+        </is>
+      </c>
+      <c r="E225" s="6" t="inlineStr">
+        <is>
+          <t>729-2: AP Business with Personal Finance - 2</t>
         </is>
       </c>
       <c r="F225" s="2" t="n"/>
@@ -6760,10 +6760,10 @@
       </c>
       <c r="C227" s="2" t="n"/>
       <c r="D227" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="E227" s="9" t="n">
         <v>5</v>
+      </c>
+      <c r="E227" s="7" t="n">
+        <v>3</v>
       </c>
       <c r="F227" s="2" t="n"/>
       <c r="G227" s="9" t="n">
@@ -7498,14 +7498,14 @@
         </is>
       </c>
       <c r="C255" s="2" t="n"/>
-      <c r="D255" s="6" t="inlineStr">
-        <is>
-          <t>131-3: British Literature H - 3</t>
-        </is>
-      </c>
-      <c r="E255" s="6" t="inlineStr">
-        <is>
-          <t>131-3: British Literature H - 3</t>
+      <c r="D255" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E255" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F255" s="2" t="n"/>
@@ -7634,14 +7634,14 @@
         </is>
       </c>
       <c r="C259" s="2" t="n"/>
-      <c r="D259" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E259" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D259" s="6" t="inlineStr">
+        <is>
+          <t>131-3: British Literature H - 3</t>
+        </is>
+      </c>
+      <c r="E259" s="6" t="inlineStr">
+        <is>
+          <t>131-3: British Literature H - 3</t>
         </is>
       </c>
       <c r="F259" s="2" t="n"/>
@@ -8228,14 +8228,14 @@
         </is>
       </c>
       <c r="C281" s="2" t="n"/>
-      <c r="D281" s="6" t="inlineStr">
-        <is>
-          <t>422-1: Geometry - 1</t>
-        </is>
-      </c>
-      <c r="E281" s="6" t="inlineStr">
-        <is>
-          <t>422-1: Geometry - 1</t>
+      <c r="D281" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E281" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F281" s="2" t="n"/>
@@ -8298,12 +8298,12 @@
       <c r="C283" s="2" t="n"/>
       <c r="D283" s="6" t="inlineStr">
         <is>
-          <t>450-2: Calculus H - 2</t>
+          <t>422-1: Geometry - 1</t>
         </is>
       </c>
       <c r="E283" s="6" t="inlineStr">
         <is>
-          <t>450-2: Calculus H - 2</t>
+          <t>422-1: Geometry - 1</t>
         </is>
       </c>
       <c r="F283" s="2" t="n"/>
@@ -8364,14 +8364,14 @@
         </is>
       </c>
       <c r="C285" s="2" t="n"/>
-      <c r="D285" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E285" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D285" s="6" t="inlineStr">
+        <is>
+          <t>450-2: Calculus H - 2</t>
+        </is>
+      </c>
+      <c r="E285" s="6" t="inlineStr">
+        <is>
+          <t>450-2: Calculus H - 2</t>
         </is>
       </c>
       <c r="F285" s="2" t="n"/>
@@ -8415,10 +8415,10 @@
       </c>
       <c r="C287" s="2" t="n"/>
       <c r="D287" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E287" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F287" s="2" t="n"/>
       <c r="G287" s="9" t="n">
@@ -8593,14 +8593,14 @@
         </is>
       </c>
       <c r="C294" s="2" t="n"/>
-      <c r="D294" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E294" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D294" s="6" t="inlineStr">
+        <is>
+          <t>435-1: Adv Algebra II / Trig H - 1</t>
+        </is>
+      </c>
+      <c r="E294" s="6" t="inlineStr">
+        <is>
+          <t>435-1: Adv Algebra II / Trig H - 1</t>
         </is>
       </c>
       <c r="F294" s="2" t="n"/>
@@ -8627,14 +8627,14 @@
         </is>
       </c>
       <c r="C295" s="2" t="n"/>
-      <c r="D295" s="6" t="inlineStr">
-        <is>
-          <t>435-1: Adv Algebra II / Trig H - 1</t>
-        </is>
-      </c>
-      <c r="E295" s="6" t="inlineStr">
-        <is>
-          <t>435-1: Adv Algebra II / Trig H - 1</t>
+      <c r="D295" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E295" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F295" s="2" t="n"/>
@@ -8892,12 +8892,12 @@
       <c r="C305" s="2" t="n"/>
       <c r="D305" s="6" t="inlineStr">
         <is>
-          <t>120-3: American Literature - 3</t>
+          <t>120-4: American Literature - 4</t>
         </is>
       </c>
       <c r="E305" s="6" t="inlineStr">
         <is>
-          <t>120-3: American Literature - 3</t>
+          <t>120-4: American Literature - 4</t>
         </is>
       </c>
       <c r="F305" s="2" t="n"/>
@@ -8926,12 +8926,12 @@
       <c r="C306" s="2" t="n"/>
       <c r="D306" s="6" t="inlineStr">
         <is>
-          <t>120-4: American Literature - 4</t>
+          <t>120-3: American Literature - 3</t>
         </is>
       </c>
       <c r="E306" s="6" t="inlineStr">
         <is>
-          <t>120-4: American Literature - 4</t>
+          <t>120-3: American Literature - 3</t>
         </is>
       </c>
       <c r="F306" s="2" t="n"/>
@@ -8960,12 +8960,12 @@
       <c r="C307" s="2" t="n"/>
       <c r="D307" s="6" t="inlineStr">
         <is>
-          <t>120-2: American Literature - 2</t>
+          <t>120-1: American Literature - 1</t>
         </is>
       </c>
       <c r="E307" s="6" t="inlineStr">
         <is>
-          <t>120-2: American Literature - 2</t>
+          <t>120-1: American Literature - 1</t>
         </is>
       </c>
       <c r="F307" s="2" t="n"/>
@@ -8994,12 +8994,12 @@
       <c r="C308" s="2" t="n"/>
       <c r="D308" s="6" t="inlineStr">
         <is>
-          <t>120-1: American Literature - 1</t>
+          <t>120-2: American Literature - 2</t>
         </is>
       </c>
       <c r="E308" s="6" t="inlineStr">
         <is>
-          <t>120-1: American Literature - 1</t>
+          <t>120-2: American Literature - 2</t>
         </is>
       </c>
       <c r="F308" s="2" t="n"/>
@@ -9520,12 +9520,12 @@
       <c r="C328" s="2" t="n"/>
       <c r="D328" s="6" t="inlineStr">
         <is>
-          <t>849-1-F: Catholic Social Teaching - 1</t>
-        </is>
-      </c>
-      <c r="E328" s="6" t="inlineStr">
-        <is>
-          <t>849-8-S: Catholic Social Teaching - 8</t>
+          <t>849-2-F: Catholic Social Teaching - 2</t>
+        </is>
+      </c>
+      <c r="E328" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F328" s="2" t="n"/>
@@ -9559,7 +9559,7 @@
       </c>
       <c r="E329" s="6" t="inlineStr">
         <is>
-          <t>849-7-S: Catholic Social Teaching - 7</t>
+          <t>849-6-S: Catholic Social Teaching - 6</t>
         </is>
       </c>
       <c r="F329" s="2" t="n"/>
@@ -9586,14 +9586,14 @@
         </is>
       </c>
       <c r="C330" s="2" t="n"/>
-      <c r="D330" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D330" s="6" t="inlineStr">
+        <is>
+          <t>849-4-F: Catholic Social Teaching - 4; 830-9: Theology 11 - 9</t>
         </is>
       </c>
       <c r="E330" s="6" t="inlineStr">
         <is>
-          <t>849-5-S: Catholic Social Teaching - 5</t>
+          <t>830-9: Theology 11 - 9</t>
         </is>
       </c>
       <c r="F330" s="2" t="n"/>
@@ -9627,7 +9627,7 @@
       </c>
       <c r="E331" s="6" t="inlineStr">
         <is>
-          <t>849-6-S: Catholic Social Teaching - 6</t>
+          <t>849-7-S: Catholic Social Teaching - 7</t>
         </is>
       </c>
       <c r="F331" s="2" t="n"/>
@@ -9654,14 +9654,14 @@
         </is>
       </c>
       <c r="C332" s="2" t="n"/>
-      <c r="D332" s="6" t="inlineStr">
-        <is>
-          <t>849-4-F: Catholic Social Teaching - 4; 830-9: Theology 11 - 9</t>
+      <c r="D332" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="E332" s="6" t="inlineStr">
         <is>
-          <t>830-9: Theology 11 - 9</t>
+          <t>849-5-S: Catholic Social Teaching - 5</t>
         </is>
       </c>
       <c r="F332" s="2" t="n"/>
@@ -9690,12 +9690,12 @@
       <c r="C333" s="2" t="n"/>
       <c r="D333" s="6" t="inlineStr">
         <is>
-          <t>849-2-F: Catholic Social Teaching - 2</t>
-        </is>
-      </c>
-      <c r="E333" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+          <t>849-1-F: Catholic Social Teaching - 1</t>
+        </is>
+      </c>
+      <c r="E333" s="6" t="inlineStr">
+        <is>
+          <t>849-8-S: Catholic Social Teaching - 8</t>
         </is>
       </c>
       <c r="F333" s="2" t="n"/>
@@ -9917,14 +9917,14 @@
         </is>
       </c>
       <c r="C342" s="2" t="n"/>
-      <c r="D342" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E342" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D342" s="6" t="inlineStr">
+        <is>
+          <t>542-1: Anatomy/Physiology - 1</t>
+        </is>
+      </c>
+      <c r="E342" s="6" t="inlineStr">
+        <is>
+          <t>542-1: Anatomy/Physiology - 1</t>
         </is>
       </c>
       <c r="F342" s="2" t="n"/>
@@ -9985,14 +9985,14 @@
         </is>
       </c>
       <c r="C344" s="2" t="n"/>
-      <c r="D344" s="6" t="inlineStr">
-        <is>
-          <t>542-1: Anatomy/Physiology - 1</t>
-        </is>
-      </c>
-      <c r="E344" s="6" t="inlineStr">
-        <is>
-          <t>542-1: Anatomy/Physiology - 1</t>
+      <c r="D344" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E344" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F344" s="2" t="n"/>
@@ -10070,10 +10070,10 @@
       </c>
       <c r="C347" s="2" t="n"/>
       <c r="D347" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E347" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F347" s="2" t="n"/>
       <c r="G347" s="7" t="n">
@@ -10649,12 +10649,12 @@
       <c r="C368" s="2" t="n"/>
       <c r="D368" s="6" t="inlineStr">
         <is>
-          <t>730-2: U.S. History II - 2</t>
+          <t>730-1: U.S. History II - 1</t>
         </is>
       </c>
       <c r="E368" s="6" t="inlineStr">
         <is>
-          <t>730-2: U.S. History II - 2</t>
+          <t>730-1: U.S. History II - 1</t>
         </is>
       </c>
       <c r="F368" s="2" t="n"/>
@@ -10683,12 +10683,12 @@
       <c r="C369" s="2" t="n"/>
       <c r="D369" s="6" t="inlineStr">
         <is>
-          <t>730-1: U.S. History II - 1</t>
+          <t>730-2: U.S. History II - 2</t>
         </is>
       </c>
       <c r="E369" s="6" t="inlineStr">
         <is>
-          <t>730-1: U.S. History II - 1</t>
+          <t>730-2: U.S. History II - 2</t>
         </is>
       </c>
       <c r="F369" s="2" t="n"/>
@@ -11173,14 +11173,14 @@
         </is>
       </c>
       <c r="C388" s="2" t="n"/>
-      <c r="D388" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E388" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D388" s="6" t="inlineStr">
+        <is>
+          <t>412-3: Algebra I - 3</t>
+        </is>
+      </c>
+      <c r="E388" s="6" t="inlineStr">
+        <is>
+          <t>412-3: Algebra I - 3</t>
         </is>
       </c>
       <c r="F388" s="2" t="n"/>
@@ -11243,12 +11243,12 @@
       <c r="C390" s="2" t="n"/>
       <c r="D390" s="6" t="inlineStr">
         <is>
-          <t>420-1: Geometry - 1</t>
+          <t>420-2: Geometry - 2</t>
         </is>
       </c>
       <c r="E390" s="6" t="inlineStr">
         <is>
-          <t>420-1: Geometry - 1</t>
+          <t>420-2: Geometry - 2</t>
         </is>
       </c>
       <c r="F390" s="2" t="n"/>
@@ -11277,12 +11277,12 @@
       <c r="C391" s="2" t="n"/>
       <c r="D391" s="6" t="inlineStr">
         <is>
-          <t>420-2: Geometry - 2</t>
+          <t>420-1: Geometry - 1</t>
         </is>
       </c>
       <c r="E391" s="6" t="inlineStr">
         <is>
-          <t>420-2: Geometry - 2</t>
+          <t>420-1: Geometry - 1</t>
         </is>
       </c>
       <c r="F391" s="2" t="n"/>
@@ -11309,14 +11309,14 @@
         </is>
       </c>
       <c r="C392" s="2" t="n"/>
-      <c r="D392" s="6" t="inlineStr">
-        <is>
-          <t>412-3: Algebra I - 3</t>
-        </is>
-      </c>
-      <c r="E392" s="6" t="inlineStr">
-        <is>
-          <t>412-3: Algebra I - 3</t>
+      <c r="D392" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E392" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F392" s="2" t="n"/>
@@ -11394,10 +11394,10 @@
       </c>
       <c r="C395" s="2" t="n"/>
       <c r="D395" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E395" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F395" s="2" t="n"/>
       <c r="G395" s="7" t="n">
@@ -11803,12 +11803,12 @@
       <c r="C411" s="2" t="n"/>
       <c r="D411" s="6" t="inlineStr">
         <is>
-          <t>510-5: Biology - 5</t>
+          <t>510-3: Biology - 3</t>
         </is>
       </c>
       <c r="E411" s="6" t="inlineStr">
         <is>
-          <t>510-5: Biology - 5</t>
+          <t>510-3: Biology - 3</t>
         </is>
       </c>
       <c r="F411" s="2" t="n"/>
@@ -11837,12 +11837,12 @@
       <c r="C412" s="2" t="n"/>
       <c r="D412" s="6" t="inlineStr">
         <is>
-          <t>510-4: Biology - 4</t>
+          <t>510-5: Biology - 5</t>
         </is>
       </c>
       <c r="E412" s="6" t="inlineStr">
         <is>
-          <t>510-4: Biology - 4</t>
+          <t>510-5: Biology - 5</t>
         </is>
       </c>
       <c r="F412" s="2" t="n"/>
@@ -11869,14 +11869,14 @@
         </is>
       </c>
       <c r="C413" s="2" t="n"/>
-      <c r="D413" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E413" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D413" s="6" t="inlineStr">
+        <is>
+          <t>510-4: Biology - 4</t>
+        </is>
+      </c>
+      <c r="E413" s="6" t="inlineStr">
+        <is>
+          <t>510-4: Biology - 4</t>
         </is>
       </c>
       <c r="F413" s="2" t="n"/>
@@ -12005,14 +12005,14 @@
         </is>
       </c>
       <c r="C417" s="2" t="n"/>
-      <c r="D417" s="6" t="inlineStr">
-        <is>
-          <t>510-3: Biology - 3</t>
-        </is>
-      </c>
-      <c r="E417" s="6" t="inlineStr">
-        <is>
-          <t>510-3: Biology - 3</t>
+      <c r="D417" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E417" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F417" s="2" t="n"/>
@@ -12132,14 +12132,14 @@
         </is>
       </c>
       <c r="C423" s="2" t="n"/>
-      <c r="D423" s="6" t="inlineStr">
-        <is>
-          <t>955-4: Academic Support - 4</t>
-        </is>
-      </c>
-      <c r="E423" s="6" t="inlineStr">
-        <is>
-          <t>955-4: Academic Support - 4</t>
+      <c r="D423" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E423" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F423" s="2" t="n"/>
@@ -12236,12 +12236,12 @@
       <c r="C426" s="2" t="n"/>
       <c r="D426" s="6" t="inlineStr">
         <is>
-          <t>955-2: Academic Support - 2</t>
+          <t>955-1: Academic Support - 1</t>
         </is>
       </c>
       <c r="E426" s="6" t="inlineStr">
         <is>
-          <t>955-2: Academic Support - 2</t>
+          <t>955-1: Academic Support - 1</t>
         </is>
       </c>
       <c r="F426" s="2" t="n"/>
@@ -12270,12 +12270,12 @@
       <c r="C427" s="2" t="n"/>
       <c r="D427" s="6" t="inlineStr">
         <is>
-          <t>955-1: Academic Support - 1</t>
+          <t>955-2: Academic Support - 2</t>
         </is>
       </c>
       <c r="E427" s="6" t="inlineStr">
         <is>
-          <t>955-1: Academic Support - 1</t>
+          <t>955-2: Academic Support - 2</t>
         </is>
       </c>
       <c r="F427" s="2" t="n"/>
@@ -12302,14 +12302,14 @@
         </is>
       </c>
       <c r="C428" s="2" t="n"/>
-      <c r="D428" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E428" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D428" s="6" t="inlineStr">
+        <is>
+          <t>955-4: Academic Support - 4</t>
+        </is>
+      </c>
+      <c r="E428" s="6" t="inlineStr">
+        <is>
+          <t>955-4: Academic Support - 4</t>
         </is>
       </c>
       <c r="F428" s="2" t="n"/>
@@ -12499,12 +12499,12 @@
       <c r="C436" s="2" t="n"/>
       <c r="D436" s="6" t="inlineStr">
         <is>
-          <t>810-7: Theology 9 - 7</t>
+          <t>810-6: Theology 9 - 6</t>
         </is>
       </c>
       <c r="E436" s="6" t="inlineStr">
         <is>
-          <t>810-7: Theology 9 - 7</t>
+          <t>810-6: Theology 9 - 6</t>
         </is>
       </c>
       <c r="F436" s="2" t="n"/>
@@ -12567,12 +12567,12 @@
       <c r="C438" s="2" t="n"/>
       <c r="D438" s="6" t="inlineStr">
         <is>
-          <t>810-6: Theology 9 - 6</t>
+          <t>810-7: Theology 9 - 7</t>
         </is>
       </c>
       <c r="E438" s="6" t="inlineStr">
         <is>
-          <t>810-6: Theology 9 - 6</t>
+          <t>810-7: Theology 9 - 7</t>
         </is>
       </c>
       <c r="F438" s="2" t="n"/>
@@ -12599,14 +12599,14 @@
         </is>
       </c>
       <c r="C439" s="2" t="n"/>
-      <c r="D439" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E439" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D439" s="6" t="inlineStr">
+        <is>
+          <t>810-4: Theology 9 - 4</t>
+        </is>
+      </c>
+      <c r="E439" s="6" t="inlineStr">
+        <is>
+          <t>810-4: Theology 9 - 4</t>
         </is>
       </c>
       <c r="F439" s="2" t="n"/>
@@ -12633,14 +12633,14 @@
         </is>
       </c>
       <c r="C440" s="2" t="n"/>
-      <c r="D440" s="6" t="inlineStr">
-        <is>
-          <t>810-4: Theology 9 - 4</t>
-        </is>
-      </c>
-      <c r="E440" s="6" t="inlineStr">
-        <is>
-          <t>810-4: Theology 9 - 4</t>
+      <c r="D440" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E440" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F440" s="2" t="n"/>
@@ -13461,9 +13461,9 @@
           <t>UNASSIGNED</t>
         </is>
       </c>
-      <c r="E471" s="6" t="inlineStr">
-        <is>
-          <t>765-2-S: AP Macroeconomics - 2</t>
+      <c r="E471" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F471" s="2" t="n"/>
@@ -13490,9 +13490,9 @@
         </is>
       </c>
       <c r="C472" s="2" t="n"/>
-      <c r="D472" s="6" t="inlineStr">
-        <is>
-          <t>766-2-F: AP Microeconomics - 2</t>
+      <c r="D472" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="E472" s="7" t="inlineStr">
@@ -13631,9 +13631,9 @@
           <t>766-1-F: AP Microeconomics - 1</t>
         </is>
       </c>
-      <c r="E476" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="E476" s="6" t="inlineStr">
+        <is>
+          <t>765-2-S: AP Macroeconomics - 2</t>
         </is>
       </c>
       <c r="F476" s="2" t="n"/>
@@ -13660,9 +13660,9 @@
         </is>
       </c>
       <c r="C477" s="2" t="n"/>
-      <c r="D477" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D477" s="6" t="inlineStr">
+        <is>
+          <t>766-2-F: AP Microeconomics - 2</t>
         </is>
       </c>
       <c r="E477" s="7" t="inlineStr">
@@ -13711,10 +13711,10 @@
       </c>
       <c r="C479" s="2" t="n"/>
       <c r="D479" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E479" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F479" s="2" t="n"/>
       <c r="G479" s="7" t="n">
@@ -13857,12 +13857,12 @@
       <c r="C485" s="2" t="n"/>
       <c r="D485" s="6" t="inlineStr">
         <is>
-          <t>530-3: Physics - 3</t>
+          <t>530-2: Physics - 2</t>
         </is>
       </c>
       <c r="E485" s="6" t="inlineStr">
         <is>
-          <t>530-3: Physics - 3</t>
+          <t>530-2: Physics - 2</t>
         </is>
       </c>
       <c r="F485" s="2" t="n"/>
@@ -13891,12 +13891,12 @@
       <c r="C486" s="2" t="n"/>
       <c r="D486" s="6" t="inlineStr">
         <is>
-          <t>530-2: Physics - 2</t>
+          <t>530-3: Physics - 3</t>
         </is>
       </c>
       <c r="E486" s="6" t="inlineStr">
         <is>
-          <t>530-2: Physics - 2</t>
+          <t>530-3: Physics - 3</t>
         </is>
       </c>
       <c r="F486" s="2" t="n"/>
@@ -14188,12 +14188,12 @@
       <c r="C497" s="2" t="n"/>
       <c r="D497" s="6" t="inlineStr">
         <is>
-          <t>820-4: Theology 10 - 4</t>
+          <t>820-3: Theology 10 - 3</t>
         </is>
       </c>
       <c r="E497" s="6" t="inlineStr">
         <is>
-          <t>820-4: Theology 10 - 4</t>
+          <t>820-3: Theology 10 - 3</t>
         </is>
       </c>
       <c r="F497" s="2" t="n"/>
@@ -14220,14 +14220,14 @@
         </is>
       </c>
       <c r="C498" s="2" t="n"/>
-      <c r="D498" s="6" t="inlineStr">
-        <is>
-          <t>820-5: Theology 10 - 5</t>
-        </is>
-      </c>
-      <c r="E498" s="6" t="inlineStr">
-        <is>
-          <t>820-5: Theology 10 - 5</t>
+      <c r="D498" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E498" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F498" s="2" t="n"/>
@@ -14254,14 +14254,14 @@
         </is>
       </c>
       <c r="C499" s="2" t="n"/>
-      <c r="D499" s="6" t="inlineStr">
-        <is>
-          <t>820-3: Theology 10 - 3</t>
-        </is>
-      </c>
-      <c r="E499" s="6" t="inlineStr">
-        <is>
-          <t>820-3: Theology 10 - 3</t>
+      <c r="D499" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E499" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F499" s="2" t="n"/>
@@ -14288,14 +14288,14 @@
         </is>
       </c>
       <c r="C500" s="2" t="n"/>
-      <c r="D500" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E500" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D500" s="6" t="inlineStr">
+        <is>
+          <t>820-4: Theology 10 - 4</t>
+        </is>
+      </c>
+      <c r="E500" s="6" t="inlineStr">
+        <is>
+          <t>820-4: Theology 10 - 4</t>
         </is>
       </c>
       <c r="F500" s="2" t="n"/>
@@ -14322,14 +14322,14 @@
         </is>
       </c>
       <c r="C501" s="2" t="n"/>
-      <c r="D501" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E501" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D501" s="6" t="inlineStr">
+        <is>
+          <t>820-5: Theology 10 - 5</t>
+        </is>
+      </c>
+      <c r="E501" s="6" t="inlineStr">
+        <is>
+          <t>820-5: Theology 10 - 5</t>
         </is>
       </c>
       <c r="F501" s="2" t="n"/>
@@ -14372,11 +14372,11 @@
         </is>
       </c>
       <c r="C503" s="2" t="n"/>
-      <c r="D503" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="E503" s="9" t="n">
-        <v>5</v>
+      <c r="D503" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E503" s="7" t="n">
+        <v>3</v>
       </c>
       <c r="F503" s="2" t="n"/>
       <c r="G503" s="7" t="n">
@@ -14449,14 +14449,14 @@
         </is>
       </c>
       <c r="C507" s="2" t="n"/>
-      <c r="D507" s="6" t="inlineStr">
-        <is>
-          <t>851-4-F: Spirituality of Vocation - 4</t>
-        </is>
-      </c>
-      <c r="E507" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D507" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E507" s="6" t="inlineStr">
+        <is>
+          <t>851-6-S: Spirituality of Vocation - 6</t>
         </is>
       </c>
       <c r="F507" s="2" t="n"/>
@@ -14519,7 +14519,7 @@
       <c r="C509" s="2" t="n"/>
       <c r="D509" s="6" t="inlineStr">
         <is>
-          <t>851-1-F: Spirituality of Vocation - 1</t>
+          <t>851-2-F: Spirituality of Vocation - 2</t>
         </is>
       </c>
       <c r="E509" s="6" t="inlineStr">
@@ -14551,14 +14551,14 @@
         </is>
       </c>
       <c r="C510" s="2" t="n"/>
-      <c r="D510" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D510" s="6" t="inlineStr">
+        <is>
+          <t>830-3: Theology 11 - 3; 851-3-F: Spirituality of Vocation - 3</t>
         </is>
       </c>
       <c r="E510" s="6" t="inlineStr">
         <is>
-          <t>851-5-S: Spirituality of Vocation - 5</t>
+          <t>830-3: Theology 11 - 3</t>
         </is>
       </c>
       <c r="F510" s="2" t="n"/>
@@ -14592,7 +14592,7 @@
       </c>
       <c r="E511" s="6" t="inlineStr">
         <is>
-          <t>851-6-S: Spirituality of Vocation - 6</t>
+          <t>851-5-S: Spirituality of Vocation - 5</t>
         </is>
       </c>
       <c r="F511" s="2" t="n"/>
@@ -14621,12 +14621,12 @@
       <c r="C512" s="2" t="n"/>
       <c r="D512" s="6" t="inlineStr">
         <is>
-          <t>830-3: Theology 11 - 3; 851-2-F: Spirituality of Vocation - 2</t>
-        </is>
-      </c>
-      <c r="E512" s="6" t="inlineStr">
-        <is>
-          <t>830-3: Theology 11 - 3</t>
+          <t>851-1-F: Spirituality of Vocation - 1</t>
+        </is>
+      </c>
+      <c r="E512" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F512" s="2" t="n"/>
@@ -14655,7 +14655,7 @@
       <c r="C513" s="2" t="n"/>
       <c r="D513" s="6" t="inlineStr">
         <is>
-          <t>851-3-F: Spirituality of Vocation - 3</t>
+          <t>851-4-F: Spirituality of Vocation - 4</t>
         </is>
       </c>
       <c r="E513" s="7" t="inlineStr">
@@ -14782,12 +14782,12 @@
       <c r="C519" s="2" t="n"/>
       <c r="D519" s="6" t="inlineStr">
         <is>
-          <t>820-8: Theology 10 - 8</t>
+          <t>820-6: Theology 10 - 6</t>
         </is>
       </c>
       <c r="E519" s="6" t="inlineStr">
         <is>
-          <t>820-8: Theology 10 - 8</t>
+          <t>820-6: Theology 10 - 6</t>
         </is>
       </c>
       <c r="F519" s="2" t="n"/>
@@ -14816,12 +14816,12 @@
       <c r="C520" s="2" t="n"/>
       <c r="D520" s="6" t="inlineStr">
         <is>
-          <t>820-6: Theology 10 - 6</t>
+          <t>820-7: Theology 10 - 7</t>
         </is>
       </c>
       <c r="E520" s="6" t="inlineStr">
         <is>
-          <t>820-6: Theology 10 - 6</t>
+          <t>820-7: Theology 10 - 7</t>
         </is>
       </c>
       <c r="F520" s="2" t="n"/>
@@ -14850,12 +14850,12 @@
       <c r="C521" s="2" t="n"/>
       <c r="D521" s="6" t="inlineStr">
         <is>
-          <t>820-7: Theology 10 - 7</t>
+          <t>820-8: Theology 10 - 8</t>
         </is>
       </c>
       <c r="E521" s="6" t="inlineStr">
         <is>
-          <t>820-7: Theology 10 - 7</t>
+          <t>820-8: Theology 10 - 8</t>
         </is>
       </c>
       <c r="F521" s="2" t="n"/>
@@ -15773,14 +15773,14 @@
         </is>
       </c>
       <c r="C555" s="2" t="n"/>
-      <c r="D555" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E555" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D555" s="6" t="inlineStr">
+        <is>
+          <t>955-7: Academic Support - 7</t>
+        </is>
+      </c>
+      <c r="E555" s="6" t="inlineStr">
+        <is>
+          <t>955-7: Academic Support - 7</t>
         </is>
       </c>
       <c r="F555" s="2" t="n"/>
@@ -15943,14 +15943,14 @@
         </is>
       </c>
       <c r="C560" s="2" t="n"/>
-      <c r="D560" s="6" t="inlineStr">
-        <is>
-          <t>955-7: Academic Support - 7</t>
-        </is>
-      </c>
-      <c r="E560" s="6" t="inlineStr">
-        <is>
-          <t>955-7: Academic Support - 7</t>
+      <c r="D560" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E560" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F560" s="2" t="n"/>
@@ -16111,7 +16111,7 @@
       </c>
       <c r="E567" s="6" t="inlineStr">
         <is>
-          <t>580-4-S: Robotics Engineering - 4</t>
+          <t>580-2-S: Robotics Engineering - 2</t>
         </is>
       </c>
       <c r="F567" s="2" t="n"/>
@@ -16172,14 +16172,14 @@
         </is>
       </c>
       <c r="C569" s="2" t="n"/>
-      <c r="D569" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E569" s="6" t="inlineStr">
-        <is>
-          <t>580-2-S: Robotics Engineering - 2</t>
+      <c r="D569" s="6" t="inlineStr">
+        <is>
+          <t>580-3-F: Robotics Engineering - 3</t>
+        </is>
+      </c>
+      <c r="E569" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F569" s="2" t="n"/>
@@ -16206,9 +16206,9 @@
         </is>
       </c>
       <c r="C570" s="2" t="n"/>
-      <c r="D570" s="6" t="inlineStr">
-        <is>
-          <t>580-1-F: Robotics Engineering - 1</t>
+      <c r="D570" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="E570" s="6" t="inlineStr">
@@ -16240,14 +16240,14 @@
         </is>
       </c>
       <c r="C571" s="2" t="n"/>
-      <c r="D571" s="6" t="inlineStr">
-        <is>
-          <t>580-3-F: Robotics Engineering - 3</t>
-        </is>
-      </c>
-      <c r="E571" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D571" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E571" s="6" t="inlineStr">
+        <is>
+          <t>580-4-S: Robotics Engineering - 4</t>
         </is>
       </c>
       <c r="F571" s="2" t="n"/>
@@ -16308,9 +16308,9 @@
         </is>
       </c>
       <c r="C573" s="2" t="n"/>
-      <c r="D573" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D573" s="6" t="inlineStr">
+        <is>
+          <t>580-1-F: Robotics Engineering - 1</t>
         </is>
       </c>
       <c r="E573" s="6" t="inlineStr">
@@ -16361,8 +16361,8 @@
       <c r="D575" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="E575" s="9" t="n">
-        <v>4</v>
+      <c r="E575" s="7" t="n">
+        <v>2</v>
       </c>
       <c r="F575" s="2" t="n"/>
       <c r="G575" s="7" t="n">
@@ -16539,12 +16539,12 @@
       <c r="C582" s="2" t="n"/>
       <c r="D582" s="6" t="inlineStr">
         <is>
-          <t>521-4: Chemistry H - 4</t>
+          <t>521-3: Chemistry H - 3</t>
         </is>
       </c>
       <c r="E582" s="6" t="inlineStr">
         <is>
-          <t>521-4: Chemistry H - 4</t>
+          <t>521-3: Chemistry H - 3</t>
         </is>
       </c>
       <c r="F582" s="2" t="n"/>
@@ -16573,12 +16573,12 @@
       <c r="C583" s="2" t="n"/>
       <c r="D583" s="6" t="inlineStr">
         <is>
-          <t>521-1: Chemistry H - 1</t>
+          <t>521-2: Chemistry H - 2</t>
         </is>
       </c>
       <c r="E583" s="6" t="inlineStr">
         <is>
-          <t>521-1: Chemistry H - 1</t>
+          <t>521-2: Chemistry H - 2</t>
         </is>
       </c>
       <c r="F583" s="2" t="n"/>
@@ -16607,12 +16607,12 @@
       <c r="C584" s="2" t="n"/>
       <c r="D584" s="6" t="inlineStr">
         <is>
-          <t>521-3: Chemistry H - 3</t>
+          <t>521-1: Chemistry H - 1</t>
         </is>
       </c>
       <c r="E584" s="6" t="inlineStr">
         <is>
-          <t>521-3: Chemistry H - 3</t>
+          <t>521-1: Chemistry H - 1</t>
         </is>
       </c>
       <c r="F584" s="2" t="n"/>
@@ -16641,12 +16641,12 @@
       <c r="C585" s="2" t="n"/>
       <c r="D585" s="6" t="inlineStr">
         <is>
-          <t>521-2: Chemistry H - 2</t>
+          <t>521-4: Chemistry H - 4</t>
         </is>
       </c>
       <c r="E585" s="6" t="inlineStr">
         <is>
-          <t>521-2: Chemistry H - 2</t>
+          <t>521-4: Chemistry H - 4</t>
         </is>
       </c>
       <c r="F585" s="2" t="n"/>
@@ -16836,12 +16836,12 @@
       <c r="C593" s="2" t="n"/>
       <c r="D593" s="6" t="inlineStr">
         <is>
-          <t>720-2: U.S. History I - 2</t>
+          <t>720-1: U.S. History I - 1</t>
         </is>
       </c>
       <c r="E593" s="6" t="inlineStr">
         <is>
-          <t>720-2: U.S. History I - 2</t>
+          <t>720-1: U.S. History I - 1</t>
         </is>
       </c>
       <c r="F593" s="2" t="n"/>
@@ -16870,12 +16870,12 @@
       <c r="C594" s="2" t="n"/>
       <c r="D594" s="6" t="inlineStr">
         <is>
-          <t>720-1: U.S. History I - 1</t>
+          <t>720-2: U.S. History I - 2</t>
         </is>
       </c>
       <c r="E594" s="6" t="inlineStr">
         <is>
-          <t>720-1: U.S. History I - 1</t>
+          <t>720-2: U.S. History I - 2</t>
         </is>
       </c>
       <c r="F594" s="2" t="n"/>
@@ -17827,14 +17827,14 @@
         </is>
       </c>
       <c r="C629" s="2" t="n"/>
-      <c r="D629" s="6" t="inlineStr">
-        <is>
-          <t>322-2: Italian II - 2</t>
-        </is>
-      </c>
-      <c r="E629" s="6" t="inlineStr">
-        <is>
-          <t>322-2: Italian II - 2</t>
+      <c r="D629" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E629" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F629" s="2" t="n"/>
@@ -17861,14 +17861,14 @@
         </is>
       </c>
       <c r="C630" s="2" t="n"/>
-      <c r="D630" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E630" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D630" s="6" t="inlineStr">
+        <is>
+          <t>332-1: Italian III - 1</t>
+        </is>
+      </c>
+      <c r="E630" s="6" t="inlineStr">
+        <is>
+          <t>332-1: Italian III - 1</t>
         </is>
       </c>
       <c r="F630" s="2" t="n"/>
@@ -17931,12 +17931,12 @@
       <c r="C632" s="2" t="n"/>
       <c r="D632" s="6" t="inlineStr">
         <is>
-          <t>332-1: Italian III - 1</t>
+          <t>322-2: Italian II - 2</t>
         </is>
       </c>
       <c r="E632" s="6" t="inlineStr">
         <is>
-          <t>332-1: Italian III - 1</t>
+          <t>322-2: Italian II - 2</t>
         </is>
       </c>
       <c r="F632" s="2" t="n"/>
@@ -18013,11 +18013,11 @@
         </is>
       </c>
       <c r="C635" s="2" t="n"/>
-      <c r="D635" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="E635" s="7" t="n">
-        <v>3</v>
+      <c r="D635" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E635" s="9" t="n">
+        <v>4</v>
       </c>
       <c r="F635" s="2" t="n"/>
       <c r="G635" s="9" t="n">
@@ -18092,12 +18092,12 @@
       <c r="C639" s="2" t="n"/>
       <c r="D639" s="6" t="inlineStr">
         <is>
-          <t>733-1: AP U.S. History - 1</t>
+          <t>733-2: AP U.S. History - 2</t>
         </is>
       </c>
       <c r="E639" s="6" t="inlineStr">
         <is>
-          <t>733-1: AP U.S. History - 1</t>
+          <t>733-2: AP U.S. History - 2</t>
         </is>
       </c>
       <c r="F639" s="2" t="n"/>
@@ -18126,12 +18126,12 @@
       <c r="C640" s="2" t="n"/>
       <c r="D640" s="6" t="inlineStr">
         <is>
-          <t>733-2: AP U.S. History - 2</t>
+          <t>733-3: AP U.S. History - 3</t>
         </is>
       </c>
       <c r="E640" s="6" t="inlineStr">
         <is>
-          <t>733-2: AP U.S. History - 2</t>
+          <t>733-3: AP U.S. History - 3</t>
         </is>
       </c>
       <c r="F640" s="2" t="n"/>
@@ -18158,14 +18158,14 @@
         </is>
       </c>
       <c r="C641" s="2" t="n"/>
-      <c r="D641" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E641" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D641" s="6" t="inlineStr">
+        <is>
+          <t>722-1: Adv U.S. History I H - 1</t>
+        </is>
+      </c>
+      <c r="E641" s="6" t="inlineStr">
+        <is>
+          <t>722-1: Adv U.S. History I H - 1</t>
         </is>
       </c>
       <c r="F641" s="2" t="n"/>
@@ -18260,14 +18260,14 @@
         </is>
       </c>
       <c r="C644" s="2" t="n"/>
-      <c r="D644" s="6" t="inlineStr">
-        <is>
-          <t>722-1: Adv U.S. History I H - 1</t>
-        </is>
-      </c>
-      <c r="E644" s="6" t="inlineStr">
-        <is>
-          <t>722-1: Adv U.S. History I H - 1</t>
+      <c r="D644" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E644" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F644" s="2" t="n"/>
@@ -18296,12 +18296,12 @@
       <c r="C645" s="2" t="n"/>
       <c r="D645" s="6" t="inlineStr">
         <is>
-          <t>733-3: AP U.S. History - 3</t>
+          <t>733-1: AP U.S. History - 1</t>
         </is>
       </c>
       <c r="E645" s="6" t="inlineStr">
         <is>
-          <t>733-3: AP U.S. History - 3</t>
+          <t>733-1: AP U.S. History - 1</t>
         </is>
       </c>
       <c r="F645" s="2" t="n"/>
@@ -18423,12 +18423,12 @@
       <c r="C651" s="2" t="n"/>
       <c r="D651" s="6" t="inlineStr">
         <is>
-          <t>140-2: World Literature - 2</t>
+          <t>140-1: World Literature - 1</t>
         </is>
       </c>
       <c r="E651" s="6" t="inlineStr">
         <is>
-          <t>140-2: World Literature - 2</t>
+          <t>140-1: World Literature - 1</t>
         </is>
       </c>
       <c r="F651" s="2" t="n"/>
@@ -18457,12 +18457,12 @@
       <c r="C652" s="2" t="n"/>
       <c r="D652" s="6" t="inlineStr">
         <is>
-          <t>140-3: World Literature - 3</t>
+          <t>140-2: World Literature - 2</t>
         </is>
       </c>
       <c r="E652" s="6" t="inlineStr">
         <is>
-          <t>140-3: World Literature - 3</t>
+          <t>140-2: World Literature - 2</t>
         </is>
       </c>
       <c r="F652" s="2" t="n"/>
@@ -18627,12 +18627,12 @@
       <c r="C657" s="2" t="n"/>
       <c r="D657" s="6" t="inlineStr">
         <is>
-          <t>140-1: World Literature - 1</t>
+          <t>140-3: World Literature - 3</t>
         </is>
       </c>
       <c r="E657" s="6" t="inlineStr">
         <is>
-          <t>140-1: World Literature - 1</t>
+          <t>140-3: World Literature - 3</t>
         </is>
       </c>
       <c r="F657" s="2" t="n"/>
@@ -18854,14 +18854,14 @@
         </is>
       </c>
       <c r="C666" s="2" t="n"/>
-      <c r="D666" s="6" t="inlineStr">
-        <is>
-          <t>121-2: American Literature H - 2</t>
-        </is>
-      </c>
-      <c r="E666" s="6" t="inlineStr">
-        <is>
-          <t>121-2: American Literature H - 2</t>
+      <c r="D666" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E666" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F666" s="2" t="n"/>
@@ -18890,12 +18890,12 @@
       <c r="C667" s="2" t="n"/>
       <c r="D667" s="6" t="inlineStr">
         <is>
-          <t>121-1: American Literature H - 1</t>
+          <t>121-2: American Literature H - 2</t>
         </is>
       </c>
       <c r="E667" s="6" t="inlineStr">
         <is>
-          <t>121-1: American Literature H - 1</t>
+          <t>121-2: American Literature H - 2</t>
         </is>
       </c>
       <c r="F667" s="2" t="n"/>
@@ -18922,14 +18922,14 @@
         </is>
       </c>
       <c r="C668" s="2" t="n"/>
-      <c r="D668" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E668" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D668" s="6" t="inlineStr">
+        <is>
+          <t>121-1: American Literature H - 1</t>
+        </is>
+      </c>
+      <c r="E668" s="6" t="inlineStr">
+        <is>
+          <t>121-1: American Literature H - 1</t>
         </is>
       </c>
       <c r="F668" s="2" t="n"/>
@@ -19085,12 +19085,12 @@
       <c r="C675" s="2" t="n"/>
       <c r="D675" s="6" t="inlineStr">
         <is>
-          <t>420-4: Geometry - 4</t>
+          <t>410-1: Algebra I - 1</t>
         </is>
       </c>
       <c r="E675" s="6" t="inlineStr">
         <is>
-          <t>420-4: Geometry - 4</t>
+          <t>410-1: Algebra I - 1</t>
         </is>
       </c>
       <c r="F675" s="2" t="n"/>
@@ -19119,12 +19119,12 @@
       <c r="C676" s="2" t="n"/>
       <c r="D676" s="6" t="inlineStr">
         <is>
-          <t>410-1: Algebra I - 1</t>
+          <t>420-4: Geometry - 4</t>
         </is>
       </c>
       <c r="E676" s="6" t="inlineStr">
         <is>
-          <t>410-1: Algebra I - 1</t>
+          <t>420-4: Geometry - 4</t>
         </is>
       </c>
       <c r="F676" s="2" t="n"/>
@@ -19516,14 +19516,14 @@
         </is>
       </c>
       <c r="C690" s="2" t="n"/>
-      <c r="D690" s="6" t="inlineStr">
-        <is>
-          <t>830-7: Theology 11 - 7</t>
-        </is>
-      </c>
-      <c r="E690" s="6" t="inlineStr">
-        <is>
-          <t>830-7: Theology 11 - 7</t>
+      <c r="D690" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E690" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F690" s="2" t="n"/>
@@ -19552,12 +19552,12 @@
       <c r="C691" s="2" t="n"/>
       <c r="D691" s="6" t="inlineStr">
         <is>
-          <t>830-5: Theology 11 - 5</t>
+          <t>830-7: Theology 11 - 7</t>
         </is>
       </c>
       <c r="E691" s="6" t="inlineStr">
         <is>
-          <t>830-5: Theology 11 - 5</t>
+          <t>830-7: Theology 11 - 7</t>
         </is>
       </c>
       <c r="F691" s="2" t="n"/>
@@ -19584,14 +19584,14 @@
         </is>
       </c>
       <c r="C692" s="2" t="n"/>
-      <c r="D692" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E692" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D692" s="6" t="inlineStr">
+        <is>
+          <t>830-5: Theology 11 - 5</t>
+        </is>
+      </c>
+      <c r="E692" s="6" t="inlineStr">
+        <is>
+          <t>830-5: Theology 11 - 5</t>
         </is>
       </c>
       <c r="F692" s="2" t="n"/>
@@ -20115,9 +20115,9 @@
           <t>2034-1-F: TV/Film Production &amp; Editing I - 1</t>
         </is>
       </c>
-      <c r="E712" s="6" t="inlineStr">
-        <is>
-          <t>2044-2-S: TV/Film Production II - 2</t>
+      <c r="E712" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F712" s="2" t="n"/>
@@ -20183,9 +20183,9 @@
           <t>UNASSIGNED</t>
         </is>
       </c>
-      <c r="E714" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="E714" s="6" t="inlineStr">
+        <is>
+          <t>2044-2-S: TV/Film Production II - 2</t>
         </is>
       </c>
       <c r="F714" s="2" t="n"/>
@@ -20333,8 +20333,8 @@
       <c r="D719" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="E719" s="7" t="n">
-        <v>3</v>
+      <c r="E719" s="9" t="n">
+        <v>4</v>
       </c>
       <c r="F719" s="2" t="n"/>
       <c r="G719" s="7" t="n">
@@ -20443,12 +20443,12 @@
       <c r="C724" s="2" t="n"/>
       <c r="D724" s="6" t="inlineStr">
         <is>
-          <t>711-1: World History H - 1</t>
+          <t>713-2: AP World History - 2</t>
         </is>
       </c>
       <c r="E724" s="6" t="inlineStr">
         <is>
-          <t>711-1: World History H - 1</t>
+          <t>713-2: AP World History - 2</t>
         </is>
       </c>
       <c r="F724" s="2" t="n"/>
@@ -20475,14 +20475,14 @@
         </is>
       </c>
       <c r="C725" s="2" t="n"/>
-      <c r="D725" s="6" t="inlineStr">
-        <is>
-          <t>713-2: AP World History - 2</t>
+      <c r="D725" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="E725" s="6" t="inlineStr">
         <is>
-          <t>713-2: AP World History - 2</t>
+          <t>744-2-S: Sociology - 2</t>
         </is>
       </c>
       <c r="F725" s="2" t="n"/>
@@ -20509,14 +20509,14 @@
         </is>
       </c>
       <c r="C726" s="2" t="n"/>
-      <c r="D726" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E726" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D726" s="6" t="inlineStr">
+        <is>
+          <t>711-1: World History H - 1</t>
+        </is>
+      </c>
+      <c r="E726" s="6" t="inlineStr">
+        <is>
+          <t>711-1: World History H - 1</t>
         </is>
       </c>
       <c r="F726" s="2" t="n"/>
@@ -20616,9 +20616,9 @@
           <t>744-1-F: Sociology - 1</t>
         </is>
       </c>
-      <c r="E729" s="6" t="inlineStr">
-        <is>
-          <t>744-2-S: Sociology - 2</t>
+      <c r="E729" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F729" s="2" t="n"/>
@@ -20661,11 +20661,11 @@
         </is>
       </c>
       <c r="C731" s="2" t="n"/>
-      <c r="D731" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="E731" s="7" t="n">
-        <v>3</v>
+      <c r="D731" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E731" s="9" t="n">
+        <v>6</v>
       </c>
       <c r="F731" s="2" t="n"/>
       <c r="G731" s="7" t="n">
@@ -20738,14 +20738,14 @@
         </is>
       </c>
       <c r="C735" s="2" t="n"/>
-      <c r="D735" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E735" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D735" s="6" t="inlineStr">
+        <is>
+          <t>331-3: Spanish III H - 3</t>
+        </is>
+      </c>
+      <c r="E735" s="6" t="inlineStr">
+        <is>
+          <t>331-3: Spanish III H - 3</t>
         </is>
       </c>
       <c r="F735" s="2" t="n"/>
@@ -20806,14 +20806,14 @@
         </is>
       </c>
       <c r="C737" s="2" t="n"/>
-      <c r="D737" s="6" t="inlineStr">
-        <is>
-          <t>330-3: Spanish III - 3</t>
-        </is>
-      </c>
-      <c r="E737" s="6" t="inlineStr">
-        <is>
-          <t>330-3: Spanish III - 3</t>
+      <c r="D737" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E737" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F737" s="2" t="n"/>
@@ -20842,12 +20842,12 @@
       <c r="C738" s="2" t="n"/>
       <c r="D738" s="6" t="inlineStr">
         <is>
-          <t>330-2: Spanish III - 2</t>
+          <t>330-3: Spanish III - 3</t>
         </is>
       </c>
       <c r="E738" s="6" t="inlineStr">
         <is>
-          <t>330-2: Spanish III - 2</t>
+          <t>330-3: Spanish III - 3</t>
         </is>
       </c>
       <c r="F738" s="2" t="n"/>
@@ -20876,12 +20876,12 @@
       <c r="C739" s="2" t="n"/>
       <c r="D739" s="6" t="inlineStr">
         <is>
-          <t>331-3: Spanish III H - 3</t>
+          <t>330-2: Spanish III - 2</t>
         </is>
       </c>
       <c r="E739" s="6" t="inlineStr">
         <is>
-          <t>331-3: Spanish III H - 3</t>
+          <t>330-2: Spanish III - 2</t>
         </is>
       </c>
       <c r="F739" s="2" t="n"/>
@@ -20910,12 +20910,12 @@
       <c r="C740" s="2" t="n"/>
       <c r="D740" s="6" t="inlineStr">
         <is>
-          <t>331-2: Spanish III H - 2</t>
+          <t>331-1: Spanish III H - 1</t>
         </is>
       </c>
       <c r="E740" s="6" t="inlineStr">
         <is>
-          <t>331-2: Spanish III H - 2</t>
+          <t>331-1: Spanish III H - 1</t>
         </is>
       </c>
       <c r="F740" s="2" t="n"/>
@@ -20944,12 +20944,12 @@
       <c r="C741" s="2" t="n"/>
       <c r="D741" s="6" t="inlineStr">
         <is>
-          <t>331-1: Spanish III H - 1</t>
+          <t>331-2: Spanish III H - 2</t>
         </is>
       </c>
       <c r="E741" s="6" t="inlineStr">
         <is>
-          <t>331-1: Spanish III H - 1</t>
+          <t>331-2: Spanish III H - 2</t>
         </is>
       </c>
       <c r="F741" s="2" t="n"/>
@@ -20993,10 +20993,10 @@
       </c>
       <c r="C743" s="2" t="n"/>
       <c r="D743" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E743" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F743" s="2" t="n"/>
       <c r="G743" s="9" t="n">
@@ -21069,14 +21069,14 @@
         </is>
       </c>
       <c r="C747" s="2" t="n"/>
-      <c r="D747" s="6" t="inlineStr">
-        <is>
-          <t>708-1-F: Introduction to Business - 1</t>
-        </is>
-      </c>
-      <c r="E747" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D747" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E747" s="6" t="inlineStr">
+        <is>
+          <t>708-2-S: Introduction to Business - 2</t>
         </is>
       </c>
       <c r="F747" s="2" t="n"/>
@@ -21108,9 +21108,9 @@
           <t>UNASSIGNED</t>
         </is>
       </c>
-      <c r="E748" s="6" t="inlineStr">
-        <is>
-          <t>708-2-S: Introduction to Business - 2</t>
+      <c r="E748" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F748" s="2" t="n"/>
@@ -21137,14 +21137,14 @@
         </is>
       </c>
       <c r="C749" s="2" t="n"/>
-      <c r="D749" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E749" s="6" t="inlineStr">
-        <is>
-          <t>708-4-S: Introduction to Business - 4</t>
+      <c r="D749" s="6" t="inlineStr">
+        <is>
+          <t>708-5-F: Introduction to Business - 5</t>
+        </is>
+      </c>
+      <c r="E749" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F749" s="2" t="n"/>
@@ -21173,7 +21173,7 @@
       <c r="C750" s="2" t="n"/>
       <c r="D750" s="6" t="inlineStr">
         <is>
-          <t>708-5-F: Introduction to Business - 5</t>
+          <t>708-1-F: Introduction to Business - 1</t>
         </is>
       </c>
       <c r="E750" s="7" t="inlineStr">
@@ -21210,9 +21210,9 @@
           <t>UNASSIGNED</t>
         </is>
       </c>
-      <c r="E751" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="E751" s="6" t="inlineStr">
+        <is>
+          <t>708-4-S: Introduction to Business - 4</t>
         </is>
       </c>
       <c r="F751" s="2" t="n"/>
@@ -21324,10 +21324,10 @@
       </c>
       <c r="C755" s="2" t="n"/>
       <c r="D755" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E755" s="7" t="n">
         <v>1</v>
-      </c>
-      <c r="E755" s="7" t="n">
-        <v>2</v>
       </c>
       <c r="F755" s="2" t="n"/>
       <c r="G755" s="7" t="n">
@@ -21504,12 +21504,12 @@
       <c r="C762" s="2" t="n"/>
       <c r="D762" s="6" t="inlineStr">
         <is>
-          <t>710-3: World History - 3</t>
+          <t>710-2: World History - 2</t>
         </is>
       </c>
       <c r="E762" s="6" t="inlineStr">
         <is>
-          <t>710-3: World History - 3</t>
+          <t>710-2: World History - 2</t>
         </is>
       </c>
       <c r="F762" s="2" t="n"/>
@@ -21538,7 +21538,7 @@
       <c r="C763" s="2" t="n"/>
       <c r="D763" s="6" t="inlineStr">
         <is>
-          <t>741-3-F: Psychology - 3</t>
+          <t>741-3-F: Psychology - 3; 723-1-F: Introduction to Political Science - 1</t>
         </is>
       </c>
       <c r="E763" s="7" t="inlineStr">
@@ -21572,12 +21572,12 @@
       <c r="C764" s="2" t="n"/>
       <c r="D764" s="6" t="inlineStr">
         <is>
-          <t>710-2: World History - 2</t>
+          <t>710-3: World History - 3</t>
         </is>
       </c>
       <c r="E764" s="6" t="inlineStr">
         <is>
-          <t>710-2: World History - 2</t>
+          <t>710-3: World History - 3</t>
         </is>
       </c>
       <c r="F764" s="2" t="n"/>
@@ -21606,7 +21606,7 @@
       <c r="C765" s="2" t="n"/>
       <c r="D765" s="6" t="inlineStr">
         <is>
-          <t>710-1: World History - 1; 723-1-F: Introduction to Political Science - 1</t>
+          <t>710-1: World History - 1</t>
         </is>
       </c>
       <c r="E765" s="6" t="inlineStr">
@@ -21733,12 +21733,12 @@
       <c r="C771" s="2" t="n"/>
       <c r="D771" s="6" t="inlineStr">
         <is>
-          <t>110-3: Composition &amp; Literature - 3</t>
+          <t>110-5: Composition &amp; Literature - 5</t>
         </is>
       </c>
       <c r="E771" s="6" t="inlineStr">
         <is>
-          <t>110-3: Composition &amp; Literature - 3</t>
+          <t>110-5: Composition &amp; Literature - 5</t>
         </is>
       </c>
       <c r="F771" s="2" t="n"/>
@@ -21767,12 +21767,12 @@
       <c r="C772" s="2" t="n"/>
       <c r="D772" s="6" t="inlineStr">
         <is>
-          <t>110-5: Composition &amp; Literature - 5</t>
+          <t>110-4: Composition &amp; Literature - 4</t>
         </is>
       </c>
       <c r="E772" s="6" t="inlineStr">
         <is>
-          <t>110-5: Composition &amp; Literature - 5</t>
+          <t>110-4: Composition &amp; Literature - 4</t>
         </is>
       </c>
       <c r="F772" s="2" t="n"/>
@@ -21835,12 +21835,12 @@
       <c r="C774" s="2" t="n"/>
       <c r="D774" s="6" t="inlineStr">
         <is>
-          <t>110-4: Composition &amp; Literature - 4</t>
+          <t>110-3: Composition &amp; Literature - 3</t>
         </is>
       </c>
       <c r="E774" s="6" t="inlineStr">
         <is>
-          <t>110-4: Composition &amp; Literature - 4</t>
+          <t>110-3: Composition &amp; Literature - 3</t>
         </is>
       </c>
       <c r="F774" s="2" t="n"/>
@@ -21901,14 +21901,14 @@
         </is>
       </c>
       <c r="C776" s="2" t="n"/>
-      <c r="D776" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E776" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D776" s="6" t="inlineStr">
+        <is>
+          <t>110-6: Composition &amp; Literature - 6</t>
+        </is>
+      </c>
+      <c r="E776" s="6" t="inlineStr">
+        <is>
+          <t>110-6: Composition &amp; Literature - 6</t>
         </is>
       </c>
       <c r="F776" s="2" t="n"/>
@@ -21935,14 +21935,14 @@
         </is>
       </c>
       <c r="C777" s="2" t="n"/>
-      <c r="D777" s="6" t="inlineStr">
-        <is>
-          <t>110-6: Composition &amp; Literature - 6</t>
-        </is>
-      </c>
-      <c r="E777" s="6" t="inlineStr">
-        <is>
-          <t>110-6: Composition &amp; Literature - 6</t>
+      <c r="D777" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E777" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F777" s="2" t="n"/>
@@ -21986,10 +21986,10 @@
       </c>
       <c r="C779" s="2" t="n"/>
       <c r="D779" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E779" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F779" s="2" t="n"/>
       <c r="G779" s="9" t="n">
@@ -22393,14 +22393,14 @@
         </is>
       </c>
       <c r="C795" s="2" t="n"/>
-      <c r="D795" s="6" t="inlineStr">
-        <is>
-          <t>820-2: Theology 10 - 2</t>
-        </is>
-      </c>
-      <c r="E795" s="6" t="inlineStr">
-        <is>
-          <t>820-2: Theology 10 - 2</t>
+      <c r="D795" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E795" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F795" s="2" t="n"/>
@@ -22463,12 +22463,12 @@
       <c r="C797" s="2" t="n"/>
       <c r="D797" s="6" t="inlineStr">
         <is>
-          <t>810-3: Theology 9 - 3</t>
+          <t>810-2: Theology 9 - 2</t>
         </is>
       </c>
       <c r="E797" s="6" t="inlineStr">
         <is>
-          <t>810-3: Theology 9 - 3</t>
+          <t>810-2: Theology 9 - 2</t>
         </is>
       </c>
       <c r="F797" s="2" t="n"/>
@@ -22495,14 +22495,14 @@
         </is>
       </c>
       <c r="C798" s="2" t="n"/>
-      <c r="D798" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E798" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D798" s="6" t="inlineStr">
+        <is>
+          <t>820-2: Theology 10 - 2</t>
+        </is>
+      </c>
+      <c r="E798" s="6" t="inlineStr">
+        <is>
+          <t>820-2: Theology 10 - 2</t>
         </is>
       </c>
       <c r="F798" s="2" t="n"/>
@@ -22531,12 +22531,12 @@
       <c r="C799" s="2" t="n"/>
       <c r="D799" s="6" t="inlineStr">
         <is>
-          <t>810-2: Theology 9 - 2</t>
+          <t>820-1: Theology 10 - 1</t>
         </is>
       </c>
       <c r="E799" s="6" t="inlineStr">
         <is>
-          <t>810-2: Theology 9 - 2</t>
+          <t>820-1: Theology 10 - 1</t>
         </is>
       </c>
       <c r="F799" s="2" t="n"/>
@@ -22565,12 +22565,12 @@
       <c r="C800" s="2" t="n"/>
       <c r="D800" s="6" t="inlineStr">
         <is>
-          <t>820-1: Theology 10 - 1</t>
+          <t>810-3: Theology 9 - 3</t>
         </is>
       </c>
       <c r="E800" s="6" t="inlineStr">
         <is>
-          <t>820-1: Theology 10 - 1</t>
+          <t>810-3: Theology 9 - 3</t>
         </is>
       </c>
       <c r="F800" s="2" t="n"/>
@@ -22647,11 +22647,11 @@
         </is>
       </c>
       <c r="C803" s="2" t="n"/>
-      <c r="D803" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="E803" s="7" t="n">
-        <v>3</v>
+      <c r="D803" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E803" s="9" t="n">
+        <v>5</v>
       </c>
       <c r="F803" s="2" t="n"/>
       <c r="G803" s="7" t="n">
@@ -23057,12 +23057,12 @@
       <c r="C819" s="2" t="n"/>
       <c r="D819" s="6" t="inlineStr">
         <is>
-          <t>310-3: Spanish I - 3</t>
+          <t>310-5: Spanish I - 5</t>
         </is>
       </c>
       <c r="E819" s="6" t="inlineStr">
         <is>
-          <t>310-3: Spanish I - 3</t>
+          <t>310-5: Spanish I - 5</t>
         </is>
       </c>
       <c r="F819" s="2" t="n"/>
@@ -23089,14 +23089,14 @@
         </is>
       </c>
       <c r="C820" s="2" t="n"/>
-      <c r="D820" s="6" t="inlineStr">
-        <is>
-          <t>310-5: Spanish I - 5</t>
-        </is>
-      </c>
-      <c r="E820" s="6" t="inlineStr">
-        <is>
-          <t>310-5: Spanish I - 5</t>
+      <c r="D820" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E820" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F820" s="2" t="n"/>
@@ -23125,12 +23125,12 @@
       <c r="C821" s="2" t="n"/>
       <c r="D821" s="6" t="inlineStr">
         <is>
-          <t>310-2: Spanish I - 2</t>
+          <t>310-4: Spanish I - 4</t>
         </is>
       </c>
       <c r="E821" s="6" t="inlineStr">
         <is>
-          <t>310-2: Spanish I - 2</t>
+          <t>310-4: Spanish I - 4</t>
         </is>
       </c>
       <c r="F821" s="2" t="n"/>
@@ -23159,12 +23159,12 @@
       <c r="C822" s="2" t="n"/>
       <c r="D822" s="6" t="inlineStr">
         <is>
-          <t>310-4: Spanish I - 4</t>
+          <t>310-3: Spanish I - 3</t>
         </is>
       </c>
       <c r="E822" s="6" t="inlineStr">
         <is>
-          <t>310-4: Spanish I - 4</t>
+          <t>310-3: Spanish I - 3</t>
         </is>
       </c>
       <c r="F822" s="2" t="n"/>
@@ -23225,14 +23225,14 @@
         </is>
       </c>
       <c r="C824" s="2" t="n"/>
-      <c r="D824" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E824" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D824" s="6" t="inlineStr">
+        <is>
+          <t>310-2: Spanish I - 2</t>
+        </is>
+      </c>
+      <c r="E824" s="6" t="inlineStr">
+        <is>
+          <t>310-2: Spanish I - 2</t>
         </is>
       </c>
       <c r="F824" s="2" t="n"/>
@@ -23388,12 +23388,12 @@
       <c r="C831" s="2" t="n"/>
       <c r="D831" s="6" t="inlineStr">
         <is>
-          <t>145-1-F: Journalism - 1</t>
-        </is>
-      </c>
-      <c r="E831" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+          <t>130-3: British Literature - 3</t>
+        </is>
+      </c>
+      <c r="E831" s="6" t="inlineStr">
+        <is>
+          <t>130-3: British Literature - 3</t>
         </is>
       </c>
       <c r="F831" s="2" t="n"/>
@@ -23420,9 +23420,9 @@
         </is>
       </c>
       <c r="C832" s="2" t="n"/>
-      <c r="D832" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D832" s="6" t="inlineStr">
+        <is>
+          <t>145-1-F: Journalism - 1</t>
         </is>
       </c>
       <c r="E832" s="7" t="inlineStr">
@@ -23558,12 +23558,12 @@
       <c r="C836" s="2" t="n"/>
       <c r="D836" s="6" t="inlineStr">
         <is>
-          <t>130-3: British Literature - 3</t>
+          <t>130-4: British Literature - 4</t>
         </is>
       </c>
       <c r="E836" s="6" t="inlineStr">
         <is>
-          <t>130-3: British Literature - 3</t>
+          <t>130-4: British Literature - 4</t>
         </is>
       </c>
       <c r="F836" s="2" t="n"/>
@@ -23590,14 +23590,14 @@
         </is>
       </c>
       <c r="C837" s="2" t="n"/>
-      <c r="D837" s="6" t="inlineStr">
-        <is>
-          <t>130-4: British Literature - 4</t>
-        </is>
-      </c>
-      <c r="E837" s="6" t="inlineStr">
-        <is>
-          <t>130-4: British Literature - 4</t>
+      <c r="D837" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E837" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F837" s="2" t="n"/>
@@ -23641,10 +23641,10 @@
       </c>
       <c r="C839" s="2" t="n"/>
       <c r="D839" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="E839" s="9" t="n">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="E839" s="7" t="n">
+        <v>3</v>
       </c>
       <c r="F839" s="2" t="n"/>
       <c r="G839" s="7" t="n">
@@ -24050,12 +24050,12 @@
       <c r="C855" s="2" t="n"/>
       <c r="D855" s="6" t="inlineStr">
         <is>
-          <t>410-4: Algebra I - 4</t>
+          <t>420-5: Geometry - 5</t>
         </is>
       </c>
       <c r="E855" s="6" t="inlineStr">
         <is>
-          <t>410-4: Algebra I - 4</t>
+          <t>420-5: Geometry - 5</t>
         </is>
       </c>
       <c r="F855" s="2" t="n"/>
@@ -24084,12 +24084,12 @@
       <c r="C856" s="2" t="n"/>
       <c r="D856" s="6" t="inlineStr">
         <is>
-          <t>420-5: Geometry - 5</t>
+          <t>410-5: Algebra I - 5</t>
         </is>
       </c>
       <c r="E856" s="6" t="inlineStr">
         <is>
-          <t>420-5: Geometry - 5</t>
+          <t>410-5: Algebra I - 5</t>
         </is>
       </c>
       <c r="F856" s="2" t="n"/>
@@ -24118,12 +24118,12 @@
       <c r="C857" s="2" t="n"/>
       <c r="D857" s="6" t="inlineStr">
         <is>
-          <t>410-5: Algebra I - 5</t>
+          <t>410-4: Algebra I - 4</t>
         </is>
       </c>
       <c r="E857" s="6" t="inlineStr">
         <is>
-          <t>410-5: Algebra I - 5</t>
+          <t>410-4: Algebra I - 4</t>
         </is>
       </c>
       <c r="F857" s="2" t="n"/>
@@ -24549,14 +24549,14 @@
         </is>
       </c>
       <c r="C872" s="2" t="n"/>
-      <c r="D872" s="6" t="inlineStr">
-        <is>
-          <t>710-6: World History - 6</t>
-        </is>
-      </c>
-      <c r="E872" s="6" t="inlineStr">
-        <is>
-          <t>710-6: World History - 6</t>
+      <c r="D872" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E872" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F872" s="2" t="n"/>
@@ -24583,14 +24583,14 @@
         </is>
       </c>
       <c r="C873" s="2" t="n"/>
-      <c r="D873" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E873" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D873" s="6" t="inlineStr">
+        <is>
+          <t>710-6: World History - 6</t>
+        </is>
+      </c>
+      <c r="E873" s="6" t="inlineStr">
+        <is>
+          <t>710-6: World History - 6</t>
         </is>
       </c>
       <c r="F873" s="2" t="n"/>
@@ -24634,10 +24634,10 @@
       </c>
       <c r="C875" s="2" t="n"/>
       <c r="D875" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E875" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F875" s="2" t="n"/>
       <c r="G875" s="9" t="n">
@@ -24715,9 +24715,9 @@
           <t>UNASSIGNED</t>
         </is>
       </c>
-      <c r="E879" s="6" t="inlineStr">
-        <is>
-          <t>732-2-S: Business Law - 2</t>
+      <c r="E879" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F879" s="2" t="n"/>
@@ -24744,14 +24744,14 @@
         </is>
       </c>
       <c r="C880" s="2" t="n"/>
-      <c r="D880" s="6" t="inlineStr">
-        <is>
-          <t>732-3-F: Business Law - 3</t>
-        </is>
-      </c>
-      <c r="E880" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D880" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E880" s="6" t="inlineStr">
+        <is>
+          <t>732-2-S: Business Law - 2</t>
         </is>
       </c>
       <c r="F880" s="2" t="n"/>
@@ -24778,9 +24778,9 @@
         </is>
       </c>
       <c r="C881" s="2" t="n"/>
-      <c r="D881" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D881" s="6" t="inlineStr">
+        <is>
+          <t>732-3-F: Business Law - 3</t>
         </is>
       </c>
       <c r="E881" s="7" t="inlineStr">
@@ -24965,7 +24965,7 @@
       </c>
       <c r="C887" s="2" t="n"/>
       <c r="D887" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E887" s="9" t="n">
         <v>4</v>
@@ -25143,14 +25143,14 @@
         </is>
       </c>
       <c r="C894" s="2" t="n"/>
-      <c r="D894" s="6" t="inlineStr">
-        <is>
-          <t>312-2: Italian I - 2</t>
-        </is>
-      </c>
-      <c r="E894" s="6" t="inlineStr">
-        <is>
-          <t>312-2: Italian I - 2</t>
+      <c r="D894" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="E894" s="7" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
         </is>
       </c>
       <c r="F894" s="2" t="n"/>
@@ -25245,14 +25245,14 @@
         </is>
       </c>
       <c r="C897" s="2" t="n"/>
-      <c r="D897" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="E897" s="7" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
+      <c r="D897" s="6" t="inlineStr">
+        <is>
+          <t>312-2: Italian I - 2</t>
+        </is>
+      </c>
+      <c r="E897" s="6" t="inlineStr">
+        <is>
+          <t>312-2: Italian I - 2</t>
         </is>
       </c>
       <c r="F897" s="2" t="n"/>
@@ -25295,11 +25295,11 @@
         </is>
       </c>
       <c r="C899" s="2" t="n"/>
-      <c r="D899" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="E899" s="9" t="n">
-        <v>6</v>
+      <c r="D899" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E899" s="7" t="n">
+        <v>3</v>
       </c>
       <c r="F899" s="2" t="n"/>
       <c r="G899" s="7" t="n">
